--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP70" headerRowCount="1">
-  <autoFilter ref="A1:EP70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP77" headerRowCount="1">
+  <autoFilter ref="A1:EP77"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP70"/>
+  <dimension ref="A1:EP77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -1504,119 +1504,111 @@
         <v>2</v>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>19</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>22</v>
-      </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Stadio Georgios Karaiskáki</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Poseidonos Avenue, Faliro, Piraeus</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>5.62</v>
+        <v>3.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.6</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -1640,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>116</v>
+        <v>5131</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -1661,37 +1653,37 @@
         <v>1</v>
       </c>
       <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
         <v>5</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7</v>
-      </c>
       <c r="BL2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BM2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT2" t="n">
         <v>3</v>
@@ -1700,25 +1692,25 @@
         <v>1</v>
       </c>
       <c r="BV2" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="BX2" t="n">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="BY2" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.31</v>
+        <v>1.22</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1757,37 +1749,37 @@
         <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ2" t="n">
         <v>1</v>
       </c>
       <c r="CR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS2" t="n">
         <v>24</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU2" t="n">
         <v>13</v>
       </c>
-      <c r="CT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>10</v>
-      </c>
       <c r="CV2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW2" t="n">
         <v>1</v>
       </c>
       <c r="CX2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="CY2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ2" t="n">
         <v>0</v>
@@ -1802,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -1859,14 +1851,14 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>32.47</v>
+        <v>31.84</v>
       </c>
       <c r="DX2" t="n">
-        <v>7.28</v>
+        <v>5.87</v>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
@@ -1874,84 +1866,60 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>5.54</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1939,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -1992,19 +1960,19 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -2013,90 +1981,98 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" t="n">
         <v>10</v>
       </c>
-      <c r="W3" t="n">
-        <v>16</v>
-      </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Stadio Georgios Karaiskáki</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Poseidonos Avenue, Faliro, Piraeus</t>
+        </is>
+      </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.4</v>
+        <v>5.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>5</v>
+        <v>18.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.98</v>
+        <v>2.95</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AU3" t="n">
         <v>2</v>
@@ -2120,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>5131</v>
+        <v>116</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -2141,37 +2117,37 @@
         <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BN3" t="n">
         <v>9</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>3</v>
@@ -2180,25 +2156,25 @@
         <v>1</v>
       </c>
       <c r="BV3" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="BW3" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="BX3" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="BY3" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.51</v>
+        <v>2.26</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.22</v>
+        <v>0.31</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -2237,37 +2213,37 @@
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
         <v>1</v>
       </c>
       <c r="CR3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="CS3" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CT3" t="n">
         <v>1</v>
       </c>
       <c r="CU3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW3" t="n">
         <v>1</v>
       </c>
       <c r="CX3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="CY3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ3" t="n">
         <v>0</v>
@@ -2282,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.5</v>
+        <v>0.17</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2339,14 +2315,14 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>31.84</v>
+        <v>32.47</v>
       </c>
       <c r="DX3" t="n">
-        <v>5.87</v>
+        <v>7.28</v>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
@@ -2354,60 +2330,84 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr"/>
-      <c r="EB3" t="inlineStr"/>
-      <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>16.28</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
         <v>1.2</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE5" t="n">
         <v>0.2</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>2.17</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="DE8" t="n">
         <v>2</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5130,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6090,10 +6090,10 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE12" t="n">
         <v>0.17</v>
@@ -6603,7 +6603,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7050,10 +7050,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         <v>2.2</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8059,7 +8059,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -8208,119 +8208,119 @@
         <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>5</v>
       </c>
-      <c r="N16" t="n">
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
         <v>6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8</v>
       </c>
       <c r="U16" t="n">
         <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y16" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z16" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AU16" t="n">
         <v>3</v>
@@ -8329,22 +8329,22 @@
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
-        <v>5199</v>
+        <v>5131</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8368,61 +8368,61 @@
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
         <v>1</v>
       </c>
       <c r="BR16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BT16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW16" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="BX16" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="BY16" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8470,46 +8470,46 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CS16" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
         <v>17</v>
       </c>
-      <c r="CT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>16</v>
-      </c>
       <c r="CV16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
       </c>
       <c r="DA16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8521,25 +8521,25 @@
         <v>1.5</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8563,14 +8563,14 @@
         <v>1</v>
       </c>
       <c r="DW16" t="n">
-        <v>35.99</v>
+        <v>29.9</v>
       </c>
       <c r="DX16" t="n">
-        <v>5.68</v>
+        <v>6.93</v>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8582,64 +8582,72 @@
       <c r="EB16" t="inlineStr"/>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr"/>
-      <c r="EH16" t="inlineStr"/>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -8659,12 +8667,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8680,19 +8688,19 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -8701,98 +8709,98 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="Z17" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AM17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
         <v>3.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
@@ -8801,22 +8809,22 @@
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB17" t="n">
-        <v>5131</v>
+        <v>5199</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8840,61 +8848,61 @@
         <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ17" t="n">
         <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BT17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW17" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BX17" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BY17" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8930,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8942,46 +8950,46 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY17" t="n">
         <v>7</v>
       </c>
-      <c r="CY17" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ17" t="n">
         <v>0</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8993,25 +9001,25 @@
         <v>1.5</v>
       </c>
       <c r="DI17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9035,14 +9043,14 @@
         <v>1</v>
       </c>
       <c r="DW17" t="n">
-        <v>29.9</v>
+        <v>35.99</v>
       </c>
       <c r="DX17" t="n">
-        <v>6.93</v>
+        <v>5.68</v>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9054,72 +9062,64 @@
       <c r="EB17" t="inlineStr"/>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EH17" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.89</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE18" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
         <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9941,7 +9941,7 @@
         <v>0.8</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9971,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11051,170 +11051,162 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>15</v>
+      </c>
+      <c r="V22" t="n">
         <v>11</v>
       </c>
-      <c r="U22" t="n">
-        <v>6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>15</v>
-      </c>
       <c r="W22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Z22" t="n">
-        <v>71</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Stadio Panetolikou</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Nikitara, Agrinio</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="AO22" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
         <v>1</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB22" t="n">
-        <v>5131</v>
+        <v>-1</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -11229,40 +11221,40 @@
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
         <v>4</v>
       </c>
       <c r="BM22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT22" t="n">
         <v>5</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>3</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
@@ -11271,22 +11263,22 @@
         <v>41</v>
       </c>
       <c r="BW22" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="BX22" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY22" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -11319,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -11334,82 +11326,82 @@
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CV22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CW22" t="n">
         <v>1</v>
       </c>
       <c r="CX22" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY22" t="n">
         <v>10</v>
       </c>
-      <c r="CY22" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>25</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ22" t="n">
         <v>100</v>
       </c>
-      <c r="DA22" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB22" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC22" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DE22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DF22" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG22" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DI22" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ22" t="n">
-        <v>0</v>
-      </c>
       <c r="DK22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="DL22" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="DM22" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="DN22" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="DO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
       </c>
       <c r="DQ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR22" t="b">
         <v>0</v>
@@ -11424,17 +11416,17 @@
         <v>0</v>
       </c>
       <c r="DV22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW22" t="n">
-        <v>26.11</v>
+        <v>29.14</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.6</v>
+        <v>4</v>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
@@ -11442,76 +11434,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA22" t="inlineStr"/>
-      <c r="EB22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EC22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="ED22" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EH22" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr"/>
       <c r="EI22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ22" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EL22" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM22" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EN22" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EO22" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EP22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -11531,162 +11523,170 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U23" t="n">
+        <v>6</v>
+      </c>
+      <c r="V23" t="n">
         <v>15</v>
       </c>
-      <c r="V23" t="n">
-        <v>11</v>
-      </c>
       <c r="W23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z23" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
         <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.64</v>
+        <v>2.21</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>-1</v>
+        <v>5131</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11701,40 +11701,40 @@
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL23" t="n">
         <v>4</v>
       </c>
       <c r="BM23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP23" t="n">
         <v>1</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR23" t="n">
         <v>2</v>
       </c>
       <c r="BS23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
@@ -11743,22 +11743,22 @@
         <v>41</v>
       </c>
       <c r="BW23" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="BX23" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BY23" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.38</v>
+        <v>0.68</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11791,10 +11791,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11806,82 +11806,82 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
       </c>
       <c r="CX23" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY23" t="n">
         <v>6</v>
       </c>
-      <c r="CY23" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DB23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DD23" t="n">
         <v>0.8</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="DI23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DJ23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK23" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DL23" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="DM23" t="n">
-        <v>0.82</v>
+        <v>1.31</v>
       </c>
       <c r="DN23" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
       </c>
       <c r="DQ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR23" t="b">
         <v>0</v>
@@ -11896,17 +11896,17 @@
         <v>0</v>
       </c>
       <c r="DV23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW23" t="n">
-        <v>29.14</v>
+        <v>26.11</v>
       </c>
       <c r="DX23" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="DY23" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ23" t="inlineStr">
@@ -11914,76 +11914,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA23" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="EB23" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+      <c r="EA23" t="inlineStr"/>
+      <c r="EB23" t="inlineStr"/>
       <c r="EC23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED23" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr"/>
-      <c r="EH23" t="inlineStr"/>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EN23" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EO23" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EP23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="DE24" t="n">
         <v>0.17</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE25" t="n">
         <v>1</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE26" t="n">
         <v>2</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13753,7 +13753,7 @@
         <v>2.17</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14713,7 +14713,7 @@
         <v>3</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14743,7 +14743,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15638,7 +15638,7 @@
         <v>75</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE31" t="n">
         <v>1.5</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16129,7 +16129,7 @@
         <v>0.6</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16614,7 +16614,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE33" t="n">
         <v>2</v>
@@ -16647,7 +16647,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         <v>1.2</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18065,7 +18065,7 @@
         <v>0.6</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -18095,7 +18095,7 @@
         <v>2.34</v>
       </c>
       <c r="DO36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18542,7 +18542,7 @@
         <v>59</v>
       </c>
       <c r="DD37" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE37" t="n">
         <v>0.17</v>
@@ -18575,7 +18575,7 @@
         <v>2.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19022,7 +19022,7 @@
         <v>17</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE38" t="n">
         <v>1.5</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19175,170 +19175,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
         <v>6</v>
       </c>
       <c r="U39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W39" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="X39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Stadio Levadias</t>
+          <t>Stadio Zirinio</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Agion Theodoron, Levadia</t>
+          <t>Kifissia, Athens</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU39" t="n">
         <v>5</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>6</v>
-      </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ39" t="n">
         <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB39" t="n">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19353,13 +19353,13 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL39" t="n">
         <v>0</v>
@@ -19368,61 +19368,61 @@
         <v>5</v>
       </c>
       <c r="BN39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="n">
         <v>2</v>
       </c>
       <c r="BS39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BT39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY39" t="n">
         <v>77</v>
       </c>
-      <c r="BW39" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>137</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>57</v>
-      </c>
       <c r="BZ39" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="CB39" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="CC39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG39" t="n">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ39" t="n">
         <v>1</v>
@@ -19461,46 +19461,46 @@
         <v>17</v>
       </c>
       <c r="CS39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV39" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY39" t="n">
         <v>10</v>
       </c>
-      <c r="CY39" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DA39" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DB39" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DC39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.17</v>
+        <v>0.8</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF39" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG39" t="n">
         <v>2</v>
@@ -19509,25 +19509,25 @@
         <v>1.4</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ39" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="DK39" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.58</v>
+        <v>0.87</v>
       </c>
       <c r="DM39" t="n">
-        <v>0.76</v>
+        <v>2.14</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="DO39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19545,20 +19545,20 @@
         <v>1</v>
       </c>
       <c r="DU39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>19.8</v>
+        <v>20.41</v>
       </c>
       <c r="DX39" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19568,82 +19568,82 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -19663,170 +19663,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
+        <v>10</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
         <v>7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>9</v>
       </c>
       <c r="T40" t="n">
         <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>11</v>
+      </c>
+      <c r="X40" t="n">
         <v>9</v>
       </c>
-      <c r="W40" t="n">
-        <v>20</v>
-      </c>
-      <c r="X40" t="n">
-        <v>18</v>
-      </c>
       <c r="Y40" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="Z40" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Stadio Zirinio</t>
+          <t>Stadio Levadias</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Kifissia, Athens</t>
+          <t>Agion Theodoron, Levadia</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="n">
-        <v>8.08</v>
+        <v>1.67</v>
       </c>
       <c r="AF40" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
         <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19841,13 +19841,13 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL40" t="n">
         <v>0</v>
@@ -19856,61 +19856,61 @@
         <v>5</v>
       </c>
       <c r="BN40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BQ40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR40" t="n">
         <v>2</v>
       </c>
       <c r="BS40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BT40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="BW40" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY40" t="n">
         <v>57</v>
       </c>
-      <c r="BX40" t="n">
-        <v>73</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>77</v>
-      </c>
       <c r="BZ40" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CC40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG40" t="n">
         <v>0</v>
@@ -19931,7 +19931,7 @@
         <v>0</v>
       </c>
       <c r="CM40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
@@ -19940,7 +19940,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ40" t="n">
         <v>1</v>
@@ -19949,46 +19949,46 @@
         <v>17</v>
       </c>
       <c r="CS40" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB40" t="n">
         <v>17</v>
       </c>
-      <c r="CV40" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY40" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ40" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA40" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB40" t="n">
-        <v>25</v>
-      </c>
       <c r="DC40" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="DD40" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="DE40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DF40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG40" t="n">
         <v>2</v>
@@ -19997,25 +19997,25 @@
         <v>1.4</v>
       </c>
       <c r="DI40" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="DJ40" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="DK40" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DL40" t="n">
-        <v>0.87</v>
+        <v>1.58</v>
       </c>
       <c r="DM40" t="n">
-        <v>2.14</v>
+        <v>0.76</v>
       </c>
       <c r="DN40" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="DO40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20033,20 +20033,20 @@
         <v>1</v>
       </c>
       <c r="DU40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW40" t="n">
-        <v>20.41</v>
+        <v>19.8</v>
       </c>
       <c r="DX40" t="n">
-        <v>3.34</v>
+        <v>2.29</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -20056,82 +20056,82 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>5.77</t>
         </is>
       </c>
     </row>
@@ -20462,7 +20462,7 @@
         <v>0</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE41" t="n">
         <v>2</v>
@@ -20495,7 +20495,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20953,7 +20953,7 @@
         <v>2.2</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21422,7 +21422,7 @@
         <v>33</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE43" t="n">
         <v>2</v>
@@ -21455,7 +21455,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21913,7 +21913,7 @@
         <v>0.4</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>1.2</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DF45" t="n">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22886,10 +22886,10 @@
         <v>84</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22919,7 +22919,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23374,7 +23374,7 @@
         <v>59</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="DE47" t="n">
         <v>0.2</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23841,7 +23841,7 @@
         <v>1.2</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24318,7 +24318,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE49" t="n">
         <v>2</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25286,7 +25286,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE51" t="n">
         <v>1</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25761,7 +25761,7 @@
         <v>0.6</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26249,7 +26249,7 @@
         <v>2.17</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF53" t="n">
         <v>2.25</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27214,7 +27214,7 @@
         <v>38</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE55" t="n">
         <v>1.5</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27719,7 +27719,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28174,10 +28174,10 @@
         <v>84</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="DE57" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28665,7 +28665,7 @@
         <v>0.4</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DF58" t="n">
         <v>0.67</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29153,7 +29153,7 @@
         <v>3</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF59" t="n">
         <v>3</v>
@@ -29183,7 +29183,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29638,10 +29638,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF60" t="n">
         <v>0.5</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30102,7 +30102,7 @@
         <v>88</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE61" t="n">
         <v>2</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30574,7 +30574,7 @@
         <v>63</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DE62" t="n">
         <v>1</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31062,10 +31062,10 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DF63" t="n">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32063,7 +32063,7 @@
         <v>2.65</v>
       </c>
       <c r="DO65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -32551,7 +32551,7 @@
         <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34564,6 +34564,3366 @@
       <c r="EP70" t="inlineStr">
         <is>
           <t>2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>11</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>45983.72916666666</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3</v>
+      </c>
+      <c r="R71" t="n">
+        <v>4</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>6</v>
+      </c>
+      <c r="V71" t="n">
+        <v>8</v>
+      </c>
+      <c r="W71" t="n">
+        <v>9</v>
+      </c>
+      <c r="X71" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>72</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ71" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB71" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR71" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS71" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU71" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV71" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX71" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY71" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ71" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA71" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB71" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC71" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DI71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DJ71" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK71" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM71" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DN71" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DO71" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW71" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="DX71" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="DY71" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="DZ71" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="EA71" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EB71" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC71" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED71" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EE71" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EF71" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG71" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EH71" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EI71" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EJ71" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EK71" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EL71" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM71" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EN71" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EO71" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EP71" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>45983.75</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>8</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>7</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>27</v>
+      </c>
+      <c r="V72" t="n">
+        <v>6</v>
+      </c>
+      <c r="W72" t="n">
+        <v>5</v>
+      </c>
+      <c r="X72" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Stadio Georgios Karaiskáki</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Poseidonos Avenue, Faliro, Piraeus</t>
+        </is>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>116</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ72" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB72" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CC72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR72" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS72" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU72" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV72" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX72" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY72" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ72" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA72" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB72" t="n">
+        <v>10</v>
+      </c>
+      <c r="DC72" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD72" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE72" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF72" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DJ72" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK72" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL72" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DM72" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DN72" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO72" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS72" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT72" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU72" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV72" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW72" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="DX72" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="DY72" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ72" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="EA72" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EB72" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC72" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED72" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EE72" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF72" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG72" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EH72" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI72" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EJ72" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EK72" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EL72" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EM72" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EN72" t="inlineStr">
+        <is>
+          <t>6.34</t>
+        </is>
+      </c>
+      <c r="EO72" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EP72" t="inlineStr">
+        <is>
+          <t>12.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>45984.625</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
+      <c r="L73" t="n">
+        <v>11</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6</v>
+      </c>
+      <c r="S73" t="n">
+        <v>8</v>
+      </c>
+      <c r="T73" t="n">
+        <v>12</v>
+      </c>
+      <c r="U73" t="n">
+        <v>10</v>
+      </c>
+      <c r="V73" t="n">
+        <v>18</v>
+      </c>
+      <c r="W73" t="n">
+        <v>13</v>
+      </c>
+      <c r="X73" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>960</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CB73" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR73" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS73" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU73" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV73" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX73" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY73" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ73" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA73" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB73" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC73" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD73" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE73" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI73" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ73" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK73" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL73" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DM73" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DN73" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO73" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW73" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="DX73" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="DY73" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="DZ73" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="EA73" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EB73" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EC73" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED73" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EE73" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF73" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG73" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH73" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI73" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EJ73" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EK73" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EL73" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EM73" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN73" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="EO73" t="inlineStr">
+        <is>
+          <t>7.37</t>
+        </is>
+      </c>
+      <c r="EP73" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>45984.70833333334</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>8</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4</v>
+      </c>
+      <c r="L74" t="n">
+        <v>12</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>6</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" t="n">
+        <v>13</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>19</v>
+      </c>
+      <c r="V74" t="n">
+        <v>6</v>
+      </c>
+      <c r="W74" t="n">
+        <v>9</v>
+      </c>
+      <c r="X74" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>19</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB74" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM74" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN74" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR74" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS74" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU74" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV74" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX74" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY74" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ74" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA74" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB74" t="n">
+        <v>10</v>
+      </c>
+      <c r="DC74" t="n">
+        <v>40</v>
+      </c>
+      <c r="DD74" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DE74" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF74" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DG74" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DI74" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ74" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK74" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL74" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM74" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN74" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="DO74" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW74" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="DX74" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="DY74" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="DZ74" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="EA74" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EB74" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC74" t="inlineStr"/>
+      <c r="ED74" t="inlineStr"/>
+      <c r="EE74" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EF74" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EG74" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH74" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EI74" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ74" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EK74" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EL74" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EM74" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EN74" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="EO74" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EP74" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>45984.79166666666</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>7</v>
+      </c>
+      <c r="R75" t="n">
+        <v>3</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>27</v>
+      </c>
+      <c r="V75" t="n">
+        <v>6</v>
+      </c>
+      <c r="W75" t="n">
+        <v>13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY75" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>30</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>70</v>
+      </c>
+      <c r="DK75" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL75" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN75" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO75" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW75" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="DX75" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="DY75" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="DZ75" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="EA75" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EB75" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC75" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED75" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr"/>
+      <c r="EF75" t="inlineStr"/>
+      <c r="EG75" t="inlineStr"/>
+      <c r="EH75" t="inlineStr"/>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ75" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EM75" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EN75" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EP75" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>11</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>45985.66666666666</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>5</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
+        <v>20</v>
+      </c>
+      <c r="V76" t="n">
+        <v>12</v>
+      </c>
+      <c r="W76" t="n">
+        <v>17</v>
+      </c>
+      <c r="X76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Dimotiko Stadio Neapolis Volou</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Efstratios Argenti, Volos</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1108</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY76" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>13</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DM76" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN76" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO76" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW76" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="DX76" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="DY76" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="DZ76" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA76" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EB76" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC76" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="ED76" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF76" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG76" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EH76" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EJ76" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EN76" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EO76" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EP76" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>11</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>45985.75</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M77" t="n">
+        <v>4</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>12</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>18</v>
+      </c>
+      <c r="V77" t="n">
+        <v>8</v>
+      </c>
+      <c r="W77" t="n">
+        <v>23</v>
+      </c>
+      <c r="X77" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM77" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DN77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DO77" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW77" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="DX77" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DY77" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="DZ77" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA77" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EB77" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC77" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED77" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EE77" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EG77" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH77" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI77" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EJ77" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EK77" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EN77" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EO77" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EP77" t="inlineStr">
+        <is>
+          <t>3.44</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -37738,7 +37738,7 @@
         <v>1</v>
       </c>
       <c r="CR77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CS77" t="n">
         <v>15</v>
@@ -37846,26 +37846,10 @@
           <t>2%</t>
         </is>
       </c>
-      <c r="EA77" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="EB77" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EC77" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED77" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+      <c r="EA77" t="inlineStr"/>
+      <c r="EB77" t="inlineStr"/>
+      <c r="EC77" t="inlineStr"/>
+      <c r="ED77" t="inlineStr"/>
       <c r="EE77" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -37888,42 +37872,42 @@
       </c>
       <c r="EI77" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EL77" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EM77" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EN77" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EO77" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EP77" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.49</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP77" headerRowCount="1">
-  <autoFilter ref="A1:EP77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP84" headerRowCount="1">
+  <autoFilter ref="A1:EP84"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP77"/>
+  <dimension ref="A1:EP84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1794,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2261,7 +2261,7 @@
         <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE4" t="n">
         <v>1.17</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>2.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3685,7 +3685,7 @@
         <v>2.67</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4162,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE7" t="n">
         <v>1.33</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4653,7 +4653,7 @@
         <v>1.8</v>
       </c>
       <c r="DE8" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE10" t="n">
         <v>1</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6573,7 +6573,7 @@
         <v>2.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6603,7 +6603,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="DE14" t="n">
         <v>1.6</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8029,7 +8029,7 @@
         <v>3</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -8059,7 +8059,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8506,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE16" t="n">
         <v>1.17</v>
@@ -8539,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8986,10 +8986,10 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9019,7 +9019,7 @@
         <v>2.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9139,37 +9139,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -9181,122 +9181,122 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
         <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Stadio Theodoros Kolokotronis</t>
+          <t>Dimotiko Stadio Neapolis Volou</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Liagora, Tripoli</t>
+          <t>Efstratios Argenti, Volos</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.2</v>
+        <v>4.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>-1</v>
+        <v>5168</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9317,134 +9317,134 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY18" t="n">
         <v>6</v>
       </c>
-      <c r="BU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ18" t="n">
         <v>0</v>
       </c>
@@ -9458,11 +9458,11 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE18" t="n">
         <v>1.4</v>
       </c>
-      <c r="DE18" t="n">
-        <v>1</v>
-      </c>
       <c r="DF18" t="n">
         <v>0</v>
       </c>
@@ -9470,25 +9470,25 @@
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
         <v>11</v>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
@@ -9515,14 +9515,14 @@
         <v>1</v>
       </c>
       <c r="DW18" t="n">
-        <v>27.55</v>
+        <v>29.47</v>
       </c>
       <c r="DX18" t="n">
-        <v>3.1</v>
+        <v>6.76</v>
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ18" t="inlineStr">
@@ -9532,74 +9532,50 @@
       </c>
       <c r="EA18" t="inlineStr"/>
       <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EF18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EH18" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+      <c r="EC18" t="inlineStr"/>
+      <c r="ED18" t="inlineStr"/>
+      <c r="EE18" t="inlineStr"/>
+      <c r="EF18" t="inlineStr"/>
+      <c r="EG18" t="inlineStr"/>
+      <c r="EH18" t="inlineStr"/>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EM18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EN18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EO18" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -9619,37 +9595,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
-        <v>9</v>
-      </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -9661,122 +9637,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
+        <v>16</v>
+      </c>
+      <c r="W19" t="n">
         <v>12</v>
       </c>
-      <c r="W19" t="n">
-        <v>22</v>
-      </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Dimotiko Stadio Neapolis Volou</t>
+          <t>Stadio Theodoros Kolokotronis</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Efstratios Argenti, Volos</t>
+          <t>Liagora, Tripoli</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS19" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5168</v>
+        <v>-1</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9797,64 +9773,64 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BW19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BX19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BY19" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9881,7 +9857,7 @@
         <v>1</v>
       </c>
       <c r="CK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -9902,28 +9878,28 @@
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ19" t="n">
         <v>0</v>
@@ -9938,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9950,28 +9926,28 @@
         <v>0</v>
       </c>
       <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
         <v>0.5</v>
       </c>
-      <c r="DI19" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DN19" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9986,7 +9962,7 @@
         <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
@@ -9995,14 +9971,14 @@
         <v>1</v>
       </c>
       <c r="DW19" t="n">
-        <v>29.47</v>
+        <v>27.55</v>
       </c>
       <c r="DX19" t="n">
-        <v>6.76</v>
+        <v>3.1</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
@@ -10012,50 +9988,74 @@
       </c>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
-      <c r="ED19" t="inlineStr"/>
-      <c r="EE19" t="inlineStr"/>
-      <c r="EF19" t="inlineStr"/>
-      <c r="EG19" t="inlineStr"/>
-      <c r="EH19" t="inlineStr"/>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EM19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EO19" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EP19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -10394,10 +10394,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE20" t="n">
         <v>2.17</v>
-      </c>
-      <c r="DE20" t="n">
-        <v>2</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10882,10 +10882,10 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE21" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11395,7 +11395,7 @@
         <v>2.09</v>
       </c>
       <c r="DO22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11842,7 +11842,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DE23" t="n">
         <v>1.17</v>
@@ -11875,7 +11875,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>1.8</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>0.33</v>
       </c>
       <c r="DE26" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13750,7 +13750,7 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE27" t="n">
         <v>1.2</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14222,10 +14222,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="DE28" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14743,7 +14743,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15174,10 +15174,10 @@
         <v>25</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF30" t="n">
         <v>1.5</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15641,7 +15641,7 @@
         <v>2.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>75</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE32" t="n">
         <v>1.33</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16617,7 +16617,7 @@
         <v>1.4</v>
       </c>
       <c r="DE33" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -16647,7 +16647,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17086,7 +17086,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE34" t="n">
         <v>1.4</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17574,10 +17574,10 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE35" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF35" t="n">
         <v>0</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18062,7 +18062,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE36" t="n">
         <v>1.17</v>
@@ -18095,7 +18095,7 @@
         <v>2.34</v>
       </c>
       <c r="DO36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18545,7 +18545,7 @@
         <v>0.67</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="DF37" t="n">
         <v>0.5</v>
@@ -18575,7 +18575,7 @@
         <v>2.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19025,7 +19025,7 @@
         <v>0.33</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19175,170 +19175,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
+        <v>10</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
         <v>7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>9</v>
       </c>
       <c r="T39" t="n">
         <v>6</v>
       </c>
       <c r="U39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V39" t="n">
+        <v>7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>11</v>
+      </c>
+      <c r="X39" t="n">
         <v>9</v>
       </c>
-      <c r="W39" t="n">
-        <v>20</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="Z39" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Stadio Zirinio</t>
+          <t>Stadio Levadias</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Kifissia, Athens</t>
+          <t>Agion Theodoron, Levadia</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>8.08</v>
+        <v>1.67</v>
       </c>
       <c r="AF39" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AU39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
         <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB39" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19353,13 +19353,13 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL39" t="n">
         <v>0</v>
@@ -19368,61 +19368,61 @@
         <v>5</v>
       </c>
       <c r="BN39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BQ39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR39" t="n">
         <v>2</v>
       </c>
       <c r="BS39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BT39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="BW39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY39" t="n">
         <v>57</v>
       </c>
-      <c r="BX39" t="n">
-        <v>73</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>77</v>
-      </c>
       <c r="BZ39" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="CB39" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CC39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG39" t="n">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ39" t="n">
         <v>1</v>
@@ -19461,46 +19461,46 @@
         <v>17</v>
       </c>
       <c r="CS39" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB39" t="n">
         <v>17</v>
       </c>
-      <c r="CV39" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX39" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY39" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ39" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA39" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB39" t="n">
-        <v>25</v>
-      </c>
       <c r="DC39" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.8</v>
+        <v>1.86</v>
       </c>
       <c r="DE39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DF39" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG39" t="n">
         <v>2</v>
@@ -19509,25 +19509,25 @@
         <v>1.4</v>
       </c>
       <c r="DI39" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="DJ39" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="DK39" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DL39" t="n">
-        <v>0.87</v>
+        <v>1.58</v>
       </c>
       <c r="DM39" t="n">
-        <v>2.14</v>
+        <v>0.76</v>
       </c>
       <c r="DN39" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="DO39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19545,20 +19545,20 @@
         <v>1</v>
       </c>
       <c r="DU39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW39" t="n">
-        <v>20.41</v>
+        <v>19.8</v>
       </c>
       <c r="DX39" t="n">
-        <v>3.34</v>
+        <v>2.29</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19568,82 +19568,82 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>5.77</t>
         </is>
       </c>
     </row>
@@ -19663,170 +19663,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
         <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="X40" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="Z40" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Stadio Levadias</t>
+          <t>Stadio Zirinio</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Agion Theodoron, Levadia</t>
+          <t>Kifissia, Athens</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU40" t="n">
         <v>5</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>6</v>
-      </c>
       <c r="AV40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ40" t="n">
         <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB40" t="n">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19841,13 +19841,13 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL40" t="n">
         <v>0</v>
@@ -19856,61 +19856,61 @@
         <v>5</v>
       </c>
       <c r="BN40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR40" t="n">
         <v>2</v>
       </c>
       <c r="BS40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BT40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY40" t="n">
         <v>77</v>
       </c>
-      <c r="BW40" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>137</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>57</v>
-      </c>
       <c r="BZ40" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="CB40" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="CC40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG40" t="n">
         <v>0</v>
@@ -19931,7 +19931,7 @@
         <v>0</v>
       </c>
       <c r="CM40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
@@ -19940,7 +19940,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ40" t="n">
         <v>1</v>
@@ -19949,46 +19949,46 @@
         <v>17</v>
       </c>
       <c r="CS40" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV40" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CW40" t="n">
         <v>1</v>
       </c>
       <c r="CX40" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY40" t="n">
         <v>10</v>
       </c>
-      <c r="CY40" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ40" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DA40" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DB40" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DC40" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DD40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE40" t="n">
         <v>2.17</v>
       </c>
-      <c r="DE40" t="n">
-        <v>1</v>
-      </c>
       <c r="DF40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG40" t="n">
         <v>2</v>
@@ -19997,25 +19997,25 @@
         <v>1.4</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ40" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="DK40" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DL40" t="n">
-        <v>1.58</v>
+        <v>0.87</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.76</v>
+        <v>2.14</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20033,20 +20033,20 @@
         <v>1</v>
       </c>
       <c r="DU40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>19.8</v>
+        <v>20.41</v>
       </c>
       <c r="DX40" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -20056,82 +20056,82 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
         <v>2.67</v>
       </c>
       <c r="DE41" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF41" t="n">
         <v>2.33</v>
@@ -20495,7 +20495,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20950,7 +20950,7 @@
         <v>59</v>
       </c>
       <c r="DD42" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="DE42" t="n">
         <v>1.17</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21425,7 +21425,7 @@
         <v>0.33</v>
       </c>
       <c r="DE43" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF43" t="n">
         <v>0.67</v>
@@ -21455,7 +21455,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21910,7 +21910,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE44" t="n">
         <v>1.6</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22398,7 +22398,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE45" t="n">
         <v>1.2</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22919,7 +22919,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23377,7 +23377,7 @@
         <v>1.8</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23838,7 +23838,7 @@
         <v>67</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE48" t="n">
         <v>1.4</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24321,7 +24321,7 @@
         <v>2.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF49" t="n">
         <v>3</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24806,7 +24806,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DE50" t="n">
         <v>1</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25289,7 +25289,7 @@
         <v>0.67</v>
       </c>
       <c r="DE51" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25758,7 +25758,7 @@
         <v>75</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE52" t="n">
         <v>1.17</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26246,7 +26246,7 @@
         <v>71</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE53" t="n">
         <v>1.17</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26734,10 +26734,10 @@
         <v>54</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="DF54" t="n">
         <v>1.67</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27217,7 +27217,7 @@
         <v>2.67</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF55" t="n">
         <v>2.5</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27689,7 +27689,7 @@
         <v>3</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -27719,7 +27719,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28662,7 +28662,7 @@
         <v>88</v>
       </c>
       <c r="DD58" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE58" t="n">
         <v>1.33</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29183,7 +29183,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30105,7 +30105,7 @@
         <v>0.67</v>
       </c>
       <c r="DE61" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF61" t="n">
         <v>1</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31550,10 +31550,10 @@
         <v>75</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE64" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DF64" t="n">
         <v>0.75</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31719,162 +31719,170 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="n">
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>8</v>
+      </c>
+      <c r="S65" t="n">
         <v>6</v>
       </c>
-      <c r="L65" t="n">
+      <c r="T65" t="n">
         <v>10</v>
       </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
+        <v>9</v>
+      </c>
+      <c r="V65" t="n">
+        <v>18</v>
+      </c>
+      <c r="W65" t="n">
+        <v>14</v>
+      </c>
+      <c r="X65" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU65" t="n">
         <v>4</v>
       </c>
-      <c r="S65" t="n">
-        <v>4</v>
-      </c>
-      <c r="T65" t="n">
-        <v>8</v>
-      </c>
-      <c r="U65" t="n">
-        <v>6</v>
-      </c>
-      <c r="V65" t="n">
-        <v>12</v>
-      </c>
-      <c r="W65" t="n">
-        <v>19</v>
-      </c>
-      <c r="X65" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31889,76 +31897,76 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS65" t="n">
         <v>4</v>
       </c>
-      <c r="BN65" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>2</v>
-      </c>
       <c r="BT65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW65" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX65" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY65" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC65" t="n">
         <v>0</v>
       </c>
       <c r="CD65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE65" t="n">
         <v>0</v>
       </c>
       <c r="CF65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG65" t="n">
         <v>0</v>
@@ -31982,7 +31990,7 @@
         <v>0</v>
       </c>
       <c r="CN65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO65" t="n">
         <v>0</v>
@@ -31994,19 +32002,19 @@
         <v>1</v>
       </c>
       <c r="CR65" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS65" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV65" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32015,67 +32023,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ65" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA65" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.17</v>
+        <v>2.17</v>
       </c>
       <c r="DF65" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ65" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK65" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM65" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32084,102 +32092,86 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW65" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX65" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB65" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC65" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED65" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr"/>
+      <c r="EB65" t="inlineStr"/>
+      <c r="EC65" t="inlineStr"/>
+      <c r="ED65" t="inlineStr"/>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -32199,170 +32191,162 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>4</v>
       </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" t="n">
+        <v>6</v>
+      </c>
+      <c r="L66" t="n">
         <v>10</v>
       </c>
-      <c r="L66" t="n">
-        <v>11</v>
-      </c>
       <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
         <v>4</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
         <v>8</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>9</v>
-      </c>
       <c r="V66" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y66" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE66" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF66" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN66" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO66" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32377,124 +32361,124 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN66" t="n">
         <v>6</v>
       </c>
-      <c r="BN66" t="n">
+      <c r="BO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
         <v>5</v>
       </c>
-      <c r="BO66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>0</v>
-      </c>
       <c r="BS66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS66" t="n">
         <v>23</v>
       </c>
-      <c r="BW66" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>30</v>
-      </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32503,67 +32487,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ66" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA66" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="DE66" t="n">
-        <v>2</v>
+        <v>0.57</v>
       </c>
       <c r="DF66" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ66" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32572,86 +32556,102 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX66" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr"/>
-      <c r="EB66" t="inlineStr"/>
-      <c r="EC66" t="inlineStr"/>
-      <c r="ED66" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -32990,10 +32990,10 @@
         <v>78</v>
       </c>
       <c r="DD67" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33478,10 +33478,10 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE68" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF68" t="n">
         <v>0.75</v>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33958,10 +33958,10 @@
         <v>58</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34430,10 +34430,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="DE70" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34935,7 +34935,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35423,7 +35423,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35903,7 +35903,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36383,7 +36383,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36855,7 +36855,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37327,7 +37327,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37807,7 +37807,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37908,6 +37908,3398 @@
       <c r="EP77" t="inlineStr">
         <is>
           <t>3.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>45990.64583333334</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L78" t="n">
+        <v>6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>4</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="n">
+        <v>12</v>
+      </c>
+      <c r="U78" t="n">
+        <v>4</v>
+      </c>
+      <c r="V78" t="n">
+        <v>16</v>
+      </c>
+      <c r="W78" t="n">
+        <v>16</v>
+      </c>
+      <c r="X78" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Stadio Thódoros Vardinoyánnis</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Parnassou, Heraklion</t>
+        </is>
+      </c>
+      <c r="AC78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>5199</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>23</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>16</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW78" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="DX78" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA78" t="inlineStr"/>
+      <c r="EB78" t="inlineStr"/>
+      <c r="EC78" t="inlineStr"/>
+      <c r="ED78" t="inlineStr"/>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EM78" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EN78" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EO78" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EP78" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>12</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>45990.72916666666</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" t="n">
+        <v>4</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>18</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>14</v>
+      </c>
+      <c r="X79" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>5131</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>80</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DO79" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW79" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="DX79" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="DY79" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="DZ79" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="EA79" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EO79" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EP79" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>12</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>45990.72916666666</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>6</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="n">
+        <v>5</v>
+      </c>
+      <c r="U80" t="n">
+        <v>21</v>
+      </c>
+      <c r="V80" t="n">
+        <v>6</v>
+      </c>
+      <c r="W80" t="n">
+        <v>11</v>
+      </c>
+      <c r="X80" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>5168</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DO80" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW80" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="DX80" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="EA80" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EO80" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EP80" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>12</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>45991.625</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="n">
+        <v>13</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>7</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>11</v>
+      </c>
+      <c r="V81" t="n">
+        <v>9</v>
+      </c>
+      <c r="W81" t="n">
+        <v>15</v>
+      </c>
+      <c r="X81" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Stadio Peristeriou</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>93 Giannitson, Peristeri, Athens</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>1107</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY81" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE81" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DF81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI81" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK81" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL81" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DM81" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DN81" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DO81" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW81" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="DX81" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC81" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="ED81" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EE81" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG81" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EH81" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI81" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>45991.625</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>9</v>
+      </c>
+      <c r="L82" t="n">
+        <v>12</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>19</v>
+      </c>
+      <c r="U82" t="n">
+        <v>6</v>
+      </c>
+      <c r="V82" t="n">
+        <v>24</v>
+      </c>
+      <c r="W82" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>116</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>81</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>146</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>22</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL82" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DM82" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DN82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DO82" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW82" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="DX82" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DY82" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ82" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED82" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EE82" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG82" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EH82" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EN82" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="EO82" t="inlineStr">
+        <is>
+          <t>12.39</t>
+        </is>
+      </c>
+      <c r="EP82" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>12</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>45991.70833333334</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>7</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6</v>
+      </c>
+      <c r="S83" t="n">
+        <v>8</v>
+      </c>
+      <c r="T83" t="n">
+        <v>8</v>
+      </c>
+      <c r="U83" t="n">
+        <v>13</v>
+      </c>
+      <c r="V83" t="n">
+        <v>14</v>
+      </c>
+      <c r="W83" t="n">
+        <v>14</v>
+      </c>
+      <c r="X83" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Stadio Levadias</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Agion Theodoron, Levadia</t>
+        </is>
+      </c>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR83" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS83" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU83" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV83" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX83" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY83" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ83" t="n">
+        <v>74</v>
+      </c>
+      <c r="DA83" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>65</v>
+      </c>
+      <c r="DC83" t="n">
+        <v>92</v>
+      </c>
+      <c r="DD83" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE83" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF83" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DG83" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH83" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DI83" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DJ83" t="n">
+        <v>27</v>
+      </c>
+      <c r="DK83" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL83" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DM83" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN83" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DO83" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW83" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="DX83" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DY83" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="DZ83" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA83" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG83" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EH83" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI83" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EJ83" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EL83" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EM83" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EN83" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EO83" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EP83" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>45991.79166666666</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>7</v>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>4</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>5</v>
+      </c>
+      <c r="R84" t="n">
+        <v>4</v>
+      </c>
+      <c r="S84" t="n">
+        <v>9</v>
+      </c>
+      <c r="T84" t="n">
+        <v>3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>14</v>
+      </c>
+      <c r="V84" t="n">
+        <v>7</v>
+      </c>
+      <c r="W84" t="n">
+        <v>18</v>
+      </c>
+      <c r="X84" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Olympiako Stadio Spyros Louis</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>37 Kifissias Avenue, Maroussi, Athens</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>2</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY84" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE84" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF84" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI84" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>80</v>
+      </c>
+      <c r="DK84" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL84" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DN84" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DO84" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW84" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="DX84" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="DY84" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="DZ84" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EE84" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG84" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EH84" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI84" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM84" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EN84" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EO84" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EP84" t="inlineStr">
+        <is>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP84" headerRowCount="1">
-  <autoFilter ref="A1:EP84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP90" headerRowCount="1">
+  <autoFilter ref="A1:EP90"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP84"/>
+  <dimension ref="A1:EP90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE5" t="n">
         <v>0.17</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE6" t="n">
         <v>0.83</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>1.86</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DE8" t="n">
         <v>2.17</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5133,7 +5133,7 @@
         <v>0.67</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6090,10 +6090,10 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE12" t="n">
         <v>0.57</v>
@@ -6603,7 +6603,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7050,10 +7050,10 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -8208,19 +8208,19 @@
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -8229,98 +8229,98 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U16" t="n">
         <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="Z16" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AM16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AU16" t="n">
         <v>3</v>
@@ -8329,22 +8329,22 @@
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>5131</v>
+        <v>5199</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8368,61 +8368,61 @@
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ16" t="n">
         <v>1</v>
       </c>
       <c r="BR16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BT16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW16" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BX16" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BY16" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8470,46 +8470,46 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY16" t="n">
         <v>7</v>
       </c>
-      <c r="CY16" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ16" t="n">
         <v>0</v>
       </c>
       <c r="DA16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8521,22 +8521,22 @@
         <v>1.5</v>
       </c>
       <c r="DI16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="DO16" t="n">
         <v>12</v>
@@ -8563,14 +8563,14 @@
         <v>1</v>
       </c>
       <c r="DW16" t="n">
-        <v>29.9</v>
+        <v>35.99</v>
       </c>
       <c r="DX16" t="n">
-        <v>6.93</v>
+        <v>5.68</v>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8582,72 +8582,64 @@
       <c r="EB16" t="inlineStr"/>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.89</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8659,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8688,119 +8680,119 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
         <v>7</v>
       </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
         <v>5</v>
       </c>
-      <c r="N17" t="n">
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z17" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AR17" t="n">
         <v>3.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
@@ -8809,22 +8801,22 @@
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5199</v>
+        <v>5131</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8848,61 +8840,61 @@
         <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ17" t="n">
         <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW17" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="BX17" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="BY17" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="CB17" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8938,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8950,46 +8942,46 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CS17" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
         <v>17</v>
       </c>
-      <c r="CT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>16</v>
-      </c>
       <c r="CV17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
       </c>
       <c r="DA17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9001,25 +8993,25 @@
         <v>1.5</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DJ17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9043,14 +9035,14 @@
         <v>1</v>
       </c>
       <c r="DW17" t="n">
-        <v>35.99</v>
+        <v>29.9</v>
       </c>
       <c r="DX17" t="n">
-        <v>5.68</v>
+        <v>6.93</v>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9062,64 +9054,72 @@
       <c r="EB17" t="inlineStr"/>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr"/>
-      <c r="EH17" t="inlineStr"/>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -9139,37 +9139,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="L18" t="n">
-        <v>9</v>
-      </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -9181,122 +9181,122 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
+        <v>16</v>
+      </c>
+      <c r="W18" t="n">
         <v>12</v>
       </c>
-      <c r="W18" t="n">
-        <v>22</v>
-      </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z18" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Dimotiko Stadio Neapolis Volou</t>
+          <t>Stadio Theodoros Kolokotronis</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Efstratios Argenti, Volos</t>
+          <t>Liagora, Tripoli</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS18" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AU18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>5168</v>
+        <v>-1</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9317,64 +9317,64 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU18" t="n">
         <v>1</v>
       </c>
       <c r="BV18" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BW18" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BX18" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BY18" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="CB18" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="CC18" t="n">
         <v>0</v>
@@ -9401,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="CK18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL18" t="n">
         <v>0</v>
@@ -9422,28 +9422,28 @@
         <v>1</v>
       </c>
       <c r="CR18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CS18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT18" t="n">
         <v>1</v>
       </c>
       <c r="CU18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV18" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CW18" t="n">
         <v>1</v>
       </c>
       <c r="CX18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ18" t="n">
         <v>0</v>
@@ -9458,10 +9458,10 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9470,28 +9470,28 @@
         <v>0</v>
       </c>
       <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
         <v>0.5</v>
       </c>
-      <c r="DI18" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DN18" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
@@ -9515,14 +9515,14 @@
         <v>1</v>
       </c>
       <c r="DW18" t="n">
-        <v>29.47</v>
+        <v>27.55</v>
       </c>
       <c r="DX18" t="n">
-        <v>6.76</v>
+        <v>3.1</v>
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ18" t="inlineStr">
@@ -9532,50 +9532,74 @@
       </c>
       <c r="EA18" t="inlineStr"/>
       <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr"/>
-      <c r="ED18" t="inlineStr"/>
-      <c r="EE18" t="inlineStr"/>
-      <c r="EF18" t="inlineStr"/>
-      <c r="EG18" t="inlineStr"/>
-      <c r="EH18" t="inlineStr"/>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EM18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EN18" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EO18" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -9595,37 +9619,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -9637,122 +9661,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
         <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Stadio Theodoros Kolokotronis</t>
+          <t>Dimotiko Stadio Neapolis Volou</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Liagora, Tripoli</t>
+          <t>Efstratios Argenti, Volos</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.2</v>
+        <v>4.48</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1</v>
+        <v>5168</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9773,134 +9797,134 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY19" t="n">
         <v>6</v>
       </c>
-      <c r="BU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ19" t="n">
         <v>0</v>
       </c>
@@ -9914,10 +9938,10 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9926,25 +9950,25 @@
         <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
         <v>12</v>
@@ -9962,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
@@ -9971,14 +9995,14 @@
         <v>1</v>
       </c>
       <c r="DW19" t="n">
-        <v>27.55</v>
+        <v>29.47</v>
       </c>
       <c r="DX19" t="n">
-        <v>3.1</v>
+        <v>6.76</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
@@ -9988,74 +10012,50 @@
       </c>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="ED19" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE19" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EF19" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EH19" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+      <c r="EC19" t="inlineStr"/>
+      <c r="ED19" t="inlineStr"/>
+      <c r="EE19" t="inlineStr"/>
+      <c r="EF19" t="inlineStr"/>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EM19" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EO19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="EP19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11365,7 +11365,7 @@
         <v>0.67</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11845,7 +11845,7 @@
         <v>1.17</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11875,7 +11875,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12322,7 +12322,7 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DE24" t="n">
         <v>0.57</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE25" t="n">
         <v>1</v>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DE26" t="n">
         <v>2.17</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13753,7 +13753,7 @@
         <v>1.86</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14713,7 +14713,7 @@
         <v>3</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14743,7 +14743,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15638,7 +15638,7 @@
         <v>75</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE31" t="n">
         <v>1.71</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16129,7 +16129,7 @@
         <v>0.5</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16614,7 +16614,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
         <v>2.17</v>
@@ -16647,7 +16647,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         <v>1</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18065,7 +18065,7 @@
         <v>0.5</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -18095,7 +18095,7 @@
         <v>2.34</v>
       </c>
       <c r="DO36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -19022,7 +19022,7 @@
         <v>17</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DE38" t="n">
         <v>1.71</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20462,7 +20462,7 @@
         <v>0</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE41" t="n">
         <v>2.17</v>
@@ -20495,7 +20495,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20953,7 +20953,7 @@
         <v>1.83</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21422,7 +21422,7 @@
         <v>33</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DE43" t="n">
         <v>2.17</v>
@@ -21455,7 +21455,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21913,7 +21913,7 @@
         <v>0.33</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>1</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22886,10 +22886,10 @@
         <v>84</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22919,7 +22919,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23374,7 +23374,7 @@
         <v>59</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DE47" t="n">
         <v>0.17</v>
@@ -23841,7 +23841,7 @@
         <v>1.5</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24318,7 +24318,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE49" t="n">
         <v>2.17</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25761,7 +25761,7 @@
         <v>0.5</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26249,7 +26249,7 @@
         <v>1.86</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF53" t="n">
         <v>2.25</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27214,7 +27214,7 @@
         <v>38</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE55" t="n">
         <v>1.71</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27719,7 +27719,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28174,10 +28174,10 @@
         <v>84</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28665,7 +28665,7 @@
         <v>0.33</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF58" t="n">
         <v>0.67</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29153,7 +29153,7 @@
         <v>3</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF59" t="n">
         <v>3</v>
@@ -29183,7 +29183,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29638,10 +29638,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF60" t="n">
         <v>0.5</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30574,7 +30574,7 @@
         <v>63</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE62" t="n">
         <v>1</v>
@@ -31062,10 +31062,10 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF63" t="n">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31719,170 +31719,162 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>4</v>
       </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
       <c r="K65" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" t="n">
         <v>10</v>
       </c>
-      <c r="L65" t="n">
-        <v>11</v>
-      </c>
       <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2</v>
+      </c>
+      <c r="R65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
         <v>8</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>6</v>
       </c>
-      <c r="T65" t="n">
-        <v>10</v>
-      </c>
-      <c r="U65" t="n">
-        <v>9</v>
-      </c>
       <c r="V65" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y65" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z65" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE65" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF65" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL65" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN65" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO65" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS65" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31897,124 +31889,124 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN65" t="n">
         <v>6</v>
       </c>
-      <c r="BN65" t="n">
+      <c r="BO65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
         <v>5</v>
       </c>
-      <c r="BO65" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>0</v>
-      </c>
       <c r="BS65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS65" t="n">
         <v>23</v>
       </c>
-      <c r="BW65" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ65" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA65" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB65" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS65" t="n">
-        <v>30</v>
-      </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV65" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32023,67 +32015,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ65" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA65" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC65" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="DE65" t="n">
-        <v>2.17</v>
+        <v>0.57</v>
       </c>
       <c r="DF65" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ65" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK65" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL65" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DM65" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DN65" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO65" t="n">
         <v>13</v>
       </c>
-      <c r="DL65" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DM65" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DN65" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DO65" t="n">
-        <v>12</v>
-      </c>
       <c r="DP65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32092,86 +32084,102 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW65" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX65" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr"/>
-      <c r="EB65" t="inlineStr"/>
-      <c r="EC65" t="inlineStr"/>
-      <c r="ED65" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB65" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC65" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED65" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -32191,162 +32199,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>11</v>
+      </c>
+      <c r="M66" t="n">
         <v>4</v>
       </c>
-      <c r="K66" t="n">
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>8</v>
+      </c>
+      <c r="S66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="n">
+      <c r="T66" t="n">
         <v>10</v>
       </c>
-      <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>6</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
+        <v>9</v>
+      </c>
+      <c r="V66" t="n">
+        <v>18</v>
+      </c>
+      <c r="W66" t="n">
+        <v>14</v>
+      </c>
+      <c r="X66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>4</v>
-      </c>
-      <c r="T66" t="n">
-        <v>8</v>
-      </c>
-      <c r="U66" t="n">
-        <v>6</v>
-      </c>
-      <c r="V66" t="n">
-        <v>12</v>
-      </c>
-      <c r="W66" t="n">
-        <v>19</v>
-      </c>
-      <c r="X66" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32361,76 +32377,76 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
       <c r="BT66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW66" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX66" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY66" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC66" t="n">
         <v>0</v>
       </c>
       <c r="CD66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE66" t="n">
         <v>0</v>
       </c>
       <c r="CF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -32454,7 +32470,7 @@
         <v>0</v>
       </c>
       <c r="CN66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO66" t="n">
         <v>0</v>
@@ -32466,19 +32482,19 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS66" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV66" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32487,67 +32503,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ66" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA66" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC66" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.57</v>
+        <v>2.17</v>
       </c>
       <c r="DF66" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ66" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32556,102 +32572,86 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX66" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB66" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC66" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED66" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr"/>
+      <c r="EB66" t="inlineStr"/>
+      <c r="EC66" t="inlineStr"/>
+      <c r="ED66" t="inlineStr"/>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34902,7 +34902,7 @@
         <v>70</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -35393,7 +35393,7 @@
         <v>3</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF72" t="n">
         <v>3</v>
@@ -35423,7 +35423,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35873,7 +35873,7 @@
         <v>0.67</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DF73" t="n">
         <v>0.8</v>
@@ -35903,7 +35903,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36350,10 +36350,10 @@
         <v>40</v>
       </c>
       <c r="DD74" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="DF74" t="n">
         <v>2.6</v>
@@ -36383,7 +36383,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36822,10 +36822,10 @@
         <v>60</v>
       </c>
       <c r="DD75" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF75" t="n">
         <v>2.4</v>
@@ -36855,7 +36855,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37294,10 +37294,10 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF76" t="n">
         <v>2.25</v>
@@ -37327,7 +37327,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37774,10 +37774,10 @@
         <v>55</v>
       </c>
       <c r="DD77" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF77" t="n">
         <v>0.4</v>
@@ -37807,7 +37807,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38279,7 +38279,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38743,7 +38743,7 @@
         <v>2.96</v>
       </c>
       <c r="DO79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39719,7 +39719,7 @@
         <v>2.34</v>
       </c>
       <c r="DO81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40695,7 +40695,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41183,7 +41183,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41300,6 +41300,2838 @@
       <c r="EP84" t="inlineStr">
         <is>
           <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>13</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>45997.625</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>12</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="n">
+        <v>20</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>32</v>
+      </c>
+      <c r="V85" t="n">
+        <v>2</v>
+      </c>
+      <c r="W85" t="n">
+        <v>16</v>
+      </c>
+      <c r="X85" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Stadio Georgios Karaiskáki</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Poseidonos Avenue, Faliro, Piraeus</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>116</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>37</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>162</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>59</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>36</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY85" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ85" t="n">
+        <v>74</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>10</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF85" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DI85" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>27</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL85" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DM85" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DN85" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DO85" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW85" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="DX85" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="DY85" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ85" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr"/>
+      <c r="ED85" t="inlineStr"/>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>12.74</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="EP85" t="inlineStr">
+        <is>
+          <t>32.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>13</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>45997.77083333334</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" t="n">
+        <v>16</v>
+      </c>
+      <c r="M86" t="n">
+        <v>4</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5</v>
+      </c>
+      <c r="R86" t="n">
+        <v>9</v>
+      </c>
+      <c r="S86" t="n">
+        <v>11</v>
+      </c>
+      <c r="T86" t="n">
+        <v>12</v>
+      </c>
+      <c r="U86" t="n">
+        <v>16</v>
+      </c>
+      <c r="V86" t="n">
+        <v>21</v>
+      </c>
+      <c r="W86" t="n">
+        <v>13</v>
+      </c>
+      <c r="X86" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Dimotiko Stadio Neapolis Volou</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>Efstratios Argenti, Volos</t>
+        </is>
+      </c>
+      <c r="AC86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="CC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM86" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR86" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY86" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ86" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA86" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB86" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC86" t="n">
+        <v>74</v>
+      </c>
+      <c r="DD86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE86" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH86" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ86" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK86" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM86" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DN86" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DO86" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW86" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="DX86" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="DY86" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="DZ86" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="EA86" t="inlineStr"/>
+      <c r="EB86" t="inlineStr"/>
+      <c r="EC86" t="inlineStr"/>
+      <c r="ED86" t="inlineStr"/>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG86" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EH86" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI86" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EJ86" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EK86" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EL86" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EM86" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EN86" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EO86" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EP86" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>13</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>45998.625</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" t="n">
+        <v>9</v>
+      </c>
+      <c r="L87" t="n">
+        <v>11</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>5</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3</v>
+      </c>
+      <c r="T87" t="n">
+        <v>9</v>
+      </c>
+      <c r="U87" t="n">
+        <v>6</v>
+      </c>
+      <c r="V87" t="n">
+        <v>14</v>
+      </c>
+      <c r="W87" t="n">
+        <v>19</v>
+      </c>
+      <c r="X87" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY87" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC87" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ87" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL87" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM87" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DN87" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DO87" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW87" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="DX87" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DY87" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ87" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="EA87" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EO87" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EP87" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>13</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>45998.64583333334</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" t="n">
+        <v>4</v>
+      </c>
+      <c r="N88" t="n">
+        <v>3</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>4</v>
+      </c>
+      <c r="R88" t="n">
+        <v>8</v>
+      </c>
+      <c r="S88" t="n">
+        <v>6</v>
+      </c>
+      <c r="T88" t="n">
+        <v>6</v>
+      </c>
+      <c r="U88" t="n">
+        <v>10</v>
+      </c>
+      <c r="V88" t="n">
+        <v>14</v>
+      </c>
+      <c r="W88" t="n">
+        <v>11</v>
+      </c>
+      <c r="X88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC88" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD88" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DJ88" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK88" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL88" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM88" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN88" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO88" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW88" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="DX88" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="DZ88" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA88" t="inlineStr"/>
+      <c r="EB88" t="inlineStr"/>
+      <c r="EC88" t="inlineStr"/>
+      <c r="ED88" t="inlineStr"/>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="EO88" t="inlineStr">
+        <is>
+          <t>9.70</t>
+        </is>
+      </c>
+      <c r="EP88" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>13</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>45998.72916666666</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>4</v>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>6</v>
+      </c>
+      <c r="R89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S89" t="n">
+        <v>13</v>
+      </c>
+      <c r="T89" t="n">
+        <v>6</v>
+      </c>
+      <c r="U89" t="n">
+        <v>19</v>
+      </c>
+      <c r="V89" t="n">
+        <v>9</v>
+      </c>
+      <c r="W89" t="n">
+        <v>11</v>
+      </c>
+      <c r="X89" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR89" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS89" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU89" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV89" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX89" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY89" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ89" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA89" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB89" t="n">
+        <v>9</v>
+      </c>
+      <c r="DC89" t="n">
+        <v>42</v>
+      </c>
+      <c r="DD89" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF89" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG89" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH89" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DI89" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ89" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK89" t="n">
+        <v>42</v>
+      </c>
+      <c r="DL89" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN89" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="DO89" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW89" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="DX89" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DY89" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="DZ89" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="EA89" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED89" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EE89" t="inlineStr"/>
+      <c r="EF89" t="inlineStr"/>
+      <c r="EG89" t="inlineStr"/>
+      <c r="EH89" t="inlineStr"/>
+      <c r="EI89" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EJ89" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EK89" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EL89" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EM89" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EN89" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="EO89" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EP89" t="inlineStr">
+        <is>
+          <t>8.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>13</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>45998.79166666666</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>9</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2</v>
+      </c>
+      <c r="S90" t="n">
+        <v>8</v>
+      </c>
+      <c r="T90" t="n">
+        <v>3</v>
+      </c>
+      <c r="U90" t="n">
+        <v>17</v>
+      </c>
+      <c r="V90" t="n">
+        <v>5</v>
+      </c>
+      <c r="W90" t="n">
+        <v>14</v>
+      </c>
+      <c r="X90" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>48</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM90" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR90" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS90" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV90" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX90" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY90" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ90" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC90" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD90" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI90" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>84</v>
+      </c>
+      <c r="DK90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL90" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM90" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DN90" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO90" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW90" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="DX90" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="EA90" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED90" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EE90" t="inlineStr"/>
+      <c r="EF90" t="inlineStr"/>
+      <c r="EG90" t="inlineStr"/>
+      <c r="EH90" t="inlineStr"/>
+      <c r="EI90" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EJ90" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EK90" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EL90" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EM90" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EN90" t="inlineStr">
+        <is>
+          <t>6.92</t>
+        </is>
+      </c>
+      <c r="EO90" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EP90" t="inlineStr">
+        <is>
+          <t>16.63</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP90" headerRowCount="1">
-  <autoFilter ref="A1:EP90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
+  <autoFilter ref="A1:EP91"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP90"/>
+  <dimension ref="A1:EP91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE9" t="n">
         <v>1</v>
@@ -5613,7 +5613,7 @@
         <v>1.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -8059,7 +8059,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8539,7 +8539,7 @@
         <v>2.22</v>
       </c>
       <c r="DO16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -11362,7 +11362,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE22" t="n">
         <v>1</v>
@@ -11395,7 +11395,7 @@
         <v>2.09</v>
       </c>
       <c r="DO22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12793,7 +12793,7 @@
         <v>2.71</v>
       </c>
       <c r="DE25" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -17743,22 +17743,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>45934.625</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>3</v>
@@ -17767,17 +17767,17 @@
         <v>2</v>
       </c>
       <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" t="n">
         <v>5</v>
       </c>
-      <c r="L36" t="n">
-        <v>7</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>4</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -17785,98 +17785,90 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W36" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="X36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y36" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z36" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Stadio Theodoros Kolokotronis</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Liagora, Tripoli</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD36" t="n">
         <v>4</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AG36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO36" t="n">
         <v>1.9</v>
       </c>
-      <c r="AH36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AP36" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AS36" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU36" t="n">
         <v>3</v>
@@ -17888,10 +17880,10 @@
         <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ36" t="n">
         <v>2</v>
@@ -17900,13 +17892,13 @@
         <v>1</v>
       </c>
       <c r="BB36" t="n">
-        <v>5130</v>
+        <v>5138</v>
       </c>
       <c r="BC36" t="n">
         <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BE36" t="n">
         <v>0</v>
@@ -17921,181 +17913,181 @@
         <v>1</v>
       </c>
       <c r="BI36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL36" t="n">
         <v>2</v>
       </c>
       <c r="BM36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN36" t="n">
         <v>4</v>
       </c>
-      <c r="BN36" t="n">
-        <v>3</v>
-      </c>
       <c r="BO36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BU36" t="n">
         <v>1</v>
       </c>
       <c r="BV36" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR36" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU36" t="n">
         <v>18</v>
       </c>
-      <c r="BW36" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX36" t="n">
+      <c r="CV36" t="n">
+        <v>25</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY36" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA36" t="n">
         <v>59</v>
       </c>
-      <c r="BY36" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS36" t="n">
-        <v>30</v>
-      </c>
-      <c r="CT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU36" t="n">
-        <v>19</v>
-      </c>
-      <c r="CV36" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX36" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY36" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ36" t="n">
-        <v>75</v>
-      </c>
-      <c r="DA36" t="n">
-        <v>75</v>
-      </c>
       <c r="DB36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC36" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="DD36" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE36" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DF36" t="n">
         <v>0.5</v>
       </c>
-      <c r="DE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF36" t="n">
-        <v>0</v>
-      </c>
       <c r="DG36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH36" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="DI36" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="DJ36" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="DK36" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="DL36" t="n">
-        <v>0.82</v>
+        <v>1.32</v>
       </c>
       <c r="DM36" t="n">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="DN36" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18116,102 +18108,102 @@
         <v>0</v>
       </c>
       <c r="DV36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW36" t="n">
-        <v>15.5</v>
+        <v>14.49</v>
       </c>
       <c r="DX36" t="n">
-        <v>5.87</v>
+        <v>4.04</v>
       </c>
       <c r="DY36" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ36" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="EA36" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EB36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC36" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED36" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EE36" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF36" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EG36" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EH36" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI36" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EJ36" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EK36" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EL36" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EM36" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EN36" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EO36" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="EP36" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -18231,22 +18223,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>45934.625</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>3</v>
@@ -18255,108 +18247,116 @@
         <v>2</v>
       </c>
       <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7</v>
+      </c>
+      <c r="M37" t="n">
         <v>4</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>6</v>
       </c>
-      <c r="M37" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="R37" t="n">
+        <v>6</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>9</v>
+      </c>
+      <c r="V37" t="n">
+        <v>12</v>
+      </c>
+      <c r="W37" t="n">
+        <v>17</v>
+      </c>
+      <c r="X37" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
         <v>4</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>10</v>
-      </c>
-      <c r="V37" t="n">
-        <v>10</v>
-      </c>
-      <c r="W37" t="n">
-        <v>25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="n">
-        <v>5</v>
-      </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AR37" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AU37" t="n">
         <v>3</v>
@@ -18368,10 +18368,10 @@
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
         <v>2</v>
@@ -18380,13 +18380,13 @@
         <v>1</v>
       </c>
       <c r="BB37" t="n">
-        <v>5138</v>
+        <v>5130</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BE37" t="n">
         <v>0</v>
@@ -18401,64 +18401,64 @@
         <v>1</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL37" t="n">
         <v>2</v>
       </c>
       <c r="BM37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BU37" t="n">
         <v>1</v>
       </c>
       <c r="BV37" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BW37" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BX37" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="BY37" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="CB37" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="CC37" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="CM37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
@@ -18500,79 +18500,79 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ37" t="n">
         <v>1</v>
       </c>
       <c r="CR37" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
         <v>19</v>
       </c>
-      <c r="CS37" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="n">
-        <v>18</v>
-      </c>
       <c r="CV37" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ37" t="n">
         <v>25</v>
       </c>
-      <c r="CW37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX37" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY37" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ37" t="n">
-        <v>17</v>
-      </c>
-      <c r="DA37" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC37" t="n">
-        <v>59</v>
-      </c>
-      <c r="DD37" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DE37" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DF37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH37" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DI37" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DJ37" t="n">
-        <v>84</v>
-      </c>
       <c r="DK37" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="DL37" t="n">
-        <v>1.32</v>
+        <v>0.82</v>
       </c>
       <c r="DM37" t="n">
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
       <c r="DN37" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="DO37" t="n">
         <v>12</v>
@@ -18596,102 +18596,102 @@
         <v>0</v>
       </c>
       <c r="DV37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW37" t="n">
-        <v>14.49</v>
+        <v>15.5</v>
       </c>
       <c r="DX37" t="n">
-        <v>4.04</v>
+        <v>5.87</v>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ37" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="EA37" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EB37" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC37" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="ED37" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EE37" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG37" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EM37" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EF37" t="inlineStr">
+      <c r="EN37" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EO37" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EP37" t="inlineStr">
         <is>
           <t>1.94</t>
-        </is>
-      </c>
-      <c r="EG37" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EH37" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EI37" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EJ37" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="EK37" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EL37" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM37" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EN37" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="EO37" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="EP37" t="inlineStr">
-        <is>
-          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
         <v>1.86</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -19527,7 +19527,7 @@
         <v>2.34</v>
       </c>
       <c r="DO39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -24809,7 +24809,7 @@
         <v>1.17</v>
       </c>
       <c r="DE50" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25286,7 +25286,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE51" t="n">
         <v>0.83</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -30102,7 +30102,7 @@
         <v>88</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE61" t="n">
         <v>2.17</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30577,7 +30577,7 @@
         <v>2.57</v>
       </c>
       <c r="DE62" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF62" t="n">
         <v>2.25</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -34905,7 +34905,7 @@
         <v>1.33</v>
       </c>
       <c r="DE71" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF71" t="n">
         <v>1.5</v>
@@ -34935,7 +34935,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35870,7 +35870,7 @@
         <v>90</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE73" t="n">
         <v>1.33</v>
@@ -39231,7 +39231,7 @@
         <v>1.76</v>
       </c>
       <c r="DO80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -40207,7 +40207,7 @@
         <v>2.5</v>
       </c>
       <c r="DO82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -41385,10 +41385,10 @@
         <v>8</v>
       </c>
       <c r="Y85" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z85" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
@@ -41844,13 +41844,13 @@
         <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S86" t="n">
         <v>11</v>
       </c>
       <c r="T86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U86" t="n">
         <v>16</v>
@@ -42031,10 +42031,10 @@
         <v>1.65</v>
       </c>
       <c r="CA86" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="CB86" t="n">
-        <v>3.86</v>
+        <v>3.79</v>
       </c>
       <c r="CC86" t="n">
         <v>1</v>
@@ -44132,6 +44132,470 @@
       <c r="EP90" t="inlineStr">
         <is>
           <t>16.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>13</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>45999.66666666666</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2</v>
+      </c>
+      <c r="S91" t="n">
+        <v>14</v>
+      </c>
+      <c r="T91" t="n">
+        <v>4</v>
+      </c>
+      <c r="U91" t="n">
+        <v>14</v>
+      </c>
+      <c r="V91" t="n">
+        <v>6</v>
+      </c>
+      <c r="W91" t="n">
+        <v>20</v>
+      </c>
+      <c r="X91" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>1103</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR91" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS91" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU91" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV91" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX91" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY91" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ91" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA91" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB91" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC91" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD91" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE91" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF91" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH91" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ91" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK91" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL91" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DM91" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DN91" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DO91" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW91" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="DX91" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="EA91" t="inlineStr"/>
+      <c r="EB91" t="inlineStr"/>
+      <c r="EC91" t="inlineStr"/>
+      <c r="ED91" t="inlineStr"/>
+      <c r="EE91" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF91" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG91" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EH91" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI91" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EJ91" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="EK91" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EL91" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM91" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EN91" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EO91" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EP91" t="inlineStr">
+        <is>
+          <t>2.89</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -42331,7 +42331,7 @@
         <v>14</v>
       </c>
       <c r="W87" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X87" t="n">
         <v>6</v>
@@ -44214,7 +44214,7 @@
         <v>20</v>
       </c>
       <c r="X91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y91" t="n">
         <v>53</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
-  <autoFilter ref="A1:EP91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP98" headerRowCount="1">
+  <autoFilter ref="A1:EP98"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP91"/>
+  <dimension ref="A1:EP98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1794,11 +1794,11 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE2" t="n">
         <v>1.5</v>
       </c>
-      <c r="DE2" t="n">
-        <v>1.71</v>
-      </c>
       <c r="DF2" t="n">
         <v>0</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2261,7 +2261,7 @@
         <v>3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>2.57</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3685,7 +3685,7 @@
         <v>2.71</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4162,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE7" t="n">
         <v>1.29</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4653,7 +4653,7 @@
         <v>1.67</v>
       </c>
       <c r="DE8" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE10" t="n">
         <v>1.29</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6573,7 +6573,7 @@
         <v>2.57</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6603,7 +6603,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE14" t="n">
         <v>1.5</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8029,7 +8029,7 @@
         <v>3</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -8059,7 +8059,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8506,10 +8506,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8539,7 +8539,7 @@
         <v>2.22</v>
       </c>
       <c r="DO16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE17" t="n">
         <v>1</v>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9139,37 +9139,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -9181,122 +9181,122 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
         <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Stadio Theodoros Kolokotronis</t>
+          <t>Dimotiko Stadio Neapolis Volou</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Liagora, Tripoli</t>
+          <t>Efstratios Argenti, Volos</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.2</v>
+        <v>4.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>-1</v>
+        <v>5168</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9317,134 +9317,134 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY18" t="n">
         <v>6</v>
       </c>
-      <c r="BU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ18" t="n">
         <v>0</v>
       </c>
@@ -9458,11 +9458,11 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE18" t="n">
         <v>1.33</v>
       </c>
-      <c r="DE18" t="n">
-        <v>0.83</v>
-      </c>
       <c r="DF18" t="n">
         <v>0</v>
       </c>
@@ -9470,25 +9470,25 @@
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
         <v>13</v>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
@@ -9515,14 +9515,14 @@
         <v>1</v>
       </c>
       <c r="DW18" t="n">
-        <v>27.55</v>
+        <v>29.47</v>
       </c>
       <c r="DX18" t="n">
-        <v>3.1</v>
+        <v>6.76</v>
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ18" t="inlineStr">
@@ -9532,74 +9532,50 @@
       </c>
       <c r="EA18" t="inlineStr"/>
       <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EF18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EH18" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+      <c r="EC18" t="inlineStr"/>
+      <c r="ED18" t="inlineStr"/>
+      <c r="EE18" t="inlineStr"/>
+      <c r="EF18" t="inlineStr"/>
+      <c r="EG18" t="inlineStr"/>
+      <c r="EH18" t="inlineStr"/>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EM18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EN18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EO18" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -9619,37 +9595,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
-        <v>9</v>
-      </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -9661,122 +9637,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
+        <v>16</v>
+      </c>
+      <c r="W19" t="n">
         <v>12</v>
       </c>
-      <c r="W19" t="n">
-        <v>22</v>
-      </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Dimotiko Stadio Neapolis Volou</t>
+          <t>Stadio Theodoros Kolokotronis</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Efstratios Argenti, Volos</t>
+          <t>Liagora, Tripoli</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS19" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5168</v>
+        <v>-1</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9797,64 +9773,64 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BW19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BX19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BY19" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9881,7 +9857,7 @@
         <v>1</v>
       </c>
       <c r="CK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -9902,28 +9878,28 @@
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ19" t="n">
         <v>0</v>
@@ -9938,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.33</v>
+        <v>0.71</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9950,28 +9926,28 @@
         <v>0</v>
       </c>
       <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
         <v>0.5</v>
       </c>
-      <c r="DI19" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DN19" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9986,7 +9962,7 @@
         <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
@@ -9995,14 +9971,14 @@
         <v>1</v>
       </c>
       <c r="DW19" t="n">
-        <v>29.47</v>
+        <v>27.55</v>
       </c>
       <c r="DX19" t="n">
-        <v>6.76</v>
+        <v>3.1</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
@@ -10012,50 +9988,74 @@
       </c>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
-      <c r="ED19" t="inlineStr"/>
-      <c r="EE19" t="inlineStr"/>
-      <c r="EF19" t="inlineStr"/>
-      <c r="EG19" t="inlineStr"/>
-      <c r="EH19" t="inlineStr"/>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EM19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EO19" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EP19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -10394,10 +10394,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10882,10 +10882,10 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE21" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11395,7 +11395,7 @@
         <v>2.09</v>
       </c>
       <c r="DO22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11842,7 +11842,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE23" t="n">
         <v>1</v>
@@ -11875,7 +11875,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>1.67</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>0.43</v>
       </c>
       <c r="DE26" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13750,7 +13750,7 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE27" t="n">
         <v>1</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14222,10 +14222,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14743,7 +14743,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15174,10 +15174,10 @@
         <v>25</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF30" t="n">
         <v>1.5</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15641,7 +15641,7 @@
         <v>2.57</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>75</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE32" t="n">
         <v>1.29</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16617,7 +16617,7 @@
         <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -16647,7 +16647,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17086,7 +17086,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE34" t="n">
         <v>1.33</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17574,10 +17574,10 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF35" t="n">
         <v>0</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17743,22 +17743,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>45934.625</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>3</v>
@@ -17767,108 +17767,116 @@
         <v>2</v>
       </c>
       <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7</v>
+      </c>
+      <c r="M36" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>6</v>
       </c>
-      <c r="M36" t="n">
-        <v>5</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="R36" t="n">
+        <v>6</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
+      </c>
+      <c r="V36" t="n">
+        <v>12</v>
+      </c>
+      <c r="W36" t="n">
+        <v>17</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
         <v>4</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T36" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>10</v>
-      </c>
-      <c r="V36" t="n">
-        <v>10</v>
-      </c>
-      <c r="W36" t="n">
-        <v>25</v>
-      </c>
-      <c r="X36" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="n">
-        <v>5</v>
-      </c>
       <c r="AD36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AR36" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AU36" t="n">
         <v>3</v>
@@ -17880,10 +17888,10 @@
         <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
         <v>2</v>
@@ -17892,13 +17900,13 @@
         <v>1</v>
       </c>
       <c r="BB36" t="n">
-        <v>5138</v>
+        <v>5130</v>
       </c>
       <c r="BC36" t="n">
         <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BE36" t="n">
         <v>0</v>
@@ -17913,64 +17921,64 @@
         <v>1</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL36" t="n">
         <v>2</v>
       </c>
       <c r="BM36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BU36" t="n">
         <v>1</v>
       </c>
       <c r="BV36" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BW36" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BX36" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="BY36" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="CB36" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="CC36" t="n">
         <v>0</v>
@@ -18003,7 +18011,7 @@
         <v>0</v>
       </c>
       <c r="CM36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN36" t="n">
         <v>0</v>
@@ -18012,79 +18020,79 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ36" t="n">
         <v>1</v>
       </c>
       <c r="CR36" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU36" t="n">
         <v>19</v>
       </c>
-      <c r="CS36" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU36" t="n">
-        <v>18</v>
-      </c>
       <c r="CV36" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY36" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC36" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD36" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG36" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI36" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ36" t="n">
         <v>25</v>
       </c>
-      <c r="CW36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX36" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY36" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ36" t="n">
-        <v>17</v>
-      </c>
-      <c r="DA36" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC36" t="n">
-        <v>59</v>
-      </c>
-      <c r="DD36" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DE36" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DF36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DI36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DJ36" t="n">
-        <v>84</v>
-      </c>
       <c r="DK36" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="DL36" t="n">
-        <v>1.32</v>
+        <v>0.82</v>
       </c>
       <c r="DM36" t="n">
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
       <c r="DN36" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="DO36" t="n">
         <v>13</v>
@@ -18108,102 +18116,102 @@
         <v>0</v>
       </c>
       <c r="DV36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW36" t="n">
-        <v>14.49</v>
+        <v>15.5</v>
       </c>
       <c r="DX36" t="n">
-        <v>4.04</v>
+        <v>5.87</v>
       </c>
       <c r="DY36" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ36" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="EA36" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EB36" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC36" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="ED36" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EE36" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EF36" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG36" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EH36" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI36" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ36" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EK36" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL36" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EM36" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EF36" t="inlineStr">
+      <c r="EN36" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EO36" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EP36" t="inlineStr">
         <is>
           <t>1.94</t>
-        </is>
-      </c>
-      <c r="EG36" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EH36" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EI36" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EJ36" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="EK36" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EL36" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM36" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EN36" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="EO36" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="EP36" t="inlineStr">
-        <is>
-          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -18223,22 +18231,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>45934.625</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>3</v>
@@ -18247,17 +18255,17 @@
         <v>2</v>
       </c>
       <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6</v>
+      </c>
+      <c r="M37" t="n">
         <v>5</v>
       </c>
-      <c r="L37" t="n">
-        <v>7</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>4</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -18265,98 +18273,90 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="X37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y37" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z37" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Stadio Theodoros Kolokotronis</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>Liagora, Tripoli</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD37" t="n">
         <v>4</v>
       </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AG37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO37" t="n">
         <v>1.9</v>
       </c>
-      <c r="AH37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AP37" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AS37" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU37" t="n">
         <v>3</v>
@@ -18368,10 +18368,10 @@
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ37" t="n">
         <v>2</v>
@@ -18380,13 +18380,13 @@
         <v>1</v>
       </c>
       <c r="BB37" t="n">
-        <v>5130</v>
+        <v>5138</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BE37" t="n">
         <v>0</v>
@@ -18401,181 +18401,181 @@
         <v>1</v>
       </c>
       <c r="BI37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL37" t="n">
         <v>2</v>
       </c>
       <c r="BM37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN37" t="n">
         <v>4</v>
       </c>
-      <c r="BN37" t="n">
-        <v>3</v>
-      </c>
       <c r="BO37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BU37" t="n">
         <v>1</v>
       </c>
       <c r="BV37" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
         <v>18</v>
       </c>
-      <c r="BW37" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX37" t="n">
+      <c r="CV37" t="n">
+        <v>25</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA37" t="n">
         <v>59</v>
       </c>
-      <c r="BY37" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CA37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS37" t="n">
-        <v>30</v>
-      </c>
-      <c r="CT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="n">
-        <v>19</v>
-      </c>
-      <c r="CV37" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX37" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY37" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ37" t="n">
-        <v>75</v>
-      </c>
-      <c r="DA37" t="n">
-        <v>75</v>
-      </c>
       <c r="DB37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC37" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="DD37" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DF37" t="n">
         <v>0.5</v>
       </c>
-      <c r="DE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF37" t="n">
-        <v>0</v>
-      </c>
       <c r="DG37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH37" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="DI37" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="DJ37" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="DK37" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="DL37" t="n">
-        <v>0.82</v>
+        <v>1.32</v>
       </c>
       <c r="DM37" t="n">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="DN37" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18596,102 +18596,102 @@
         <v>0</v>
       </c>
       <c r="DV37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW37" t="n">
-        <v>15.5</v>
+        <v>14.49</v>
       </c>
       <c r="DX37" t="n">
-        <v>5.87</v>
+        <v>4.04</v>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ37" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="EA37" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EB37" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC37" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED37" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EE37" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF37" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EG37" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EH37" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI37" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EJ37" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EK37" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EL37" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EM37" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EN37" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EO37" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="EP37" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
         <v>0.43</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19494,7 +19494,7 @@
         <v>34</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE39" t="n">
         <v>1.29</v>
@@ -19527,7 +19527,7 @@
         <v>2.34</v>
       </c>
       <c r="DO39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19982,10 +19982,10 @@
         <v>25</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE40" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF40" t="n">
         <v>1.5</v>
@@ -20015,7 +20015,7 @@
         <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20465,7 +20465,7 @@
         <v>2.71</v>
       </c>
       <c r="DE41" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF41" t="n">
         <v>2.33</v>
@@ -20495,7 +20495,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20950,7 +20950,7 @@
         <v>59</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE42" t="n">
         <v>1</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21425,7 +21425,7 @@
         <v>0.43</v>
       </c>
       <c r="DE43" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF43" t="n">
         <v>0.67</v>
@@ -21455,7 +21455,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21910,7 +21910,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE44" t="n">
         <v>1.5</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22398,7 +22398,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE45" t="n">
         <v>1</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22919,7 +22919,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23377,7 +23377,7 @@
         <v>1.67</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23838,7 +23838,7 @@
         <v>67</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE48" t="n">
         <v>1.33</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24321,7 +24321,7 @@
         <v>2.57</v>
       </c>
       <c r="DE49" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF49" t="n">
         <v>3</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24806,7 +24806,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE50" t="n">
         <v>1.29</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25289,7 +25289,7 @@
         <v>0.57</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25758,7 +25758,7 @@
         <v>75</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE52" t="n">
         <v>1</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26246,7 +26246,7 @@
         <v>71</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE53" t="n">
         <v>1</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26734,10 +26734,10 @@
         <v>54</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DF54" t="n">
         <v>1.67</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27217,7 +27217,7 @@
         <v>2.71</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF55" t="n">
         <v>2.5</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27689,7 +27689,7 @@
         <v>3</v>
       </c>
       <c r="DE56" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -27719,7 +27719,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28662,7 +28662,7 @@
         <v>88</v>
       </c>
       <c r="DD58" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE58" t="n">
         <v>1.29</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29183,7 +29183,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30105,7 +30105,7 @@
         <v>0.57</v>
       </c>
       <c r="DE61" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF61" t="n">
         <v>1</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31550,10 +31550,10 @@
         <v>75</v>
       </c>
       <c r="DD64" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF64" t="n">
         <v>0.75</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32030,10 +32030,10 @@
         <v>65</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DF65" t="n">
         <v>1.25</v>
@@ -32063,7 +32063,7 @@
         <v>2.65</v>
       </c>
       <c r="DO65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -32518,10 +32518,10 @@
         <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE66" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DF66" t="n">
         <v>1</v>
@@ -32551,7 +32551,7 @@
         <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32990,10 +32990,10 @@
         <v>78</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33478,10 +33478,10 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF68" t="n">
         <v>0.75</v>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33958,10 +33958,10 @@
         <v>58</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34430,10 +34430,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE70" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34935,7 +34935,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35423,7 +35423,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35903,7 +35903,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36383,7 +36383,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36855,7 +36855,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37327,7 +37327,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37807,7 +37807,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38246,10 +38246,10 @@
         <v>65</v>
       </c>
       <c r="DD78" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF78" t="n">
         <v>0.6</v>
@@ -38279,7 +38279,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38399,120 +38399,128 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>6</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>8</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
       <c r="U79" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W79" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y79" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z79" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF79" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK79" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -38521,10 +38529,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -38536,10 +38544,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -38548,13 +38556,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38569,19 +38577,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -38590,55 +38598,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT79" t="n">
         <v>4</v>
       </c>
-      <c r="BT79" t="n">
-        <v>6</v>
-      </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW79" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX79" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY79" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -38659,7 +38667,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38674,76 +38682,76 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA79" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC79" t="n">
         <v>80</v>
       </c>
-      <c r="DB79" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC79" t="n">
-        <v>60</v>
-      </c>
       <c r="DD79" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.83</v>
+        <v>0.14</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG79" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH79" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ79" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38764,102 +38772,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>9.869999999999999</v>
+        <v>14.67</v>
       </c>
       <c r="DX79" t="n">
-        <v>5.91</v>
+        <v>7.45</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -38879,128 +38887,120 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>7</v>
+      </c>
+      <c r="M80" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
         <v>8</v>
       </c>
-      <c r="M80" t="n">
-        <v>2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>6</v>
-      </c>
       <c r="R80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
+        <v>18</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>14</v>
+      </c>
+      <c r="X80" t="n">
         <v>21</v>
       </c>
-      <c r="V80" t="n">
-        <v>6</v>
-      </c>
-      <c r="W80" t="n">
-        <v>11</v>
-      </c>
-      <c r="X80" t="n">
-        <v>13</v>
-      </c>
       <c r="Y80" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z80" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -39009,10 +39009,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -39024,10 +39024,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -39036,13 +39036,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -39057,19 +39057,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -39078,55 +39078,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW80" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX80" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY80" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -39147,7 +39147,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -39162,76 +39162,76 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS80" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
         <v>13</v>
       </c>
-      <c r="CV80" t="n">
-        <v>11</v>
-      </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC80" t="n">
         <v>60</v>
       </c>
-      <c r="DA80" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC80" t="n">
+      <c r="DD80" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ80" t="n">
         <v>80</v>
       </c>
-      <c r="DD80" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>40</v>
-      </c>
       <c r="DK80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM80" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN80" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39252,102 +39252,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="n">
-        <v>14.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DX80" t="n">
-        <v>7.45</v>
+        <v>5.91</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="EC80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EJ80" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EK80" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL80" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EN80" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -39367,12 +39367,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -39388,119 +39388,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>19</v>
+      </c>
+      <c r="U81" t="n">
         <v>6</v>
       </c>
-      <c r="L81" t="n">
+      <c r="V81" t="n">
+        <v>24</v>
+      </c>
+      <c r="W81" t="n">
+        <v>8</v>
+      </c>
+      <c r="X81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
         <v>13</v>
       </c>
-      <c r="M81" t="n">
-        <v>2</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>4</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6</v>
-      </c>
-      <c r="S81" t="n">
-        <v>7</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3</v>
-      </c>
-      <c r="U81" t="n">
-        <v>11</v>
-      </c>
-      <c r="V81" t="n">
-        <v>9</v>
-      </c>
-      <c r="W81" t="n">
-        <v>15</v>
-      </c>
-      <c r="X81" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF81" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI81" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ81" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM81" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR81" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -39509,28 +39509,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -39542,13 +39542,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ81" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -39557,52 +39557,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW81" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX81" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY81" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ81" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -39635,91 +39635,91 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS81" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>22</v>
       </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
+      <c r="CY81" t="n">
         <v>4</v>
       </c>
-      <c r="CY81" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ81" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA81" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.57</v>
+        <v>2</v>
       </c>
       <c r="DF81" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG81" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH81" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI81" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ81" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM81" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39743,99 +39743,99 @@
         <v>0</v>
       </c>
       <c r="DW81" t="n">
-        <v>16.31</v>
+        <v>14.32</v>
       </c>
       <c r="DX81" t="n">
-        <v>5.04</v>
+        <v>1.76</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EM81" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN81" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EO81" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EP81" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -39855,12 +39855,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -39876,119 +39876,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
+        <v>13</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>11</v>
+      </c>
+      <c r="V82" t="n">
         <v>9</v>
       </c>
-      <c r="L82" t="n">
-        <v>12</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2</v>
-      </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
-        <v>4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>19</v>
-      </c>
-      <c r="U82" t="n">
-        <v>6</v>
-      </c>
-      <c r="V82" t="n">
-        <v>24</v>
-      </c>
       <c r="W82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X82" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y82" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z82" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE82" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF82" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL82" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM82" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ82" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR82" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -39997,28 +39997,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB82" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -40030,13 +40030,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -40045,52 +40045,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW82" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX82" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY82" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA82" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB82" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -40123,91 +40123,91 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW82" t="n">
         <v>1</v>
       </c>
       <c r="CX82" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ82" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD82" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DE82" t="n">
-        <v>2.17</v>
+        <v>0.63</v>
       </c>
       <c r="DF82" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG82" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH82" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI82" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ82" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL82" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40231,99 +40231,99 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>14.32</v>
+        <v>16.31</v>
       </c>
       <c r="DX82" t="n">
-        <v>1.76</v>
+        <v>5.04</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EJ82" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EK82" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EL82" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EN82" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EO82" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EP82" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -40662,10 +40662,10 @@
         <v>92</v>
       </c>
       <c r="DD83" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE83" t="n">
         <v>1.86</v>
-      </c>
-      <c r="DE83" t="n">
-        <v>2.17</v>
       </c>
       <c r="DF83" t="n">
         <v>2.17</v>
@@ -40695,7 +40695,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41150,10 +41150,10 @@
         <v>50</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE84" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF84" t="n">
         <v>2.2</v>
@@ -41183,7 +41183,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41671,7 +41671,7 @@
         <v>3.31</v>
       </c>
       <c r="DO85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -42151,7 +42151,7 @@
         <v>3.01</v>
       </c>
       <c r="DO86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42623,7 +42623,7 @@
         <v>2.39</v>
       </c>
       <c r="DO87" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43103,7 +43103,7 @@
         <v>3.02</v>
       </c>
       <c r="DO88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43567,7 +43567,7 @@
         <v>3.26</v>
       </c>
       <c r="DO89" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -44031,7 +44031,7 @@
         <v>2.86</v>
       </c>
       <c r="DO90" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44495,7 +44495,7 @@
         <v>1.9</v>
       </c>
       <c r="DO91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44596,6 +44596,3382 @@
       <c r="EP91" t="inlineStr">
         <is>
           <t>2.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>14</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46004.625</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>9</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" t="n">
+        <v>11</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>6</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>12</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2</v>
+      </c>
+      <c r="U92" t="n">
+        <v>18</v>
+      </c>
+      <c r="V92" t="n">
+        <v>3</v>
+      </c>
+      <c r="W92" t="n">
+        <v>9</v>
+      </c>
+      <c r="X92" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Stadio Levadias</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>Agion Theodoron, Levadia</t>
+        </is>
+      </c>
+      <c r="AC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>1108</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>143</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY92" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB92" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC92" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD92" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE92" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF92" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG92" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH92" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DI92" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DJ92" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK92" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL92" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DM92" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN92" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO92" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW92" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="DX92" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DY92" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ92" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="EA92" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EB92" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EC92" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED92" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EE92" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EF92" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EG92" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI92" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EJ92" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EK92" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EL92" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM92" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN92" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EO92" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EP92" t="inlineStr">
+        <is>
+          <t>8.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>14</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46004.66666666666</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" t="n">
+        <v>5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>13</v>
+      </c>
+      <c r="M93" t="n">
+        <v>4</v>
+      </c>
+      <c r="N93" t="n">
+        <v>3</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4</v>
+      </c>
+      <c r="R93" t="n">
+        <v>3</v>
+      </c>
+      <c r="S93" t="n">
+        <v>7</v>
+      </c>
+      <c r="T93" t="n">
+        <v>5</v>
+      </c>
+      <c r="U93" t="n">
+        <v>11</v>
+      </c>
+      <c r="V93" t="n">
+        <v>8</v>
+      </c>
+      <c r="W93" t="n">
+        <v>16</v>
+      </c>
+      <c r="X93" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Stadio Thódoros Vardinoyánnis</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>Parnassou, Heraklion</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DO93" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW93" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="DX93" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="DY93" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="DZ93" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="EA93" t="inlineStr"/>
+      <c r="EB93" t="inlineStr"/>
+      <c r="EC93" t="inlineStr"/>
+      <c r="ED93" t="inlineStr"/>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EF93" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EG93" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI93" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ93" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EM93" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EN93" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EO93" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EP93" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>14</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46004.75</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>6</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4</v>
+      </c>
+      <c r="L94" t="n">
+        <v>10</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="n">
+        <v>3</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>6</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3</v>
+      </c>
+      <c r="S94" t="n">
+        <v>14</v>
+      </c>
+      <c r="T94" t="n">
+        <v>6</v>
+      </c>
+      <c r="U94" t="n">
+        <v>20</v>
+      </c>
+      <c r="V94" t="n">
+        <v>9</v>
+      </c>
+      <c r="W94" t="n">
+        <v>17</v>
+      </c>
+      <c r="X94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Dimotiko Gipedo Neapolis Nikaias</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>Grigoriou Labraki &amp; Parnassou, Neapoli, Nikaia, Athens</t>
+        </is>
+      </c>
+      <c r="AC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI94" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK94" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL94" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM94" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN94" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DO94" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW94" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="DX94" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="DY94" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="DZ94" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA94" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EE94" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EF94" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG94" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EH94" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EI94" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EJ94" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EK94" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EL94" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM94" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EN94" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EO94" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EP94" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>14</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46005.64583333334</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" t="n">
+        <v>5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" t="n">
+        <v>5</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>10</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="n">
+        <v>3</v>
+      </c>
+      <c r="U95" t="n">
+        <v>5</v>
+      </c>
+      <c r="V95" t="n">
+        <v>13</v>
+      </c>
+      <c r="W95" t="n">
+        <v>13</v>
+      </c>
+      <c r="X95" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR95" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS95" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU95" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV95" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX95" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY95" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ95" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA95" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB95" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC95" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD95" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE95" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DF95" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG95" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH95" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI95" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DJ95" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK95" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL95" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DM95" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN95" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO95" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW95" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="DX95" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DY95" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ95" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA95" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="ED95" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EE95" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF95" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EG95" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH95" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI95" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EJ95" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EL95" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EM95" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EN95" t="inlineStr">
+        <is>
+          <t>4.68</t>
+        </is>
+      </c>
+      <c r="EO95" t="inlineStr">
+        <is>
+          <t>8.90</t>
+        </is>
+      </c>
+      <c r="EP95" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>14</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46005.66666666666</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3</v>
+      </c>
+      <c r="K96" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" t="n">
+        <v>12</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>2</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="n">
+        <v>9</v>
+      </c>
+      <c r="U96" t="n">
+        <v>7</v>
+      </c>
+      <c r="V96" t="n">
+        <v>11</v>
+      </c>
+      <c r="W96" t="n">
+        <v>16</v>
+      </c>
+      <c r="X96" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Stadio Peristeriou</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>93 Giannitson, Peristeri, Athens</t>
+        </is>
+      </c>
+      <c r="AC96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>1109</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY96" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>58</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>92</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK96" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL96" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DM96" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN96" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO96" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW96" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="DX96" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DY96" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="DZ96" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EI96" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ96" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="EP96" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>14</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46005.75</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>3</v>
+      </c>
+      <c r="K97" t="n">
+        <v>5</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>4</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>5</v>
+      </c>
+      <c r="S97" t="n">
+        <v>12</v>
+      </c>
+      <c r="T97" t="n">
+        <v>10</v>
+      </c>
+      <c r="U97" t="n">
+        <v>12</v>
+      </c>
+      <c r="V97" t="n">
+        <v>15</v>
+      </c>
+      <c r="W97" t="n">
+        <v>7</v>
+      </c>
+      <c r="X97" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>72</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>138</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY97" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ97" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA97" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB97" t="n">
+        <v>9</v>
+      </c>
+      <c r="DC97" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD97" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE97" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF97" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG97" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH97" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DI97" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DJ97" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK97" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL97" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DM97" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DN97" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DO97" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW97" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="DX97" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="DZ97" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="EP97" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>14</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46005.79166666666</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>6</v>
+      </c>
+      <c r="K98" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" t="n">
+        <v>11</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N98" t="n">
+        <v>6</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>2</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="n">
+        <v>7</v>
+      </c>
+      <c r="U98" t="n">
+        <v>7</v>
+      </c>
+      <c r="V98" t="n">
+        <v>11</v>
+      </c>
+      <c r="W98" t="n">
+        <v>20</v>
+      </c>
+      <c r="X98" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Olympiako Stadio Spyros Louis</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>37 Kifissias Avenue, Maroussi, Athens</t>
+        </is>
+      </c>
+      <c r="AC98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>960</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR98" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS98" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU98" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX98" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY98" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ98" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB98" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC98" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD98" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DJ98" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK98" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL98" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM98" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN98" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO98" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW98" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="DX98" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="DZ98" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr"/>
+      <c r="EF98" t="inlineStr"/>
+      <c r="EG98" t="inlineStr"/>
+      <c r="EH98" t="inlineStr"/>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EM98" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EN98" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="EO98" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EP98" t="inlineStr">
+        <is>
+          <t>9.87</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -44901,7 +44901,7 @@
         <v>20</v>
       </c>
       <c r="CS92" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT92" t="n">
         <v>1</v>
@@ -45641,10 +45641,10 @@
         <v>10</v>
       </c>
       <c r="Y94" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z94" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -46611,10 +46611,10 @@
         <v>11</v>
       </c>
       <c r="W96" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X96" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y96" t="n">
         <v>30</v>
@@ -47069,7 +47069,7 @@
         <v>8</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N97" t="n">
         <v>2</v>
@@ -47113,7 +47113,7 @@
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD97" t="n">
         <v>3</v>
@@ -47233,7 +47233,7 @@
         <v>2</v>
       </c>
       <c r="BQ97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR97" t="n">
         <v>1</v>
@@ -47242,7 +47242,7 @@
         <v>2</v>
       </c>
       <c r="BT97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU97" t="n">
         <v>1</v>
@@ -47424,7 +47424,7 @@
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
@@ -47434,12 +47434,12 @@
       </c>
       <c r="EC97" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="ED97" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EE97" t="inlineStr">
@@ -47464,17 +47464,17 @@
       </c>
       <c r="EI97" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EJ97" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="EK97" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EL97" t="inlineStr">
@@ -47489,17 +47489,17 @@
       </c>
       <c r="EN97" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EO97" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="EP97" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
@@ -47579,10 +47579,10 @@
         <v>11</v>
       </c>
       <c r="W98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X98" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y98" t="n">
         <v>44</v>
@@ -47802,7 +47802,7 @@
         <v>1</v>
       </c>
       <c r="CR98" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CS98" t="n">
         <v>19</v>
@@ -47811,10 +47811,10 @@
         <v>1</v>
       </c>
       <c r="CU98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CW98" t="n">
         <v>1</v>
@@ -47912,22 +47912,22 @@
       </c>
       <c r="EA98" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EB98" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EC98" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="ED98" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="EE98" t="inlineStr"/>
@@ -47936,42 +47936,42 @@
       <c r="EH98" t="inlineStr"/>
       <c r="EI98" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ98" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EK98" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EL98" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EM98" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EN98" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="EO98" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EP98" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>9.51</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -46611,10 +46611,10 @@
         <v>11</v>
       </c>
       <c r="W96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y96" t="n">
         <v>30</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP98" headerRowCount="1">
-  <autoFilter ref="A1:EP98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP101" headerRowCount="1">
+  <autoFilter ref="A1:EP101"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP98"/>
+  <dimension ref="A1:EP101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -1504,19 +1504,19 @@
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1525,90 +1525,98 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="V2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" t="n">
         <v>10</v>
       </c>
-      <c r="W2" t="n">
-        <v>16</v>
-      </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Stadio Georgios Karaiskáki</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Poseidonos Avenue, Faliro, Piraeus</t>
+        </is>
+      </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.4</v>
+        <v>5.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>5</v>
+        <v>18.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.98</v>
+        <v>2.95</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -1632,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>5131</v>
+        <v>116</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -1653,37 +1661,37 @@
         <v>1</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BN2" t="n">
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>3</v>
@@ -1692,25 +1700,25 @@
         <v>1</v>
       </c>
       <c r="BV2" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="BW2" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="BY2" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.51</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.22</v>
+        <v>0.31</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1749,37 +1757,37 @@
         <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ2" t="n">
         <v>1</v>
       </c>
       <c r="CR2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="CS2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CT2" t="n">
         <v>1</v>
       </c>
       <c r="CU2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW2" t="n">
         <v>1</v>
       </c>
       <c r="CX2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="CY2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ2" t="n">
         <v>0</v>
@@ -1794,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.43</v>
+        <v>2.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.5</v>
+        <v>0.63</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1827,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -1851,14 +1859,14 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>31.84</v>
+        <v>32.47</v>
       </c>
       <c r="DX2" t="n">
-        <v>5.87</v>
+        <v>7.28</v>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
@@ -1866,60 +1874,84 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
-      <c r="EC2" t="inlineStr"/>
-      <c r="ED2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr"/>
-      <c r="EH2" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>16.28</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1971,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -1960,119 +1992,111 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>19</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>22</v>
-      </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="Z3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Stadio Georgios Karaiskáki</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Poseidonos Avenue, Faliro, Piraeus</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.62</v>
+        <v>3.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.6</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AU3" t="n">
         <v>2</v>
@@ -2096,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>116</v>
+        <v>5131</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -2117,37 +2141,37 @@
         <v>1</v>
       </c>
       <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
         <v>5</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>7</v>
-      </c>
       <c r="BL3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BM3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
         <v>9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT3" t="n">
         <v>3</v>
@@ -2156,25 +2180,25 @@
         <v>1</v>
       </c>
       <c r="BV3" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="BW3" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="BX3" t="n">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="BY3" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.31</v>
+        <v>1.22</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -2213,37 +2237,37 @@
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ3" t="n">
         <v>1</v>
       </c>
       <c r="CR3" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS3" t="n">
         <v>24</v>
       </c>
-      <c r="CS3" t="n">
+      <c r="CT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU3" t="n">
         <v>13</v>
       </c>
-      <c r="CT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>10</v>
-      </c>
       <c r="CV3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW3" t="n">
         <v>1</v>
       </c>
       <c r="CX3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="CY3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CZ3" t="n">
         <v>0</v>
@@ -2258,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.63</v>
+        <v>1.5</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2291,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2315,14 +2339,14 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>32.47</v>
+        <v>31.84</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.28</v>
+        <v>5.87</v>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
@@ -2330,84 +2354,60 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>5.54</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>2</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE8" t="n">
         <v>2</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5613,7 +5613,7 @@
         <v>1.43</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6093,7 +6093,7 @@
         <v>0.43</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE15" t="n">
         <v>0.14</v>
@@ -8539,7 +8539,7 @@
         <v>2.22</v>
       </c>
       <c r="DO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8981,7 +8981,7 @@
         <v>0.71</v>
       </c>
       <c r="DE17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9914,7 +9914,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE19" t="n">
         <v>0.71</v>
@@ -11845,7 +11845,7 @@
         <v>1.14</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11875,7 +11875,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12322,7 +12322,7 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE24" t="n">
         <v>0.63</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12793,7 +12793,7 @@
         <v>2.71</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -14710,7 +14710,7 @@
         <v>50</v>
       </c>
       <c r="DD29" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE29" t="n">
         <v>1.5</v>
@@ -16129,7 +16129,7 @@
         <v>0.86</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -16614,7 +16614,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE33" t="n">
         <v>1.86</v>
@@ -17743,22 +17743,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>45934.625</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>3</v>
@@ -17767,17 +17767,17 @@
         <v>2</v>
       </c>
       <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" t="n">
         <v>5</v>
       </c>
-      <c r="L36" t="n">
-        <v>7</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>4</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -17785,98 +17785,90 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W36" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="X36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y36" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z36" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Stadio Theodoros Kolokotronis</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Liagora, Tripoli</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD36" t="n">
         <v>4</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AG36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO36" t="n">
         <v>1.9</v>
       </c>
-      <c r="AH36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AP36" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AS36" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU36" t="n">
         <v>3</v>
@@ -17888,10 +17880,10 @@
         <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ36" t="n">
         <v>2</v>
@@ -17900,13 +17892,13 @@
         <v>1</v>
       </c>
       <c r="BB36" t="n">
-        <v>5130</v>
+        <v>5138</v>
       </c>
       <c r="BC36" t="n">
         <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BE36" t="n">
         <v>0</v>
@@ -17921,181 +17913,181 @@
         <v>1</v>
       </c>
       <c r="BI36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL36" t="n">
         <v>2</v>
       </c>
       <c r="BM36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN36" t="n">
         <v>4</v>
       </c>
-      <c r="BN36" t="n">
-        <v>3</v>
-      </c>
       <c r="BO36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BU36" t="n">
         <v>1</v>
       </c>
       <c r="BV36" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR36" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU36" t="n">
         <v>18</v>
       </c>
-      <c r="BW36" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX36" t="n">
+      <c r="CV36" t="n">
+        <v>25</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY36" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA36" t="n">
         <v>59</v>
       </c>
-      <c r="BY36" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS36" t="n">
-        <v>30</v>
-      </c>
-      <c r="CT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU36" t="n">
-        <v>19</v>
-      </c>
-      <c r="CV36" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX36" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY36" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ36" t="n">
-        <v>75</v>
-      </c>
-      <c r="DA36" t="n">
-        <v>75</v>
-      </c>
       <c r="DB36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC36" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="DE36" t="n">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="DF36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DG36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH36" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="DI36" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="DJ36" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="DK36" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="DL36" t="n">
-        <v>0.82</v>
+        <v>1.32</v>
       </c>
       <c r="DM36" t="n">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="DN36" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18116,102 +18108,102 @@
         <v>0</v>
       </c>
       <c r="DV36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW36" t="n">
-        <v>15.5</v>
+        <v>14.49</v>
       </c>
       <c r="DX36" t="n">
-        <v>5.87</v>
+        <v>4.04</v>
       </c>
       <c r="DY36" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ36" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="EA36" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EB36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC36" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED36" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EE36" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF36" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EG36" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EH36" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI36" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EJ36" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EK36" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EL36" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EM36" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EN36" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="EO36" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="EP36" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -18231,22 +18223,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>45934.625</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>3</v>
@@ -18255,108 +18247,116 @@
         <v>2</v>
       </c>
       <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7</v>
+      </c>
+      <c r="M37" t="n">
         <v>4</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>6</v>
       </c>
-      <c r="M37" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="R37" t="n">
+        <v>6</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>9</v>
+      </c>
+      <c r="V37" t="n">
+        <v>12</v>
+      </c>
+      <c r="W37" t="n">
+        <v>17</v>
+      </c>
+      <c r="X37" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
         <v>4</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>10</v>
-      </c>
-      <c r="V37" t="n">
-        <v>10</v>
-      </c>
-      <c r="W37" t="n">
-        <v>25</v>
-      </c>
-      <c r="X37" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="n">
-        <v>5</v>
-      </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AR37" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AU37" t="n">
         <v>3</v>
@@ -18368,10 +18368,10 @@
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
         <v>2</v>
@@ -18380,13 +18380,13 @@
         <v>1</v>
       </c>
       <c r="BB37" t="n">
-        <v>5138</v>
+        <v>5130</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BE37" t="n">
         <v>0</v>
@@ -18401,64 +18401,64 @@
         <v>1</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL37" t="n">
         <v>2</v>
       </c>
       <c r="BM37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BU37" t="n">
         <v>1</v>
       </c>
       <c r="BV37" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BW37" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BX37" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="BY37" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.31</v>
+        <v>1.67</v>
       </c>
       <c r="CB37" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="CC37" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="CM37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
@@ -18500,82 +18500,82 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ37" t="n">
         <v>1</v>
       </c>
       <c r="CR37" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
         <v>19</v>
       </c>
-      <c r="CS37" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU37" t="n">
-        <v>18</v>
-      </c>
       <c r="CV37" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ37" t="n">
         <v>25</v>
       </c>
-      <c r="CW37" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX37" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY37" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ37" t="n">
-        <v>17</v>
-      </c>
-      <c r="DA37" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC37" t="n">
-        <v>59</v>
-      </c>
-      <c r="DD37" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DE37" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="DF37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH37" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DI37" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DJ37" t="n">
-        <v>84</v>
-      </c>
       <c r="DK37" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="DL37" t="n">
-        <v>1.32</v>
+        <v>0.82</v>
       </c>
       <c r="DM37" t="n">
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
       <c r="DN37" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="DO37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18596,102 +18596,102 @@
         <v>0</v>
       </c>
       <c r="DV37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW37" t="n">
-        <v>14.49</v>
+        <v>15.5</v>
       </c>
       <c r="DX37" t="n">
-        <v>4.04</v>
+        <v>5.87</v>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ37" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="EA37" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EB37" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC37" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="ED37" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EE37" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG37" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EM37" t="inlineStr">
+        <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="EF37" t="inlineStr">
+      <c r="EN37" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EO37" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EP37" t="inlineStr">
         <is>
           <t>1.94</t>
-        </is>
-      </c>
-      <c r="EG37" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EH37" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EI37" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EJ37" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="EK37" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EL37" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM37" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EN37" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="EO37" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="EP37" t="inlineStr">
-        <is>
-          <t>2.85</t>
         </is>
       </c>
     </row>
@@ -19175,170 +19175,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
         <v>6</v>
       </c>
       <c r="U39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W39" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="X39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Stadio Levadias</t>
+          <t>Stadio Zirinio</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Agion Theodoron, Levadia</t>
+          <t>Kifissia, Athens</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU39" t="n">
         <v>5</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>6</v>
-      </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ39" t="n">
         <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB39" t="n">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19353,13 +19353,13 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL39" t="n">
         <v>0</v>
@@ -19368,61 +19368,61 @@
         <v>5</v>
       </c>
       <c r="BN39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="n">
         <v>2</v>
       </c>
       <c r="BS39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BT39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY39" t="n">
         <v>77</v>
       </c>
-      <c r="BW39" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>137</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>57</v>
-      </c>
       <c r="BZ39" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="CB39" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="CC39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG39" t="n">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ39" t="n">
         <v>1</v>
@@ -19461,46 +19461,46 @@
         <v>17</v>
       </c>
       <c r="CS39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV39" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY39" t="n">
         <v>10</v>
       </c>
-      <c r="CY39" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DA39" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DB39" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DC39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DD39" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.29</v>
+        <v>2.29</v>
       </c>
       <c r="DF39" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG39" t="n">
         <v>2</v>
@@ -19509,22 +19509,22 @@
         <v>1.4</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ39" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="DK39" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.58</v>
+        <v>0.87</v>
       </c>
       <c r="DM39" t="n">
-        <v>0.76</v>
+        <v>2.14</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="DO39" t="n">
         <v>14</v>
@@ -19545,20 +19545,20 @@
         <v>1</v>
       </c>
       <c r="DU39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>19.8</v>
+        <v>20.41</v>
       </c>
       <c r="DX39" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19568,82 +19568,82 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -19663,170 +19663,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
+        <v>10</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
         <v>7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>9</v>
       </c>
       <c r="T40" t="n">
         <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>11</v>
+      </c>
+      <c r="X40" t="n">
         <v>9</v>
       </c>
-      <c r="W40" t="n">
-        <v>20</v>
-      </c>
-      <c r="X40" t="n">
-        <v>18</v>
-      </c>
       <c r="Y40" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="Z40" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Stadio Zirinio</t>
+          <t>Stadio Levadias</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Kifissia, Athens</t>
+          <t>Agion Theodoron, Levadia</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="n">
-        <v>8.08</v>
+        <v>1.67</v>
       </c>
       <c r="AF40" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
         <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19841,13 +19841,13 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL40" t="n">
         <v>0</v>
@@ -19856,61 +19856,61 @@
         <v>5</v>
       </c>
       <c r="BN40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BQ40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR40" t="n">
         <v>2</v>
       </c>
       <c r="BS40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BT40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="BW40" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY40" t="n">
         <v>57</v>
       </c>
-      <c r="BX40" t="n">
-        <v>73</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>77</v>
-      </c>
       <c r="BZ40" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CC40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG40" t="n">
         <v>0</v>
@@ -19931,7 +19931,7 @@
         <v>0</v>
       </c>
       <c r="CM40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
@@ -19940,7 +19940,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ40" t="n">
         <v>1</v>
@@ -19949,46 +19949,46 @@
         <v>17</v>
       </c>
       <c r="CS40" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB40" t="n">
         <v>17</v>
       </c>
-      <c r="CV40" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY40" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ40" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA40" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB40" t="n">
-        <v>25</v>
-      </c>
       <c r="DC40" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="DE40" t="n">
-        <v>2.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG40" t="n">
         <v>2</v>
@@ -19997,22 +19997,22 @@
         <v>1.4</v>
       </c>
       <c r="DI40" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="DJ40" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="DK40" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DL40" t="n">
-        <v>0.87</v>
+        <v>1.58</v>
       </c>
       <c r="DM40" t="n">
-        <v>2.14</v>
+        <v>0.76</v>
       </c>
       <c r="DN40" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="DO40" t="n">
         <v>14</v>
@@ -20033,20 +20033,20 @@
         <v>1</v>
       </c>
       <c r="DU40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW40" t="n">
-        <v>20.41</v>
+        <v>19.8</v>
       </c>
       <c r="DX40" t="n">
-        <v>3.34</v>
+        <v>2.29</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -20056,82 +20056,82 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>5.77</t>
         </is>
       </c>
     </row>
@@ -22886,10 +22886,10 @@
         <v>84</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22919,7 +22919,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23374,7 +23374,7 @@
         <v>59</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE47" t="n">
         <v>0.14</v>
@@ -24809,7 +24809,7 @@
         <v>1.14</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26249,7 +26249,7 @@
         <v>2</v>
       </c>
       <c r="DE53" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF53" t="n">
         <v>2.25</v>
@@ -27686,7 +27686,7 @@
         <v>33</v>
       </c>
       <c r="DD56" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE56" t="n">
         <v>2.29</v>
@@ -28174,7 +28174,7 @@
         <v>84</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE57" t="n">
         <v>1.33</v>
@@ -28665,7 +28665,7 @@
         <v>0.71</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF58" t="n">
         <v>0.67</v>
@@ -29150,10 +29150,10 @@
         <v>63</v>
       </c>
       <c r="DD59" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE59" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF59" t="n">
         <v>3</v>
@@ -29183,7 +29183,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -30577,7 +30577,7 @@
         <v>2.57</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF62" t="n">
         <v>2.25</v>
@@ -31062,7 +31062,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -32063,7 +32063,7 @@
         <v>2.65</v>
       </c>
       <c r="DO65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -32551,7 +32551,7 @@
         <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -34902,10 +34902,10 @@
         <v>70</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF71" t="n">
         <v>1.5</v>
@@ -34935,7 +34935,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35390,7 +35390,7 @@
         <v>50</v>
       </c>
       <c r="DD72" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE72" t="n">
         <v>1</v>
@@ -36353,7 +36353,7 @@
         <v>2.71</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF74" t="n">
         <v>2.6</v>
@@ -36825,7 +36825,7 @@
         <v>2.57</v>
       </c>
       <c r="DE75" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF75" t="n">
         <v>2.4</v>
@@ -37294,7 +37294,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE76" t="n">
         <v>1.5</v>
@@ -39367,12 +39367,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -39388,119 +39388,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="n">
+        <v>13</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>7</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>11</v>
+      </c>
+      <c r="V81" t="n">
         <v>9</v>
       </c>
-      <c r="L81" t="n">
-        <v>12</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5</v>
-      </c>
-      <c r="S81" t="n">
-        <v>4</v>
-      </c>
-      <c r="T81" t="n">
-        <v>19</v>
-      </c>
-      <c r="U81" t="n">
-        <v>6</v>
-      </c>
-      <c r="V81" t="n">
-        <v>24</v>
-      </c>
       <c r="W81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X81" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y81" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z81" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE81" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF81" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI81" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL81" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM81" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ81" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR81" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -39509,28 +39509,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -39542,13 +39542,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -39557,52 +39557,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW81" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX81" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY81" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA81" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB81" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -39635,88 +39635,88 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW81" t="n">
         <v>1</v>
       </c>
       <c r="CX81" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY81" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ81" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA81" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="DE81" t="n">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="DF81" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG81" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH81" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI81" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ81" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK81" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL81" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO81" t="n">
         <v>14</v>
@@ -39743,99 +39743,99 @@
         <v>0</v>
       </c>
       <c r="DW81" t="n">
-        <v>14.32</v>
+        <v>16.31</v>
       </c>
       <c r="DX81" t="n">
-        <v>1.76</v>
+        <v>5.04</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EJ81" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EK81" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EL81" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EN81" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EO81" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EP81" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -39855,12 +39855,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -39876,119 +39876,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K82" t="n">
+        <v>9</v>
+      </c>
+      <c r="L82" t="n">
+        <v>12</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>19</v>
+      </c>
+      <c r="U82" t="n">
         <v>6</v>
       </c>
-      <c r="L82" t="n">
+      <c r="V82" t="n">
+        <v>24</v>
+      </c>
+      <c r="W82" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
         <v>13</v>
       </c>
-      <c r="M82" t="n">
-        <v>2</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>4</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>7</v>
-      </c>
-      <c r="T82" t="n">
-        <v>3</v>
-      </c>
-      <c r="U82" t="n">
-        <v>11</v>
-      </c>
-      <c r="V82" t="n">
-        <v>9</v>
-      </c>
-      <c r="W82" t="n">
-        <v>15</v>
-      </c>
-      <c r="X82" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF82" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI82" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ82" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM82" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR82" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -39997,28 +39997,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -40030,13 +40030,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ82" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ82" t="n">
-        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -40045,52 +40045,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW82" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX82" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY82" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ82" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB82" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -40123,91 +40123,91 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS82" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
         <v>22</v>
       </c>
-      <c r="CT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU82" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
+      <c r="CY82" t="n">
         <v>4</v>
       </c>
-      <c r="CY82" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ82" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA82" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="DF82" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG82" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH82" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI82" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ82" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK82" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM82" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40231,99 +40231,99 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>16.31</v>
+        <v>14.32</v>
       </c>
       <c r="DX82" t="n">
-        <v>5.04</v>
+        <v>1.76</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ82" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EM82" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN82" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EO82" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EP82" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -41638,7 +41638,7 @@
         <v>55</v>
       </c>
       <c r="DD85" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DE85" t="n">
         <v>1</v>
@@ -42118,10 +42118,10 @@
         <v>74</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DF86" t="n">
         <v>1.8</v>
@@ -42151,7 +42151,7 @@
         <v>3.01</v>
       </c>
       <c r="DO86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42590,7 +42590,7 @@
         <v>100</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE87" t="n">
         <v>1.5</v>
@@ -43537,7 +43537,7 @@
         <v>2.71</v>
       </c>
       <c r="DE89" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF89" t="n">
         <v>2.67</v>
@@ -44465,7 +44465,7 @@
         <v>0.57</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DF91" t="n">
         <v>0.67</v>
@@ -45927,7 +45927,7 @@
         <v>2.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP94" t="b">
         <v>0</v>
@@ -47383,7 +47383,7 @@
         <v>3.37</v>
       </c>
       <c r="DO97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -47972,6 +47972,1446 @@
       <c r="EP98" t="inlineStr">
         <is>
           <t>9.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>15</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46011.58333333334</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>7</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3</v>
+      </c>
+      <c r="L99" t="n">
+        <v>10</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3</v>
+      </c>
+      <c r="N99" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>4</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="n">
+        <v>3</v>
+      </c>
+      <c r="T99" t="n">
+        <v>10</v>
+      </c>
+      <c r="U99" t="n">
+        <v>7</v>
+      </c>
+      <c r="V99" t="n">
+        <v>11</v>
+      </c>
+      <c r="W99" t="n">
+        <v>12</v>
+      </c>
+      <c r="X99" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>5131</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL99" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DM99" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN99" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DO99" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW99" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="DX99" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr"/>
+      <c r="EF99" t="inlineStr"/>
+      <c r="EG99" t="inlineStr"/>
+      <c r="EH99" t="inlineStr"/>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EO99" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EP99" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>15</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46011.66666666666</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" t="n">
+        <v>9</v>
+      </c>
+      <c r="L100" t="n">
+        <v>13</v>
+      </c>
+      <c r="M100" t="n">
+        <v>3</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>3</v>
+      </c>
+      <c r="R100" t="n">
+        <v>4</v>
+      </c>
+      <c r="S100" t="n">
+        <v>6</v>
+      </c>
+      <c r="T100" t="n">
+        <v>10</v>
+      </c>
+      <c r="U100" t="n">
+        <v>9</v>
+      </c>
+      <c r="V100" t="n">
+        <v>14</v>
+      </c>
+      <c r="W100" t="n">
+        <v>13</v>
+      </c>
+      <c r="X100" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Dimotiko Stadio Neapolis Volou</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Efstratios Argenti, Volos</t>
+        </is>
+      </c>
+      <c r="AC100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>5199</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>32</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>68</v>
+      </c>
+      <c r="DK100" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL100" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM100" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DN100" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DO100" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW100" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="DX100" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EO100" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP100" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>15</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46011.77083333334</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" t="n">
+        <v>18</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>19</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>4</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>6</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>23</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4</v>
+      </c>
+      <c r="U101" t="n">
+        <v>29</v>
+      </c>
+      <c r="V101" t="n">
+        <v>5</v>
+      </c>
+      <c r="W101" t="n">
+        <v>11</v>
+      </c>
+      <c r="X101" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Stadio Georgios Karaiskáki</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Poseidonos Avenue, Faliro, Piraeus</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>144</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW101" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="DX101" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr"/>
+      <c r="ED101" t="inlineStr"/>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EK101" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EL101" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EM101" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EN101" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="EO101" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EP101" t="inlineStr">
+        <is>
+          <t>10.24</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP101" headerRowCount="1">
-  <autoFilter ref="A1:EP101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP105" headerRowCount="1">
+  <autoFilter ref="A1:EP105"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP101"/>
+  <dimension ref="A1:EP105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE6" t="n">
         <v>0.71</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5130,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6090,7 +6090,7 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE11" t="n">
         <v>1.25</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE12" t="n">
         <v>0.63</v>
@@ -6603,7 +6603,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7050,7 +7050,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         <v>2</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8059,7 +8059,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -8208,119 +8208,119 @@
         <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>5</v>
       </c>
-      <c r="N16" t="n">
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
         <v>6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8</v>
       </c>
       <c r="U16" t="n">
         <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y16" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z16" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AU16" t="n">
         <v>3</v>
@@ -8329,22 +8329,22 @@
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
-        <v>5199</v>
+        <v>5131</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8368,61 +8368,61 @@
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
         <v>1</v>
       </c>
       <c r="BR16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BT16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW16" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="BX16" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="BY16" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8470,46 +8470,46 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CS16" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
         <v>17</v>
       </c>
-      <c r="CT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>16</v>
-      </c>
       <c r="CV16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
       </c>
       <c r="DA16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8521,22 +8521,22 @@
         <v>1.5</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
         <v>15</v>
@@ -8563,14 +8563,14 @@
         <v>1</v>
       </c>
       <c r="DW16" t="n">
-        <v>35.99</v>
+        <v>29.9</v>
       </c>
       <c r="DX16" t="n">
-        <v>5.68</v>
+        <v>6.93</v>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8582,64 +8582,72 @@
       <c r="EB16" t="inlineStr"/>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr"/>
-      <c r="EH16" t="inlineStr"/>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -8659,12 +8667,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8680,19 +8688,19 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -8701,98 +8709,98 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y17" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="Z17" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AM17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AR17" t="n">
         <v>3.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
@@ -8801,22 +8809,22 @@
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB17" t="n">
-        <v>5131</v>
+        <v>5199</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8840,61 +8848,61 @@
         <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ17" t="n">
         <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BT17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW17" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BX17" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BY17" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8930,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8942,46 +8950,46 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY17" t="n">
         <v>7</v>
       </c>
-      <c r="CY17" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ17" t="n">
         <v>0</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8993,25 +9001,25 @@
         <v>1.5</v>
       </c>
       <c r="DI17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9035,14 +9043,14 @@
         <v>1</v>
       </c>
       <c r="DW17" t="n">
-        <v>29.9</v>
+        <v>35.99</v>
       </c>
       <c r="DX17" t="n">
-        <v>6.93</v>
+        <v>5.68</v>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9054,72 +9062,64 @@
       <c r="EB17" t="inlineStr"/>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EH17" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.89</t>
         </is>
       </c>
     </row>
@@ -9139,37 +9139,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="L18" t="n">
-        <v>9</v>
-      </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -9181,122 +9181,122 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
+        <v>16</v>
+      </c>
+      <c r="W18" t="n">
         <v>12</v>
       </c>
-      <c r="W18" t="n">
-        <v>22</v>
-      </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z18" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Dimotiko Stadio Neapolis Volou</t>
+          <t>Stadio Theodoros Kolokotronis</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Efstratios Argenti, Volos</t>
+          <t>Liagora, Tripoli</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS18" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AU18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>5168</v>
+        <v>-1</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9317,64 +9317,64 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU18" t="n">
         <v>1</v>
       </c>
       <c r="BV18" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BW18" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BX18" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BY18" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="CB18" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="CC18" t="n">
         <v>0</v>
@@ -9401,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="CK18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL18" t="n">
         <v>0</v>
@@ -9422,28 +9422,28 @@
         <v>1</v>
       </c>
       <c r="CR18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CS18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT18" t="n">
         <v>1</v>
       </c>
       <c r="CU18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV18" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CW18" t="n">
         <v>1</v>
       </c>
       <c r="CX18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ18" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1.14</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.33</v>
+        <v>0.71</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9470,28 +9470,28 @@
         <v>0</v>
       </c>
       <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
         <v>0.5</v>
       </c>
-      <c r="DI18" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DN18" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
@@ -9515,14 +9515,14 @@
         <v>1</v>
       </c>
       <c r="DW18" t="n">
-        <v>29.47</v>
+        <v>27.55</v>
       </c>
       <c r="DX18" t="n">
-        <v>6.76</v>
+        <v>3.1</v>
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ18" t="inlineStr">
@@ -9532,50 +9532,74 @@
       </c>
       <c r="EA18" t="inlineStr"/>
       <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr"/>
-      <c r="ED18" t="inlineStr"/>
-      <c r="EE18" t="inlineStr"/>
-      <c r="EF18" t="inlineStr"/>
-      <c r="EG18" t="inlineStr"/>
-      <c r="EH18" t="inlineStr"/>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EM18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EN18" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EO18" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -9595,37 +9619,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -9637,122 +9661,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
         <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Stadio Theodoros Kolokotronis</t>
+          <t>Dimotiko Stadio Neapolis Volou</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Liagora, Tripoli</t>
+          <t>Efstratios Argenti, Volos</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.2</v>
+        <v>4.48</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1</v>
+        <v>5168</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9773,133 +9797,133 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY19" t="n">
         <v>6</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>9</v>
       </c>
       <c r="CZ19" t="n">
         <v>0</v>
@@ -9917,7 +9941,7 @@
         <v>1.14</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.71</v>
+        <v>1.14</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9926,25 +9950,25 @@
         <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
         <v>14</v>
@@ -9962,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
@@ -9971,14 +9995,14 @@
         <v>1</v>
       </c>
       <c r="DW19" t="n">
-        <v>27.55</v>
+        <v>29.47</v>
       </c>
       <c r="DX19" t="n">
-        <v>3.1</v>
+        <v>6.76</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
@@ -9988,74 +10012,50 @@
       </c>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="ED19" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE19" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EF19" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EH19" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+      <c r="EC19" t="inlineStr"/>
+      <c r="ED19" t="inlineStr"/>
+      <c r="EE19" t="inlineStr"/>
+      <c r="EF19" t="inlineStr"/>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EM19" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EO19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="EP19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11051,162 +11051,170 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" t="n">
         <v>15</v>
       </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
       <c r="W22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.64</v>
+        <v>2.21</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ22" t="n">
         <v>1</v>
       </c>
       <c r="BA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>-1</v>
+        <v>5131</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -11221,40 +11229,40 @@
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL22" t="n">
         <v>4</v>
       </c>
       <c r="BM22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
       </c>
       <c r="BQ22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR22" t="n">
         <v>2</v>
       </c>
       <c r="BS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
@@ -11263,22 +11271,22 @@
         <v>41</v>
       </c>
       <c r="BW22" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="BX22" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.38</v>
+        <v>0.68</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -11311,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -11326,82 +11334,82 @@
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CW22" t="n">
         <v>1</v>
       </c>
       <c r="CX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY22" t="n">
         <v>6</v>
       </c>
-      <c r="CY22" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DB22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="DI22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DJ22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DL22" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="DM22" t="n">
-        <v>0.82</v>
+        <v>1.31</v>
       </c>
       <c r="DN22" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="DO22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
       </c>
       <c r="DQ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR22" t="b">
         <v>0</v>
@@ -11416,17 +11424,17 @@
         <v>0</v>
       </c>
       <c r="DV22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW22" t="n">
-        <v>29.14</v>
+        <v>26.11</v>
       </c>
       <c r="DX22" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
@@ -11434,76 +11442,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA22" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="EB22" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr"/>
       <c r="EC22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED22" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr"/>
-      <c r="EH22" t="inlineStr"/>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EJ22" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EN22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EO22" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EP22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -11523,170 +11531,162 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>15</v>
+      </c>
+      <c r="V23" t="n">
         <v>11</v>
       </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>15</v>
-      </c>
       <c r="W23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Z23" t="n">
-        <v>71</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Stadio Panetolikou</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Nikitara, Agrinio</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD23" t="n">
         <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB23" t="n">
-        <v>5131</v>
+        <v>-1</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11701,40 +11701,40 @@
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL23" t="n">
         <v>4</v>
       </c>
       <c r="BM23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT23" t="n">
         <v>5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>3</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
@@ -11743,22 +11743,22 @@
         <v>41</v>
       </c>
       <c r="BW23" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="BX23" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY23" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11791,10 +11791,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11806,73 +11806,73 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CV23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
       </c>
       <c r="CX23" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY23" t="n">
         <v>10</v>
       </c>
-      <c r="CY23" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ23" t="n">
         <v>100</v>
       </c>
-      <c r="DA23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DE23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DF23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DI23" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ23" t="n">
-        <v>0</v>
-      </c>
       <c r="DK23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="DL23" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="DM23" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="DN23" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="DO23" t="n">
         <v>15</v>
@@ -11881,7 +11881,7 @@
         <v>1</v>
       </c>
       <c r="DQ23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR23" t="b">
         <v>0</v>
@@ -11896,17 +11896,17 @@
         <v>0</v>
       </c>
       <c r="DV23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW23" t="n">
-        <v>26.11</v>
+        <v>29.14</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.6</v>
+        <v>4</v>
       </c>
       <c r="DY23" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="DZ23" t="inlineStr">
@@ -11914,76 +11914,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA23" t="inlineStr"/>
-      <c r="EB23" t="inlineStr"/>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EC23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="ED23" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EH23" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr"/>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EL23" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EN23" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EO23" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EP23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE25" t="n">
         <v>1.13</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE26" t="n">
         <v>2.29</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13753,7 +13753,7 @@
         <v>2</v>
       </c>
       <c r="DE27" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14713,7 +14713,7 @@
         <v>2.75</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14743,7 +14743,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15638,7 +15638,7 @@
         <v>75</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE31" t="n">
         <v>1.5</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16647,7 +16647,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         <v>0.86</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18054,7 +18054,7 @@
         <v>59</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE36" t="n">
         <v>0.63</v>
@@ -18087,7 +18087,7 @@
         <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18575,7 +18575,7 @@
         <v>2.34</v>
       </c>
       <c r="DO37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19022,7 +19022,7 @@
         <v>17</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE38" t="n">
         <v>1.5</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19527,7 +19527,7 @@
         <v>3.01</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20015,7 +20015,7 @@
         <v>2.34</v>
       </c>
       <c r="DO40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20462,7 +20462,7 @@
         <v>0</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE41" t="n">
         <v>2</v>
@@ -20495,7 +20495,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21422,7 +21422,7 @@
         <v>33</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE43" t="n">
         <v>2</v>
@@ -21455,7 +21455,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21913,7 +21913,7 @@
         <v>0.71</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22401,7 +22401,7 @@
         <v>0.86</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF45" t="n">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23841,7 +23841,7 @@
         <v>1.43</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24318,7 +24318,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE49" t="n">
         <v>1.86</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25286,7 +25286,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE51" t="n">
         <v>0.71</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27214,7 +27214,7 @@
         <v>38</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE55" t="n">
         <v>1.5</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27719,7 +27719,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28177,7 +28177,7 @@
         <v>1.86</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29638,10 +29638,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF60" t="n">
         <v>0.5</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30102,7 +30102,7 @@
         <v>88</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE61" t="n">
         <v>1.86</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30574,7 +30574,7 @@
         <v>63</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE62" t="n">
         <v>1.13</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31065,7 +31065,7 @@
         <v>1.14</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF63" t="n">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31719,162 +31719,170 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="n">
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>8</v>
+      </c>
+      <c r="S65" t="n">
         <v>6</v>
       </c>
-      <c r="L65" t="n">
+      <c r="T65" t="n">
         <v>10</v>
       </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
+        <v>9</v>
+      </c>
+      <c r="V65" t="n">
+        <v>18</v>
+      </c>
+      <c r="W65" t="n">
+        <v>14</v>
+      </c>
+      <c r="X65" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU65" t="n">
         <v>4</v>
       </c>
-      <c r="S65" t="n">
-        <v>4</v>
-      </c>
-      <c r="T65" t="n">
-        <v>8</v>
-      </c>
-      <c r="U65" t="n">
-        <v>6</v>
-      </c>
-      <c r="V65" t="n">
-        <v>12</v>
-      </c>
-      <c r="W65" t="n">
-        <v>19</v>
-      </c>
-      <c r="X65" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31889,76 +31897,76 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS65" t="n">
         <v>4</v>
       </c>
-      <c r="BN65" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>2</v>
-      </c>
       <c r="BT65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW65" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX65" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY65" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC65" t="n">
         <v>0</v>
       </c>
       <c r="CD65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE65" t="n">
         <v>0</v>
       </c>
       <c r="CF65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG65" t="n">
         <v>0</v>
@@ -31982,7 +31990,7 @@
         <v>0</v>
       </c>
       <c r="CN65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO65" t="n">
         <v>0</v>
@@ -31994,19 +32002,19 @@
         <v>1</v>
       </c>
       <c r="CR65" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS65" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV65" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32015,67 +32023,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ65" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA65" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="DF65" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ65" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK65" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM65" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO65" t="n">
         <v>15</v>
       </c>
       <c r="DP65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32084,102 +32092,86 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW65" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX65" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB65" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC65" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED65" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr"/>
+      <c r="EB65" t="inlineStr"/>
+      <c r="EC65" t="inlineStr"/>
+      <c r="ED65" t="inlineStr"/>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -32199,170 +32191,162 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>4</v>
       </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" t="n">
+        <v>6</v>
+      </c>
+      <c r="L66" t="n">
         <v>10</v>
       </c>
-      <c r="L66" t="n">
-        <v>11</v>
-      </c>
       <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
         <v>4</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
         <v>8</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>9</v>
-      </c>
       <c r="V66" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y66" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE66" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF66" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN66" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO66" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32377,124 +32361,124 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN66" t="n">
         <v>6</v>
       </c>
-      <c r="BN66" t="n">
+      <c r="BO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
         <v>5</v>
       </c>
-      <c r="BO66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>0</v>
-      </c>
       <c r="BS66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS66" t="n">
         <v>23</v>
       </c>
-      <c r="BW66" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>30</v>
-      </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32503,67 +32487,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ66" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA66" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="DE66" t="n">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="DF66" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ66" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
         <v>15</v>
       </c>
       <c r="DP66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32572,86 +32556,102 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX66" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr"/>
-      <c r="EB66" t="inlineStr"/>
-      <c r="EC66" t="inlineStr"/>
-      <c r="ED66" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35423,7 +35423,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35870,10 +35870,10 @@
         <v>90</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF73" t="n">
         <v>0.8</v>
@@ -35903,7 +35903,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36350,7 +36350,7 @@
         <v>40</v>
       </c>
       <c r="DD74" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE74" t="n">
         <v>1.25</v>
@@ -36383,7 +36383,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36822,7 +36822,7 @@
         <v>60</v>
       </c>
       <c r="DD75" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE75" t="n">
         <v>1.25</v>
@@ -36855,7 +36855,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37297,7 +37297,7 @@
         <v>1.86</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF76" t="n">
         <v>2.25</v>
@@ -37327,7 +37327,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37774,10 +37774,10 @@
         <v>55</v>
       </c>
       <c r="DD77" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE77" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF77" t="n">
         <v>0.4</v>
@@ -37807,7 +37807,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38279,7 +38279,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38751,7 +38751,7 @@
         <v>1.76</v>
       </c>
       <c r="DO79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39231,7 +39231,7 @@
         <v>2.96</v>
       </c>
       <c r="DO80" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39367,12 +39367,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -39388,119 +39388,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>19</v>
+      </c>
+      <c r="U81" t="n">
         <v>6</v>
       </c>
-      <c r="L81" t="n">
+      <c r="V81" t="n">
+        <v>24</v>
+      </c>
+      <c r="W81" t="n">
+        <v>8</v>
+      </c>
+      <c r="X81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
         <v>13</v>
       </c>
-      <c r="M81" t="n">
-        <v>2</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>4</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6</v>
-      </c>
-      <c r="S81" t="n">
-        <v>7</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3</v>
-      </c>
-      <c r="U81" t="n">
-        <v>11</v>
-      </c>
-      <c r="V81" t="n">
-        <v>9</v>
-      </c>
-      <c r="W81" t="n">
-        <v>15</v>
-      </c>
-      <c r="X81" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF81" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI81" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ81" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM81" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR81" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -39509,28 +39509,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -39542,13 +39542,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ81" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -39557,52 +39557,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW81" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX81" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY81" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ81" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -39635,91 +39635,91 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS81" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>22</v>
       </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
+      <c r="CY81" t="n">
         <v>4</v>
       </c>
-      <c r="CY81" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ81" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA81" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="DF81" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG81" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH81" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI81" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ81" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM81" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39743,99 +39743,99 @@
         <v>0</v>
       </c>
       <c r="DW81" t="n">
-        <v>16.31</v>
+        <v>14.32</v>
       </c>
       <c r="DX81" t="n">
-        <v>5.04</v>
+        <v>1.76</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EM81" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN81" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EO81" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EP81" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -39855,12 +39855,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -39876,119 +39876,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
+        <v>13</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>11</v>
+      </c>
+      <c r="V82" t="n">
         <v>9</v>
       </c>
-      <c r="L82" t="n">
-        <v>12</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2</v>
-      </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
-        <v>4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>19</v>
-      </c>
-      <c r="U82" t="n">
-        <v>6</v>
-      </c>
-      <c r="V82" t="n">
-        <v>24</v>
-      </c>
       <c r="W82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X82" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y82" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z82" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE82" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF82" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL82" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM82" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ82" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR82" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -39997,28 +39997,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB82" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -40030,13 +40030,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -40045,52 +40045,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW82" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX82" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY82" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA82" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB82" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -40123,88 +40123,88 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW82" t="n">
         <v>1</v>
       </c>
       <c r="CX82" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ82" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="DE82" t="n">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="DF82" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG82" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH82" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI82" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ82" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL82" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO82" t="n">
         <v>15</v>
@@ -40231,99 +40231,99 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>14.32</v>
+        <v>16.31</v>
       </c>
       <c r="DX82" t="n">
-        <v>1.76</v>
+        <v>5.04</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EJ82" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EK82" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EL82" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EN82" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EO82" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EP82" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41183,7 +41183,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41641,7 +41641,7 @@
         <v>2.75</v>
       </c>
       <c r="DE85" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41671,7 +41671,7 @@
         <v>3.31</v>
       </c>
       <c r="DO85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -42593,7 +42593,7 @@
         <v>1.14</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF87" t="n">
         <v>1.4</v>
@@ -42623,7 +42623,7 @@
         <v>2.39</v>
       </c>
       <c r="DO87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43070,10 +43070,10 @@
         <v>84</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF88" t="n">
         <v>0.33</v>
@@ -43103,7 +43103,7 @@
         <v>3.02</v>
       </c>
       <c r="DO88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43534,7 +43534,7 @@
         <v>42</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DE89" t="n">
         <v>1.25</v>
@@ -43567,7 +43567,7 @@
         <v>3.26</v>
       </c>
       <c r="DO89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43998,7 +43998,7 @@
         <v>59</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE90" t="n">
         <v>1</v>
@@ -44031,7 +44031,7 @@
         <v>2.86</v>
       </c>
       <c r="DO90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44462,7 +44462,7 @@
         <v>67</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DE91" t="n">
         <v>1.13</v>
@@ -44495,7 +44495,7 @@
         <v>1.9</v>
       </c>
       <c r="DO91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44967,7 +44967,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45455,7 +45455,7 @@
         <v>1.48</v>
       </c>
       <c r="DO93" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -46415,7 +46415,7 @@
         <v>2.56</v>
       </c>
       <c r="DO95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46903,7 +46903,7 @@
         <v>2.92</v>
       </c>
       <c r="DO96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47871,7 +47871,7 @@
         <v>2.65</v>
       </c>
       <c r="DO98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -49412,6 +49412,1902 @@
       <c r="EP101" t="inlineStr">
         <is>
           <t>10.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>15</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46012.64583333334</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>4</v>
+      </c>
+      <c r="L102" t="n">
+        <v>5</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2</v>
+      </c>
+      <c r="N102" t="n">
+        <v>5</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>2</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" t="n">
+        <v>9</v>
+      </c>
+      <c r="U102" t="n">
+        <v>4</v>
+      </c>
+      <c r="V102" t="n">
+        <v>9</v>
+      </c>
+      <c r="W102" t="n">
+        <v>19</v>
+      </c>
+      <c r="X102" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR102" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS102" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU102" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX102" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ102" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DJ102" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK102" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL102" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM102" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DN102" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DO102" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW102" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="DX102" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED102" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EE102" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EF102" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EG102" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH102" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI102" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EJ102" t="inlineStr">
+        <is>
+          <t>4.68</t>
+        </is>
+      </c>
+      <c r="EK102" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EL102" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EM102" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EN102" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EO102" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EP102" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>15</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46012.72916666666</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2</v>
+      </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3</v>
+      </c>
+      <c r="L103" t="n">
+        <v>10</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>11</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="n">
+        <v>2</v>
+      </c>
+      <c r="U103" t="n">
+        <v>16</v>
+      </c>
+      <c r="V103" t="n">
+        <v>3</v>
+      </c>
+      <c r="W103" t="n">
+        <v>13</v>
+      </c>
+      <c r="X103" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL103" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM103" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DN103" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="DO103" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW103" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="DX103" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC103" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="ED103" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EE103" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF103" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG103" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EH103" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI103" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EJ103" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EK103" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EL103" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EM103" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EN103" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EO103" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP103" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>15</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46012.79166666666</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" t="n">
+        <v>3</v>
+      </c>
+      <c r="L104" t="n">
+        <v>8</v>
+      </c>
+      <c r="M104" t="n">
+        <v>4</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>5</v>
+      </c>
+      <c r="R104" t="n">
+        <v>3</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="n">
+        <v>9</v>
+      </c>
+      <c r="U104" t="n">
+        <v>15</v>
+      </c>
+      <c r="V104" t="n">
+        <v>12</v>
+      </c>
+      <c r="W104" t="n">
+        <v>20</v>
+      </c>
+      <c r="X104" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>49</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>63</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>24</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>37</v>
+      </c>
+      <c r="DL104" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM104" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DN104" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DO104" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW104" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="DX104" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr"/>
+      <c r="ED104" t="inlineStr"/>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EM104" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EN104" t="inlineStr">
+        <is>
+          <t>8.60</t>
+        </is>
+      </c>
+      <c r="EO104" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EP104" t="inlineStr">
+        <is>
+          <t>17.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>15</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46013.66666666666</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>7</v>
+      </c>
+      <c r="L105" t="n">
+        <v>9</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>2</v>
+      </c>
+      <c r="O105" t="n">
+        <v>2</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6</v>
+      </c>
+      <c r="S105" t="n">
+        <v>7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>11</v>
+      </c>
+      <c r="U105" t="n">
+        <v>8</v>
+      </c>
+      <c r="V105" t="n">
+        <v>17</v>
+      </c>
+      <c r="W105" t="n">
+        <v>14</v>
+      </c>
+      <c r="X105" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>1108</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ105" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB105" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC105" t="n">
+        <v>93</v>
+      </c>
+      <c r="DD105" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE105" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF105" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DG105" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH105" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="DI105" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DJ105" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK105" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL105" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DM105" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN105" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO105" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW105" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="DX105" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr"/>
+      <c r="EB105" t="inlineStr"/>
+      <c r="EC105" t="inlineStr"/>
+      <c r="ED105" t="inlineStr"/>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EH105" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI105" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EJ105" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EK105" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EL105" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM105" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EN105" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="EO105" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="EP105" t="inlineStr">
+        <is>
+          <t>1.55</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -33669,7 +33669,7 @@
         <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>4</v>
@@ -33721,7 +33721,7 @@
         </is>
       </c>
       <c r="AC69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD69" t="n">
         <v>4</v>
@@ -33841,7 +33841,7 @@
         <v>2</v>
       </c>
       <c r="BQ69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR69" t="n">
         <v>2</v>
@@ -33850,7 +33850,7 @@
         <v>3</v>
       </c>
       <c r="BT69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -34141,7 +34141,7 @@
         <v>8</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
         <v>3</v>
@@ -34193,7 +34193,7 @@
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD70" t="n">
         <v>3</v>
@@ -34313,7 +34313,7 @@
         <v>0</v>
       </c>
       <c r="BQ70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR70" t="n">
         <v>3</v>
@@ -34322,7 +34322,7 @@
         <v>1</v>
       </c>
       <c r="BT70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -42331,7 +42331,7 @@
         <v>14</v>
       </c>
       <c r="W87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X87" t="n">
         <v>6</v>
@@ -47069,7 +47069,7 @@
         <v>8</v>
       </c>
       <c r="M97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N97" t="n">
         <v>2</v>
@@ -47113,7 +47113,7 @@
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD97" t="n">
         <v>3</v>
@@ -47233,16 +47233,16 @@
         <v>2</v>
       </c>
       <c r="BQ97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT97" t="n">
         <v>6</v>
-      </c>
-      <c r="BR97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS97" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT97" t="n">
-        <v>7</v>
       </c>
       <c r="BU97" t="n">
         <v>1</v>
@@ -47549,10 +47549,10 @@
         <v>11</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -47601,10 +47601,10 @@
         </is>
       </c>
       <c r="AC98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE98" t="n">
         <v>1.28</v>
@@ -47715,22 +47715,22 @@
         <v>4</v>
       </c>
       <c r="BO98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR98" t="n">
         <v>4</v>
       </c>
       <c r="BS98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT98" t="n">
         <v>4</v>
-      </c>
-      <c r="BT98" t="n">
-        <v>5</v>
       </c>
       <c r="BU98" t="n">
         <v>1</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP105" headerRowCount="1">
-  <autoFilter ref="A1:EP105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP106" headerRowCount="1">
+  <autoFilter ref="A1:EP106"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP105"/>
+  <dimension ref="A1:EP106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -3685,7 +3685,7 @@
         <v>2.75</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -9461,7 +9461,7 @@
         <v>1.14</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE19" t="n">
         <v>1.14</v>
@@ -11370,7 +11370,7 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE22" t="n">
         <v>1.25</v>
@@ -17577,7 +17577,7 @@
         <v>0.71</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF35" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
         <v>25</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE39" t="n">
         <v>2.29</v>
@@ -24806,7 +24806,7 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE50" t="n">
         <v>1.13</v>
@@ -25289,7 +25289,7 @@
         <v>0.5</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -31553,7 +31553,7 @@
         <v>0.86</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF64" t="n">
         <v>0.75</v>
@@ -31719,170 +31719,162 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>4</v>
       </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
       <c r="K65" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" t="n">
         <v>10</v>
       </c>
-      <c r="L65" t="n">
-        <v>11</v>
-      </c>
       <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2</v>
+      </c>
+      <c r="R65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
         <v>8</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>6</v>
       </c>
-      <c r="T65" t="n">
-        <v>10</v>
-      </c>
-      <c r="U65" t="n">
-        <v>9</v>
-      </c>
       <c r="V65" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y65" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z65" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE65" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF65" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL65" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN65" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO65" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS65" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31897,124 +31889,124 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN65" t="n">
         <v>6</v>
       </c>
-      <c r="BN65" t="n">
+      <c r="BO65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
         <v>5</v>
       </c>
-      <c r="BO65" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>0</v>
-      </c>
       <c r="BS65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS65" t="n">
         <v>23</v>
       </c>
-      <c r="BW65" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ65" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA65" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB65" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS65" t="n">
-        <v>30</v>
-      </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV65" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32023,67 +32015,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ65" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA65" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC65" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="DE65" t="n">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="DF65" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ65" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK65" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM65" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO65" t="n">
         <v>15</v>
       </c>
       <c r="DP65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32092,86 +32084,102 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW65" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX65" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr"/>
-      <c r="EB65" t="inlineStr"/>
-      <c r="EC65" t="inlineStr"/>
-      <c r="ED65" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB65" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC65" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED65" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -32191,162 +32199,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>11</v>
+      </c>
+      <c r="M66" t="n">
         <v>4</v>
       </c>
-      <c r="K66" t="n">
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>8</v>
+      </c>
+      <c r="S66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="n">
+      <c r="T66" t="n">
         <v>10</v>
       </c>
-      <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>6</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
+        <v>9</v>
+      </c>
+      <c r="V66" t="n">
+        <v>18</v>
+      </c>
+      <c r="W66" t="n">
+        <v>14</v>
+      </c>
+      <c r="X66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>4</v>
-      </c>
-      <c r="T66" t="n">
-        <v>8</v>
-      </c>
-      <c r="U66" t="n">
-        <v>6</v>
-      </c>
-      <c r="V66" t="n">
-        <v>12</v>
-      </c>
-      <c r="W66" t="n">
-        <v>19</v>
-      </c>
-      <c r="X66" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32361,76 +32377,76 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
       <c r="BT66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW66" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX66" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY66" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC66" t="n">
         <v>0</v>
       </c>
       <c r="CD66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE66" t="n">
         <v>0</v>
       </c>
       <c r="CF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -32454,7 +32470,7 @@
         <v>0</v>
       </c>
       <c r="CN66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO66" t="n">
         <v>0</v>
@@ -32466,19 +32482,19 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS66" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV66" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32487,67 +32503,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ66" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA66" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC66" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="DF66" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ66" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO66" t="n">
         <v>15</v>
       </c>
       <c r="DP66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32556,102 +32572,86 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX66" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB66" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC66" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED66" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr"/>
+      <c r="EB66" t="inlineStr"/>
+      <c r="EC66" t="inlineStr"/>
+      <c r="ED66" t="inlineStr"/>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -38399,128 +38399,120 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" t="n">
         <v>4</v>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>6</v>
-      </c>
       <c r="R79" t="n">
         <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
+        <v>18</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>14</v>
+      </c>
+      <c r="X79" t="n">
         <v>21</v>
       </c>
-      <c r="V79" t="n">
-        <v>6</v>
-      </c>
-      <c r="W79" t="n">
-        <v>11</v>
-      </c>
-      <c r="X79" t="n">
-        <v>13</v>
-      </c>
       <c r="Y79" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z79" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -38529,10 +38521,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -38544,10 +38536,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -38556,13 +38548,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38577,19 +38569,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -38598,55 +38590,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW79" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX79" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY79" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -38667,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38682,73 +38674,73 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS79" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
         <v>13</v>
       </c>
-      <c r="CV79" t="n">
-        <v>11</v>
-      </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC79" t="n">
         <v>60</v>
       </c>
-      <c r="DA79" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB79" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC79" t="n">
+      <c r="DD79" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ79" t="n">
         <v>80</v>
       </c>
-      <c r="DD79" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>40</v>
-      </c>
       <c r="DK79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM79" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN79" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO79" t="n">
         <v>15</v>
@@ -38772,102 +38764,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>14.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DX79" t="n">
-        <v>7.45</v>
+        <v>5.91</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="EC79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -38887,120 +38879,128 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>6</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>8</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
       <c r="U80" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y80" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z80" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF80" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK80" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -39009,10 +39009,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -39024,10 +39024,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -39036,13 +39036,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -39057,19 +39057,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -39078,55 +39078,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT80" t="n">
         <v>4</v>
       </c>
-      <c r="BT80" t="n">
-        <v>6</v>
-      </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW80" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX80" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY80" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -39147,7 +39147,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -39162,73 +39162,73 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV80" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA80" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC80" t="n">
         <v>80</v>
       </c>
-      <c r="DB80" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>60</v>
-      </c>
       <c r="DD80" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.71</v>
+        <v>0.14</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG80" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH80" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ80" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN80" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO80" t="n">
         <v>15</v>
@@ -39252,102 +39252,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>9.869999999999999</v>
+        <v>14.67</v>
       </c>
       <c r="DX80" t="n">
-        <v>5.91</v>
+        <v>7.45</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EN80" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -44937,7 +44937,7 @@
         <v>2</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DF92" t="n">
         <v>1.86</v>
@@ -45894,7 +45894,7 @@
         <v>77</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE94" t="n">
         <v>0.63</v>
@@ -51308,6 +51308,494 @@
       <c r="EP105" t="inlineStr">
         <is>
           <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>16</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46032.625</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" t="n">
+        <v>4</v>
+      </c>
+      <c r="L106" t="n">
+        <v>8</v>
+      </c>
+      <c r="M106" t="n">
+        <v>4</v>
+      </c>
+      <c r="N106" t="n">
+        <v>3</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>6</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7</v>
+      </c>
+      <c r="S106" t="n">
+        <v>17</v>
+      </c>
+      <c r="T106" t="n">
+        <v>6</v>
+      </c>
+      <c r="U106" t="n">
+        <v>23</v>
+      </c>
+      <c r="V106" t="n">
+        <v>13</v>
+      </c>
+      <c r="W106" t="n">
+        <v>18</v>
+      </c>
+      <c r="X106" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY106" t="n">
+        <v>21</v>
+      </c>
+      <c r="CZ106" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA106" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB106" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC106" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD106" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE106" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF106" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG106" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH106" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI106" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DJ106" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK106" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL106" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM106" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DN106" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DO106" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW106" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="DX106" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ106" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA106" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EB106" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC106" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED106" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EE106" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EH106" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI106" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EJ106" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EK106" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EL106" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM106" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN106" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EO106" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP106" t="inlineStr">
+        <is>
+          <t>4.56</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP106" headerRowCount="1">
-  <autoFilter ref="A1:EP106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP112" headerRowCount="1">
+  <autoFilter ref="A1:EP112"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP106"/>
+  <dimension ref="A1:EP112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>2.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>2.63</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4162,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE7" t="n">
         <v>1.25</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4653,7 +4653,7 @@
         <v>1.86</v>
       </c>
       <c r="DE8" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE10" t="n">
         <v>1.13</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6573,7 +6573,7 @@
         <v>2.63</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6603,7 +6603,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE14" t="n">
         <v>1.71</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8029,7 +8029,7 @@
         <v>2.75</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -8059,7 +8059,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8506,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE16" t="n">
         <v>1.25</v>
@@ -8539,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8986,10 +8986,10 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9019,7 +9019,7 @@
         <v>2.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9491,7 +9491,7 @@
         <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9971,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10394,10 +10394,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10882,10 +10882,10 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11051,170 +11051,162 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>15</v>
+      </c>
+      <c r="V22" t="n">
         <v>11</v>
       </c>
-      <c r="U22" t="n">
-        <v>6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>15</v>
-      </c>
       <c r="W22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Z22" t="n">
-        <v>71</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Stadio Panetolikou</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Nikitara, Agrinio</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="AO22" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
         <v>1</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB22" t="n">
-        <v>5131</v>
+        <v>-1</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -11229,40 +11221,40 @@
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
         <v>4</v>
       </c>
       <c r="BM22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT22" t="n">
         <v>5</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>3</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
@@ -11271,22 +11263,22 @@
         <v>41</v>
       </c>
       <c r="BW22" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="BX22" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY22" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -11319,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -11334,82 +11326,82 @@
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CV22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CW22" t="n">
         <v>1</v>
       </c>
       <c r="CX22" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY22" t="n">
         <v>10</v>
       </c>
-      <c r="CY22" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>25</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ22" t="n">
         <v>100</v>
       </c>
-      <c r="DA22" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB22" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC22" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DF22" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG22" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DI22" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ22" t="n">
-        <v>0</v>
-      </c>
       <c r="DK22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="DL22" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="DM22" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="DN22" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
       </c>
       <c r="DQ22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR22" t="b">
         <v>0</v>
@@ -11424,17 +11416,17 @@
         <v>0</v>
       </c>
       <c r="DV22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW22" t="n">
-        <v>26.11</v>
+        <v>29.14</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.6</v>
+        <v>4</v>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
@@ -11442,76 +11434,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA22" t="inlineStr"/>
-      <c r="EB22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EC22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="ED22" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EH22" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr"/>
       <c r="EI22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ22" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EL22" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM22" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EN22" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EO22" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EP22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -11531,162 +11523,170 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U23" t="n">
+        <v>6</v>
+      </c>
+      <c r="V23" t="n">
         <v>15</v>
       </c>
-      <c r="V23" t="n">
-        <v>11</v>
-      </c>
       <c r="W23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z23" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
         <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.64</v>
+        <v>2.21</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>-1</v>
+        <v>5131</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11701,40 +11701,40 @@
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL23" t="n">
         <v>4</v>
       </c>
       <c r="BM23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP23" t="n">
         <v>1</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR23" t="n">
         <v>2</v>
       </c>
       <c r="BS23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
@@ -11743,22 +11743,22 @@
         <v>41</v>
       </c>
       <c r="BW23" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="BX23" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BY23" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.38</v>
+        <v>0.68</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11791,10 +11791,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11806,82 +11806,82 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
       </c>
       <c r="CX23" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY23" t="n">
         <v>6</v>
       </c>
-      <c r="CY23" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DB23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DF23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="DI23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DJ23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK23" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DL23" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="DM23" t="n">
-        <v>0.82</v>
+        <v>1.31</v>
       </c>
       <c r="DN23" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
       </c>
       <c r="DQ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR23" t="b">
         <v>0</v>
@@ -11896,17 +11896,17 @@
         <v>0</v>
       </c>
       <c r="DV23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW23" t="n">
-        <v>29.14</v>
+        <v>26.11</v>
       </c>
       <c r="DX23" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="DY23" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ23" t="inlineStr">
@@ -11914,76 +11914,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA23" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="EB23" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+      <c r="EA23" t="inlineStr"/>
+      <c r="EB23" t="inlineStr"/>
       <c r="EC23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED23" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr"/>
-      <c r="EH23" t="inlineStr"/>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM23" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EN23" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EO23" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EP23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
         <v>1.86</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12355,7 +12355,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>0.5</v>
       </c>
       <c r="DE26" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13750,7 +13750,7 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE27" t="n">
         <v>0.86</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14222,10 +14222,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE28" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14743,7 +14743,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15174,10 +15174,10 @@
         <v>25</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF30" t="n">
         <v>1.5</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15641,7 +15641,7 @@
         <v>2.63</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>75</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE32" t="n">
         <v>1.25</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16617,7 +16617,7 @@
         <v>1.14</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -16647,7 +16647,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17086,7 +17086,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE34" t="n">
         <v>1.14</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17574,7 +17574,7 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE35" t="n">
         <v>0.75</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18057,7 +18057,7 @@
         <v>0.5</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -18087,7 +18087,7 @@
         <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18542,7 +18542,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE37" t="n">
         <v>1.25</v>
@@ -18575,7 +18575,7 @@
         <v>2.34</v>
       </c>
       <c r="DO37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19025,7 +19025,7 @@
         <v>0.5</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19175,170 +19175,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
+        <v>10</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
         <v>7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>9</v>
       </c>
       <c r="T39" t="n">
         <v>6</v>
       </c>
       <c r="U39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V39" t="n">
+        <v>7</v>
+      </c>
+      <c r="W39" t="n">
+        <v>11</v>
+      </c>
+      <c r="X39" t="n">
         <v>9</v>
       </c>
-      <c r="W39" t="n">
-        <v>20</v>
-      </c>
-      <c r="X39" t="n">
-        <v>18</v>
-      </c>
       <c r="Y39" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="Z39" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Stadio Zirinio</t>
+          <t>Stadio Levadias</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Kifissia, Athens</t>
+          <t>Agion Theodoron, Levadia</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>8.08</v>
+        <v>1.67</v>
       </c>
       <c r="AF39" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AU39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
         <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB39" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19353,13 +19353,13 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL39" t="n">
         <v>0</v>
@@ -19368,61 +19368,61 @@
         <v>5</v>
       </c>
       <c r="BN39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BQ39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR39" t="n">
         <v>2</v>
       </c>
       <c r="BS39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BT39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="BW39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY39" t="n">
         <v>57</v>
       </c>
-      <c r="BX39" t="n">
-        <v>73</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>77</v>
-      </c>
       <c r="BZ39" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="CB39" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CC39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG39" t="n">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ39" t="n">
         <v>1</v>
@@ -19461,46 +19461,46 @@
         <v>17</v>
       </c>
       <c r="CS39" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB39" t="n">
         <v>17</v>
       </c>
-      <c r="CV39" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX39" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY39" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ39" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA39" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB39" t="n">
-        <v>25</v>
-      </c>
       <c r="DC39" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="DD39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE39" t="n">
         <v>1.13</v>
       </c>
-      <c r="DE39" t="n">
-        <v>2.29</v>
-      </c>
       <c r="DF39" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG39" t="n">
         <v>2</v>
@@ -19509,25 +19509,25 @@
         <v>1.4</v>
       </c>
       <c r="DI39" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="DJ39" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="DK39" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DL39" t="n">
-        <v>0.87</v>
+        <v>1.58</v>
       </c>
       <c r="DM39" t="n">
-        <v>2.14</v>
+        <v>0.76</v>
       </c>
       <c r="DN39" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="DO39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19545,20 +19545,20 @@
         <v>1</v>
       </c>
       <c r="DU39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW39" t="n">
-        <v>20.41</v>
+        <v>19.8</v>
       </c>
       <c r="DX39" t="n">
-        <v>3.34</v>
+        <v>2.29</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19568,82 +19568,82 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>5.77</t>
         </is>
       </c>
     </row>
@@ -19663,170 +19663,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
         <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="X40" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="Z40" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Stadio Levadias</t>
+          <t>Stadio Zirinio</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Agion Theodoron, Levadia</t>
+          <t>Kifissia, Athens</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU40" t="n">
         <v>5</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>6</v>
-      </c>
       <c r="AV40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ40" t="n">
         <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB40" t="n">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19841,13 +19841,13 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL40" t="n">
         <v>0</v>
@@ -19856,61 +19856,61 @@
         <v>5</v>
       </c>
       <c r="BN40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR40" t="n">
         <v>2</v>
       </c>
       <c r="BS40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BT40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY40" t="n">
         <v>77</v>
       </c>
-      <c r="BW40" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>137</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>57</v>
-      </c>
       <c r="BZ40" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="CB40" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="CC40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG40" t="n">
         <v>0</v>
@@ -19931,7 +19931,7 @@
         <v>0</v>
       </c>
       <c r="CM40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
@@ -19940,7 +19940,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ40" t="n">
         <v>1</v>
@@ -19949,46 +19949,46 @@
         <v>17</v>
       </c>
       <c r="CS40" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV40" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CW40" t="n">
         <v>1</v>
       </c>
       <c r="CX40" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY40" t="n">
         <v>10</v>
       </c>
-      <c r="CY40" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ40" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DA40" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DB40" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DC40" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DF40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG40" t="n">
         <v>2</v>
@@ -19997,25 +19997,25 @@
         <v>1.4</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ40" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="DK40" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DL40" t="n">
-        <v>1.58</v>
+        <v>0.87</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.76</v>
+        <v>2.14</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20033,20 +20033,20 @@
         <v>1</v>
       </c>
       <c r="DU40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>19.8</v>
+        <v>20.41</v>
       </c>
       <c r="DX40" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -20056,82 +20056,82 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
         <v>2.75</v>
       </c>
       <c r="DE41" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DF41" t="n">
         <v>2.33</v>
@@ -20495,7 +20495,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20950,7 +20950,7 @@
         <v>59</v>
       </c>
       <c r="DD42" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE42" t="n">
         <v>1</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21425,7 +21425,7 @@
         <v>0.5</v>
       </c>
       <c r="DE43" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DF43" t="n">
         <v>0.67</v>
@@ -21455,7 +21455,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21910,7 +21910,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE44" t="n">
         <v>1.71</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22398,7 +22398,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE45" t="n">
         <v>0.86</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22919,7 +22919,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23377,7 +23377,7 @@
         <v>1.86</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23838,7 +23838,7 @@
         <v>67</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE48" t="n">
         <v>1.14</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24321,7 +24321,7 @@
         <v>2.63</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF49" t="n">
         <v>3</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25758,7 +25758,7 @@
         <v>75</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE52" t="n">
         <v>1</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26246,7 +26246,7 @@
         <v>71</v>
       </c>
       <c r="DD53" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE53" t="n">
         <v>1.25</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26734,10 +26734,10 @@
         <v>54</v>
       </c>
       <c r="DD54" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF54" t="n">
         <v>1.67</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27217,7 +27217,7 @@
         <v>2.75</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF55" t="n">
         <v>2.5</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27689,7 +27689,7 @@
         <v>2.75</v>
       </c>
       <c r="DE56" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -27719,7 +27719,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28662,7 +28662,7 @@
         <v>88</v>
       </c>
       <c r="DD58" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE58" t="n">
         <v>1.25</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29183,7 +29183,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30105,7 +30105,7 @@
         <v>0.5</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF61" t="n">
         <v>1</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31550,7 +31550,7 @@
         <v>75</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE64" t="n">
         <v>0.75</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31719,162 +31719,170 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="n">
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>8</v>
+      </c>
+      <c r="S65" t="n">
         <v>6</v>
       </c>
-      <c r="L65" t="n">
+      <c r="T65" t="n">
         <v>10</v>
       </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
+        <v>9</v>
+      </c>
+      <c r="V65" t="n">
+        <v>18</v>
+      </c>
+      <c r="W65" t="n">
+        <v>14</v>
+      </c>
+      <c r="X65" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU65" t="n">
         <v>4</v>
       </c>
-      <c r="S65" t="n">
-        <v>4</v>
-      </c>
-      <c r="T65" t="n">
-        <v>8</v>
-      </c>
-      <c r="U65" t="n">
-        <v>6</v>
-      </c>
-      <c r="V65" t="n">
-        <v>12</v>
-      </c>
-      <c r="W65" t="n">
-        <v>19</v>
-      </c>
-      <c r="X65" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31889,76 +31897,76 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS65" t="n">
         <v>4</v>
       </c>
-      <c r="BN65" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>2</v>
-      </c>
       <c r="BT65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW65" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX65" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY65" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC65" t="n">
         <v>0</v>
       </c>
       <c r="CD65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE65" t="n">
         <v>0</v>
       </c>
       <c r="CF65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG65" t="n">
         <v>0</v>
@@ -31982,7 +31990,7 @@
         <v>0</v>
       </c>
       <c r="CN65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO65" t="n">
         <v>0</v>
@@ -31994,19 +32002,19 @@
         <v>1</v>
       </c>
       <c r="CR65" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS65" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV65" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32015,67 +32023,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ65" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA65" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.63</v>
+        <v>2.13</v>
       </c>
       <c r="DF65" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ65" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK65" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM65" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32084,102 +32092,86 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW65" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX65" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB65" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC65" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED65" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr"/>
+      <c r="EB65" t="inlineStr"/>
+      <c r="EC65" t="inlineStr"/>
+      <c r="ED65" t="inlineStr"/>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -32199,170 +32191,162 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>4</v>
       </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" t="n">
+        <v>6</v>
+      </c>
+      <c r="L66" t="n">
         <v>10</v>
       </c>
-      <c r="L66" t="n">
-        <v>11</v>
-      </c>
       <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
         <v>4</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
         <v>8</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>9</v>
-      </c>
       <c r="V66" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y66" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE66" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF66" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN66" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO66" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32377,124 +32361,124 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN66" t="n">
         <v>6</v>
       </c>
-      <c r="BN66" t="n">
+      <c r="BO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
         <v>5</v>
       </c>
-      <c r="BO66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>0</v>
-      </c>
       <c r="BS66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS66" t="n">
         <v>23</v>
       </c>
-      <c r="BW66" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>30</v>
-      </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32503,67 +32487,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ66" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA66" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="DE66" t="n">
-        <v>2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF66" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ66" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32572,86 +32556,102 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX66" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr"/>
-      <c r="EB66" t="inlineStr"/>
-      <c r="EC66" t="inlineStr"/>
-      <c r="ED66" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -32990,10 +32990,10 @@
         <v>78</v>
       </c>
       <c r="DD67" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33478,10 +33478,10 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF68" t="n">
         <v>0.75</v>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33958,10 +33958,10 @@
         <v>58</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34430,10 +34430,10 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34935,7 +34935,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35423,7 +35423,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35903,7 +35903,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36383,7 +36383,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36855,7 +36855,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37327,7 +37327,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37807,7 +37807,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38246,10 +38246,10 @@
         <v>65</v>
       </c>
       <c r="DD78" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF78" t="n">
         <v>0.6</v>
@@ -38279,7 +38279,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38710,7 +38710,7 @@
         <v>60</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE79" t="n">
         <v>0.75</v>
@@ -38743,7 +38743,7 @@
         <v>2.96</v>
       </c>
       <c r="DO79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39201,7 +39201,7 @@
         <v>1.13</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF80" t="n">
         <v>0.8</v>
@@ -39231,7 +39231,7 @@
         <v>1.76</v>
       </c>
       <c r="DO80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39367,12 +39367,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -39388,119 +39388,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="n">
+        <v>13</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>7</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>11</v>
+      </c>
+      <c r="V81" t="n">
         <v>9</v>
       </c>
-      <c r="L81" t="n">
-        <v>12</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5</v>
-      </c>
-      <c r="S81" t="n">
-        <v>4</v>
-      </c>
-      <c r="T81" t="n">
-        <v>19</v>
-      </c>
-      <c r="U81" t="n">
-        <v>6</v>
-      </c>
-      <c r="V81" t="n">
-        <v>24</v>
-      </c>
       <c r="W81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X81" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y81" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z81" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE81" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF81" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI81" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL81" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM81" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ81" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR81" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -39509,28 +39509,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -39542,13 +39542,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -39557,52 +39557,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW81" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX81" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY81" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA81" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB81" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -39635,91 +39635,91 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW81" t="n">
         <v>1</v>
       </c>
       <c r="CX81" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY81" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ81" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA81" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="DE81" t="n">
-        <v>2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF81" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG81" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH81" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI81" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ81" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK81" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL81" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39743,99 +39743,99 @@
         <v>0</v>
       </c>
       <c r="DW81" t="n">
-        <v>14.32</v>
+        <v>16.31</v>
       </c>
       <c r="DX81" t="n">
-        <v>1.76</v>
+        <v>5.04</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EJ81" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EK81" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EL81" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EN81" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EO81" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EP81" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -39855,12 +39855,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -39876,119 +39876,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K82" t="n">
+        <v>9</v>
+      </c>
+      <c r="L82" t="n">
+        <v>12</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>19</v>
+      </c>
+      <c r="U82" t="n">
         <v>6</v>
       </c>
-      <c r="L82" t="n">
+      <c r="V82" t="n">
+        <v>24</v>
+      </c>
+      <c r="W82" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
         <v>13</v>
       </c>
-      <c r="M82" t="n">
-        <v>2</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>4</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>7</v>
-      </c>
-      <c r="T82" t="n">
-        <v>3</v>
-      </c>
-      <c r="U82" t="n">
-        <v>11</v>
-      </c>
-      <c r="V82" t="n">
-        <v>9</v>
-      </c>
-      <c r="W82" t="n">
-        <v>15</v>
-      </c>
-      <c r="X82" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF82" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI82" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ82" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM82" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR82" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -39997,28 +39997,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -40030,13 +40030,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ82" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ82" t="n">
-        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -40045,52 +40045,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW82" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX82" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY82" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ82" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB82" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -40123,91 +40123,91 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS82" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
         <v>22</v>
       </c>
-      <c r="CT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU82" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
+      <c r="CY82" t="n">
         <v>4</v>
       </c>
-      <c r="CY82" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ82" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA82" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.63</v>
+        <v>2.13</v>
       </c>
       <c r="DF82" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG82" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH82" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI82" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ82" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK82" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM82" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40231,99 +40231,99 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>16.31</v>
+        <v>14.32</v>
       </c>
       <c r="DX82" t="n">
-        <v>5.04</v>
+        <v>1.76</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ82" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EM82" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN82" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EO82" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EP82" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -40662,10 +40662,10 @@
         <v>92</v>
       </c>
       <c r="DD83" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF83" t="n">
         <v>2.17</v>
@@ -40695,7 +40695,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41150,10 +41150,10 @@
         <v>50</v>
       </c>
       <c r="DD84" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE84" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF84" t="n">
         <v>2.2</v>
@@ -41183,7 +41183,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41671,7 +41671,7 @@
         <v>3.31</v>
       </c>
       <c r="DO85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -42151,7 +42151,7 @@
         <v>3.01</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42623,7 +42623,7 @@
         <v>2.39</v>
       </c>
       <c r="DO87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43103,7 +43103,7 @@
         <v>3.02</v>
       </c>
       <c r="DO88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43567,7 +43567,7 @@
         <v>3.26</v>
       </c>
       <c r="DO89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -44031,7 +44031,7 @@
         <v>2.86</v>
       </c>
       <c r="DO90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44495,7 +44495,7 @@
         <v>1.9</v>
       </c>
       <c r="DO91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44934,7 +44934,7 @@
         <v>85</v>
       </c>
       <c r="DD92" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE92" t="n">
         <v>0.75</v>
@@ -44967,7 +44967,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45422,10 +45422,10 @@
         <v>75</v>
       </c>
       <c r="DD93" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF93" t="n">
         <v>0.5</v>
@@ -45455,7 +45455,7 @@
         <v>1.48</v>
       </c>
       <c r="DO93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45897,7 +45897,7 @@
         <v>1.13</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF94" t="n">
         <v>1.17</v>
@@ -45927,7 +45927,7 @@
         <v>2.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP94" t="b">
         <v>0</v>
@@ -46382,10 +46382,10 @@
         <v>59</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE95" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DF95" t="n">
         <v>1</v>
@@ -46415,7 +46415,7 @@
         <v>2.56</v>
       </c>
       <c r="DO95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46870,10 +46870,10 @@
         <v>92</v>
       </c>
       <c r="DD96" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF96" t="n">
         <v>0.33</v>
@@ -46903,7 +46903,7 @@
         <v>2.92</v>
       </c>
       <c r="DO96" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -47350,10 +47350,10 @@
         <v>50</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE97" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DF97" t="n">
         <v>1.5</v>
@@ -47383,7 +47383,7 @@
         <v>3.37</v>
       </c>
       <c r="DO97" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -47838,10 +47838,10 @@
         <v>55</v>
       </c>
       <c r="DD98" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF98" t="n">
         <v>1.83</v>
@@ -47871,7 +47871,7 @@
         <v>2.65</v>
       </c>
       <c r="DO98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48343,7 +48343,7 @@
         <v>2.41</v>
       </c>
       <c r="DO99" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -48815,7 +48815,7 @@
         <v>2.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49303,7 +49303,7 @@
         <v>4.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49775,7 +49775,7 @@
         <v>2.15</v>
       </c>
       <c r="DO102" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -50255,7 +50255,7 @@
         <v>3.68</v>
       </c>
       <c r="DO103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50735,7 +50735,7 @@
         <v>2.97</v>
       </c>
       <c r="DO104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -51207,7 +51207,7 @@
         <v>2.24</v>
       </c>
       <c r="DO105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51496,7 +51496,7 @@
         <v>0</v>
       </c>
       <c r="BF106" t="n">
-        <v>-1</v>
+        <v>965</v>
       </c>
       <c r="BG106" t="n">
         <v>2</v>
@@ -51796,6 +51796,2862 @@
       <c r="EP106" t="inlineStr">
         <is>
           <t>4.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>16</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46032.72916666666</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2</v>
+      </c>
+      <c r="R107" t="n">
+        <v>5</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" t="n">
+        <v>4</v>
+      </c>
+      <c r="U107" t="n">
+        <v>4</v>
+      </c>
+      <c r="V107" t="n">
+        <v>9</v>
+      </c>
+      <c r="W107" t="n">
+        <v>16</v>
+      </c>
+      <c r="X107" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Stadio Peristeriou</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>93 Giannitson, Peristeri, Athens</t>
+        </is>
+      </c>
+      <c r="AC107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>116</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>2818</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>76</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>33</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY107" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ107" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC107" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD107" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DE107" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DG107" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH107" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DI107" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DJ107" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL107" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM107" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN107" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DO107" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW107" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="DX107" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA107" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr"/>
+      <c r="EJ107" t="inlineStr"/>
+      <c r="EK107" t="inlineStr"/>
+      <c r="EL107" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN107" t="inlineStr">
+        <is>
+          <t>5.80</t>
+        </is>
+      </c>
+      <c r="EO107" t="inlineStr">
+        <is>
+          <t>11.28</t>
+        </is>
+      </c>
+      <c r="EP107" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>16</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46032.72916666666</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>5</v>
+      </c>
+      <c r="K108" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" t="n">
+        <v>13</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1</v>
+      </c>
+      <c r="R108" t="n">
+        <v>8</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="n">
+        <v>15</v>
+      </c>
+      <c r="U108" t="n">
+        <v>2</v>
+      </c>
+      <c r="V108" t="n">
+        <v>23</v>
+      </c>
+      <c r="W108" t="n">
+        <v>14</v>
+      </c>
+      <c r="X108" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>1843</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ108" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DO108" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW108" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="DX108" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF108" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EJ108" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EK108" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EL108" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="EO108" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="EP108" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>16</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46033.58333333334</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>4</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3</v>
+      </c>
+      <c r="L109" t="n">
+        <v>4</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>3</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>6</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
+        <v>8</v>
+      </c>
+      <c r="T109" t="n">
+        <v>11</v>
+      </c>
+      <c r="U109" t="n">
+        <v>14</v>
+      </c>
+      <c r="V109" t="n">
+        <v>13</v>
+      </c>
+      <c r="W109" t="n">
+        <v>11</v>
+      </c>
+      <c r="X109" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Stadio Levadias</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Agion Theodoron, Levadia</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>1108</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>1239</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN109" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO109" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW109" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="DX109" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI109" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ109" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EK109" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EL109" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EM109" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN109" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="EO109" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EP109" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>16</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>46033.64583333334</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>4</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>6</v>
+      </c>
+      <c r="L110" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>3</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>7</v>
+      </c>
+      <c r="R110" t="n">
+        <v>3</v>
+      </c>
+      <c r="S110" t="n">
+        <v>11</v>
+      </c>
+      <c r="T110" t="n">
+        <v>12</v>
+      </c>
+      <c r="U110" t="n">
+        <v>18</v>
+      </c>
+      <c r="V110" t="n">
+        <v>15</v>
+      </c>
+      <c r="W110" t="n">
+        <v>15</v>
+      </c>
+      <c r="X110" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Stadio Thódoros Vardinoyánnis</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>Parnassou, Heraklion</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>61</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DN110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DO110" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW110" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="DX110" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr"/>
+      <c r="EB110" t="inlineStr"/>
+      <c r="EC110" t="inlineStr"/>
+      <c r="ED110" t="inlineStr"/>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH110" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI110" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EJ110" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="EK110" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EL110" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EM110" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EN110" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EO110" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EP110" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>16</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>46033.72916666666</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>7</v>
+      </c>
+      <c r="K111" t="n">
+        <v>4</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3</v>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>4</v>
+      </c>
+      <c r="R111" t="n">
+        <v>3</v>
+      </c>
+      <c r="S111" t="n">
+        <v>6</v>
+      </c>
+      <c r="T111" t="n">
+        <v>7</v>
+      </c>
+      <c r="U111" t="n">
+        <v>10</v>
+      </c>
+      <c r="V111" t="n">
+        <v>10</v>
+      </c>
+      <c r="W111" t="n">
+        <v>14</v>
+      </c>
+      <c r="X111" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>56</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR111" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS111" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV111" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX111" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY111" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ111" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA111" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB111" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC111" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD111" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE111" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DF111" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG111" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DH111" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI111" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DJ111" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK111" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL111" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM111" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DN111" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="DO111" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW111" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="DX111" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="DY111" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ111" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="EA111" t="inlineStr"/>
+      <c r="EB111" t="inlineStr"/>
+      <c r="EC111" t="inlineStr"/>
+      <c r="ED111" t="inlineStr"/>
+      <c r="EE111" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EF111" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EG111" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EH111" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EI111" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EJ111" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EK111" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EL111" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EM111" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN111" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EO111" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EP111" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>16</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>46033.79166666666</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>10</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" t="n">
+        <v>11</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" t="n">
+        <v>4</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>10</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="n">
+        <v>9</v>
+      </c>
+      <c r="T112" t="n">
+        <v>2</v>
+      </c>
+      <c r="U112" t="n">
+        <v>19</v>
+      </c>
+      <c r="V112" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" t="n">
+        <v>13</v>
+      </c>
+      <c r="X112" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Olympiako Stadio Spyros Louis</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>37 Kifissias Avenue, Maroussi, Athens</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>960</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>35</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU112" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV112" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX112" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY112" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ112" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA112" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB112" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC112" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD112" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DE112" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF112" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG112" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DH112" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DI112" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ112" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK112" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL112" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM112" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DN112" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO112" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW112" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="DX112" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="DY112" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ112" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="EA112" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EB112" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EC112" t="inlineStr"/>
+      <c r="ED112" t="inlineStr"/>
+      <c r="EE112" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EF112" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EG112" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH112" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EI112" t="inlineStr"/>
+      <c r="EJ112" t="inlineStr"/>
+      <c r="EK112" t="inlineStr"/>
+      <c r="EL112" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EM112" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EN112" t="inlineStr">
+        <is>
+          <t>8.93</t>
+        </is>
+      </c>
+      <c r="EO112" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EP112" t="inlineStr">
+        <is>
+          <t>18.07</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -53062,10 +53062,10 @@
         <v>1</v>
       </c>
       <c r="CR109" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CS109" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CT109" t="n">
         <v>1</v>
@@ -53436,7 +53436,7 @@
         <v>0</v>
       </c>
       <c r="BF110" t="n">
-        <v>-1</v>
+        <v>5741</v>
       </c>
       <c r="BG110" t="n">
         <v>2</v>
@@ -53763,10 +53763,10 @@
         <v>7</v>
       </c>
       <c r="K111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L111" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M111" t="n">
         <v>3</v>
@@ -53790,25 +53790,25 @@
         <v>6</v>
       </c>
       <c r="T111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U111" t="n">
         <v>10</v>
       </c>
       <c r="V111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W111" t="n">
+        <v>18</v>
+      </c>
+      <c r="X111" t="n">
         <v>14</v>
       </c>
-      <c r="X111" t="n">
-        <v>13</v>
-      </c>
       <c r="Y111" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z111" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr"/>
@@ -53900,7 +53900,7 @@
         <v>0</v>
       </c>
       <c r="BF111" t="n">
-        <v>-1</v>
+        <v>4573</v>
       </c>
       <c r="BG111" t="n">
         <v>-1</v>
@@ -53963,10 +53963,10 @@
         <v>1.2</v>
       </c>
       <c r="CA111" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="CB111" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="CC111" t="n">
         <v>0</v>
@@ -54017,22 +54017,22 @@
         <v>15</v>
       </c>
       <c r="CS111" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV111" t="n">
         <v>18</v>
       </c>
-      <c r="CT111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU111" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV111" t="n">
-        <v>14</v>
-      </c>
       <c r="CW111" t="n">
         <v>1</v>
       </c>
       <c r="CX111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY111" t="n">
         <v>2</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP112" headerRowCount="1">
-  <autoFilter ref="A1:EP112"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP116" headerRowCount="1">
+  <autoFilter ref="A1:EP116"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP112"/>
+  <dimension ref="A1:EP116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE5" t="n">
         <v>0.13</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE6" t="n">
         <v>0.75</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>2.11</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -5130,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6090,10 +6090,10 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE12" t="n">
         <v>0.5600000000000001</v>
@@ -7050,7 +7050,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8509,7 +8509,7 @@
         <v>0.63</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -9941,7 +9941,7 @@
         <v>1.13</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9971,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10915,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11362,7 +11362,7 @@
         <v>25</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE22" t="n">
         <v>1</v>
@@ -11845,7 +11845,7 @@
         <v>1.13</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11875,7 +11875,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12790,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE25" t="n">
         <v>1.13</v>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE26" t="n">
         <v>2.13</v>
@@ -13295,7 +13295,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13753,7 +13753,7 @@
         <v>2.11</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13783,7 +13783,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15207,7 +15207,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15638,7 +15638,7 @@
         <v>75</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE31" t="n">
         <v>1.33</v>
@@ -16129,7 +16129,7 @@
         <v>1.13</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -16159,7 +16159,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -17089,7 +17089,7 @@
         <v>0.75</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18054,7 +18054,7 @@
         <v>59</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE36" t="n">
         <v>0.5600000000000001</v>
@@ -18545,7 +18545,7 @@
         <v>1.13</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18575,7 +18575,7 @@
         <v>2.34</v>
       </c>
       <c r="DO37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19022,7 +19022,7 @@
         <v>17</v>
       </c>
       <c r="DD38" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE38" t="n">
         <v>1.33</v>
@@ -20015,7 +20015,7 @@
         <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20462,7 +20462,7 @@
         <v>0</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE41" t="n">
         <v>2.13</v>
@@ -20983,7 +20983,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21422,7 +21422,7 @@
         <v>33</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE43" t="n">
         <v>2.13</v>
@@ -22401,7 +22401,7 @@
         <v>0.75</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF45" t="n">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22889,7 +22889,7 @@
         <v>1.14</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -23841,7 +23841,7 @@
         <v>1.38</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -23871,7 +23871,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24318,7 +24318,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE49" t="n">
         <v>2</v>
@@ -24351,7 +24351,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25286,7 +25286,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE51" t="n">
         <v>0.75</v>
@@ -25319,7 +25319,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25791,7 +25791,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26249,7 +26249,7 @@
         <v>2.11</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF53" t="n">
         <v>2.25</v>
@@ -26767,7 +26767,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27214,7 +27214,7 @@
         <v>38</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE55" t="n">
         <v>1.33</v>
@@ -28177,7 +28177,7 @@
         <v>1.86</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -28207,7 +28207,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28665,7 +28665,7 @@
         <v>0.63</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF58" t="n">
         <v>0.67</v>
@@ -29153,7 +29153,7 @@
         <v>2.75</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF59" t="n">
         <v>3</v>
@@ -29638,7 +29638,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE60" t="n">
         <v>1.71</v>
@@ -30102,7 +30102,7 @@
         <v>88</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE61" t="n">
         <v>2</v>
@@ -30135,7 +30135,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30574,7 +30574,7 @@
         <v>63</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE62" t="n">
         <v>1.13</v>
@@ -31065,7 +31065,7 @@
         <v>1.14</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF63" t="n">
         <v>1</v>
@@ -31095,7 +31095,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31719,170 +31719,162 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>4</v>
       </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
       <c r="K65" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" t="n">
         <v>10</v>
       </c>
-      <c r="L65" t="n">
-        <v>11</v>
-      </c>
       <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2</v>
+      </c>
+      <c r="R65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
         <v>8</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>6</v>
       </c>
-      <c r="T65" t="n">
-        <v>10</v>
-      </c>
-      <c r="U65" t="n">
-        <v>9</v>
-      </c>
       <c r="V65" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y65" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z65" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE65" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF65" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL65" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN65" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO65" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS65" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31897,124 +31889,124 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN65" t="n">
         <v>6</v>
       </c>
-      <c r="BN65" t="n">
+      <c r="BO65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
         <v>5</v>
       </c>
-      <c r="BO65" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>0</v>
-      </c>
       <c r="BS65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS65" t="n">
         <v>23</v>
       </c>
-      <c r="BW65" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ65" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA65" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB65" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS65" t="n">
-        <v>30</v>
-      </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV65" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32023,67 +32015,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ65" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA65" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC65" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="DE65" t="n">
-        <v>2.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF65" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ65" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK65" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM65" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO65" t="n">
         <v>16</v>
       </c>
       <c r="DP65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32092,86 +32084,102 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW65" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX65" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr"/>
-      <c r="EB65" t="inlineStr"/>
-      <c r="EC65" t="inlineStr"/>
-      <c r="ED65" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB65" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC65" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED65" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -32191,162 +32199,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>11</v>
+      </c>
+      <c r="M66" t="n">
         <v>4</v>
       </c>
-      <c r="K66" t="n">
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>8</v>
+      </c>
+      <c r="S66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="n">
+      <c r="T66" t="n">
         <v>10</v>
       </c>
-      <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>6</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
+        <v>9</v>
+      </c>
+      <c r="V66" t="n">
+        <v>18</v>
+      </c>
+      <c r="W66" t="n">
+        <v>14</v>
+      </c>
+      <c r="X66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>4</v>
-      </c>
-      <c r="T66" t="n">
-        <v>8</v>
-      </c>
-      <c r="U66" t="n">
-        <v>6</v>
-      </c>
-      <c r="V66" t="n">
-        <v>12</v>
-      </c>
-      <c r="W66" t="n">
-        <v>19</v>
-      </c>
-      <c r="X66" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32361,76 +32377,76 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
       <c r="BT66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW66" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX66" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY66" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC66" t="n">
         <v>0</v>
       </c>
       <c r="CD66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE66" t="n">
         <v>0</v>
       </c>
       <c r="CF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -32454,7 +32470,7 @@
         <v>0</v>
       </c>
       <c r="CN66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO66" t="n">
         <v>0</v>
@@ -32466,19 +32482,19 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS66" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV66" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32487,67 +32503,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ66" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA66" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC66" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="DF66" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ66" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO66" t="n">
         <v>16</v>
       </c>
       <c r="DP66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32556,102 +32572,86 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX66" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB66" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC66" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED66" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr"/>
+      <c r="EB66" t="inlineStr"/>
+      <c r="EC66" t="inlineStr"/>
+      <c r="ED66" t="inlineStr"/>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -33511,7 +33511,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34463,7 +34463,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35870,10 +35870,10 @@
         <v>90</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF73" t="n">
         <v>0.8</v>
@@ -35903,7 +35903,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36350,10 +36350,10 @@
         <v>40</v>
       </c>
       <c r="DD74" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF74" t="n">
         <v>2.6</v>
@@ -36383,7 +36383,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36822,10 +36822,10 @@
         <v>60</v>
       </c>
       <c r="DD75" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF75" t="n">
         <v>2.4</v>
@@ -36855,7 +36855,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37774,10 +37774,10 @@
         <v>55</v>
       </c>
       <c r="DD77" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF77" t="n">
         <v>0.4</v>
@@ -37807,7 +37807,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38279,7 +38279,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38399,120 +38399,128 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>6</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>8</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
       <c r="U79" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W79" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y79" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z79" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF79" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK79" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -38521,10 +38529,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -38536,10 +38544,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -38548,13 +38556,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38569,19 +38577,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -38590,55 +38598,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT79" t="n">
         <v>4</v>
       </c>
-      <c r="BT79" t="n">
-        <v>6</v>
-      </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW79" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX79" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY79" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -38659,7 +38667,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38674,76 +38682,76 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA79" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC79" t="n">
         <v>80</v>
       </c>
-      <c r="DB79" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC79" t="n">
-        <v>60</v>
-      </c>
       <c r="DD79" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.75</v>
+        <v>0.13</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG79" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH79" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ79" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38764,102 +38772,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>9.869999999999999</v>
+        <v>14.67</v>
       </c>
       <c r="DX79" t="n">
-        <v>5.91</v>
+        <v>7.45</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -38879,128 +38887,120 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>7</v>
+      </c>
+      <c r="M80" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
         <v>8</v>
       </c>
-      <c r="M80" t="n">
-        <v>2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>6</v>
-      </c>
       <c r="R80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
+        <v>18</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>14</v>
+      </c>
+      <c r="X80" t="n">
         <v>21</v>
       </c>
-      <c r="V80" t="n">
-        <v>6</v>
-      </c>
-      <c r="W80" t="n">
-        <v>11</v>
-      </c>
-      <c r="X80" t="n">
-        <v>13</v>
-      </c>
       <c r="Y80" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z80" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -39009,10 +39009,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -39024,10 +39024,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -39036,13 +39036,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -39057,19 +39057,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -39078,55 +39078,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW80" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX80" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY80" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -39147,7 +39147,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -39162,76 +39162,76 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS80" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
         <v>13</v>
       </c>
-      <c r="CV80" t="n">
-        <v>11</v>
-      </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC80" t="n">
         <v>60</v>
       </c>
-      <c r="DA80" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC80" t="n">
+      <c r="DD80" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ80" t="n">
         <v>80</v>
       </c>
-      <c r="DD80" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>40</v>
-      </c>
       <c r="DK80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM80" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN80" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39252,102 +39252,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="n">
-        <v>14.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DX80" t="n">
-        <v>7.45</v>
+        <v>5.91</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="EC80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EJ80" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EK80" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL80" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EN80" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -39367,12 +39367,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -39388,119 +39388,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>19</v>
+      </c>
+      <c r="U81" t="n">
         <v>6</v>
       </c>
-      <c r="L81" t="n">
+      <c r="V81" t="n">
+        <v>24</v>
+      </c>
+      <c r="W81" t="n">
+        <v>8</v>
+      </c>
+      <c r="X81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
         <v>13</v>
       </c>
-      <c r="M81" t="n">
-        <v>2</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>4</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6</v>
-      </c>
-      <c r="S81" t="n">
-        <v>7</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3</v>
-      </c>
-      <c r="U81" t="n">
-        <v>11</v>
-      </c>
-      <c r="V81" t="n">
-        <v>9</v>
-      </c>
-      <c r="W81" t="n">
-        <v>15</v>
-      </c>
-      <c r="X81" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF81" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI81" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ81" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM81" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR81" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -39509,28 +39509,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -39542,13 +39542,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ81" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -39557,52 +39557,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW81" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX81" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY81" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ81" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -39635,88 +39635,88 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS81" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>22</v>
       </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
+      <c r="CY81" t="n">
         <v>4</v>
       </c>
-      <c r="CY81" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ81" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA81" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="DF81" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG81" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH81" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI81" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ81" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM81" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO81" t="n">
         <v>16</v>
@@ -39743,99 +39743,99 @@
         <v>0</v>
       </c>
       <c r="DW81" t="n">
-        <v>16.31</v>
+        <v>14.32</v>
       </c>
       <c r="DX81" t="n">
-        <v>5.04</v>
+        <v>1.76</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EM81" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN81" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EO81" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EP81" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -39855,12 +39855,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -39876,119 +39876,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
+        <v>13</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>11</v>
+      </c>
+      <c r="V82" t="n">
         <v>9</v>
       </c>
-      <c r="L82" t="n">
-        <v>12</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2</v>
-      </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
-        <v>4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>19</v>
-      </c>
-      <c r="U82" t="n">
-        <v>6</v>
-      </c>
-      <c r="V82" t="n">
-        <v>24</v>
-      </c>
       <c r="W82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X82" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y82" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z82" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE82" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF82" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL82" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM82" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ82" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR82" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -39997,28 +39997,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB82" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -40030,13 +40030,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -40045,52 +40045,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW82" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX82" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY82" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA82" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB82" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -40123,88 +40123,88 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW82" t="n">
         <v>1</v>
       </c>
       <c r="CX82" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ82" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="DE82" t="n">
-        <v>2.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF82" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG82" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH82" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI82" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ82" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL82" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO82" t="n">
         <v>16</v>
@@ -40231,99 +40231,99 @@
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>14.32</v>
+        <v>16.31</v>
       </c>
       <c r="DX82" t="n">
-        <v>1.76</v>
+        <v>5.04</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EJ82" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EK82" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EL82" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EN82" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EO82" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EP82" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -41183,7 +41183,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41641,7 +41641,7 @@
         <v>2.75</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -41671,7 +41671,7 @@
         <v>3.31</v>
       </c>
       <c r="DO85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -42121,7 +42121,7 @@
         <v>1.86</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF86" t="n">
         <v>1.8</v>
@@ -43070,10 +43070,10 @@
         <v>84</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF88" t="n">
         <v>0.33</v>
@@ -43103,7 +43103,7 @@
         <v>3.02</v>
       </c>
       <c r="DO88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43534,10 +43534,10 @@
         <v>42</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF89" t="n">
         <v>2.67</v>
@@ -43567,7 +43567,7 @@
         <v>3.26</v>
       </c>
       <c r="DO89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43998,7 +43998,7 @@
         <v>59</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE90" t="n">
         <v>1</v>
@@ -44462,7 +44462,7 @@
         <v>67</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE91" t="n">
         <v>1.13</v>
@@ -45455,7 +45455,7 @@
         <v>1.48</v>
       </c>
       <c r="DO93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -47871,7 +47871,7 @@
         <v>2.65</v>
       </c>
       <c r="DO98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -48313,7 +48313,7 @@
         <v>1.14</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF99" t="n">
         <v>1.33</v>
@@ -49273,7 +49273,7 @@
         <v>2.75</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DF101" t="n">
         <v>3</v>
@@ -49742,7 +49742,7 @@
         <v>71</v>
       </c>
       <c r="DD102" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE102" t="n">
         <v>1</v>
@@ -50222,10 +50222,10 @@
         <v>72</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF103" t="n">
         <v>2.71</v>
@@ -50255,7 +50255,7 @@
         <v>3.68</v>
       </c>
       <c r="DO103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50702,10 +50702,10 @@
         <v>62</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DF104" t="n">
         <v>2.57</v>
@@ -50735,7 +50735,7 @@
         <v>2.97</v>
       </c>
       <c r="DO104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -51174,7 +51174,7 @@
         <v>93</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DE105" t="n">
         <v>1.71</v>
@@ -51679,7 +51679,7 @@
         <v>2.48</v>
       </c>
       <c r="DO106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -53619,7 +53619,7 @@
         <v>1.85</v>
       </c>
       <c r="DO110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -54083,7 +54083,7 @@
         <v>3.24</v>
       </c>
       <c r="DO111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -54555,7 +54555,7 @@
         <v>2.12</v>
       </c>
       <c r="DO112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54652,6 +54652,1910 @@
       <c r="EP112" t="inlineStr">
         <is>
           <t>18.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>17</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>46039.5625</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" t="n">
+        <v>7</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" t="n">
+        <v>10</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>2</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>12</v>
+      </c>
+      <c r="R113" t="n">
+        <v>3</v>
+      </c>
+      <c r="S113" t="n">
+        <v>4</v>
+      </c>
+      <c r="T113" t="n">
+        <v>5</v>
+      </c>
+      <c r="U113" t="n">
+        <v>16</v>
+      </c>
+      <c r="V113" t="n">
+        <v>8</v>
+      </c>
+      <c r="W113" t="n">
+        <v>22</v>
+      </c>
+      <c r="X113" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>5138</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR113" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS113" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU113" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV113" t="n">
+        <v>22</v>
+      </c>
+      <c r="CW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX113" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY113" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ113" t="n">
+        <v>51</v>
+      </c>
+      <c r="DA113" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB113" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC113" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD113" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE113" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH113" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DI113" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DJ113" t="n">
+        <v>51</v>
+      </c>
+      <c r="DK113" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL113" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DM113" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DN113" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DO113" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW113" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DX113" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DY113" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="DZ113" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA113" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EB113" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC113" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED113" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EE113" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EF113" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EH113" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI113" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ113" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EK113" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EL113" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM113" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EN113" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EO113" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EP113" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>17</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>46040.625</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>4</v>
+      </c>
+      <c r="K114" t="n">
+        <v>6</v>
+      </c>
+      <c r="L114" t="n">
+        <v>10</v>
+      </c>
+      <c r="M114" t="n">
+        <v>5</v>
+      </c>
+      <c r="N114" t="n">
+        <v>4</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>5</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" t="n">
+        <v>7</v>
+      </c>
+      <c r="T114" t="n">
+        <v>6</v>
+      </c>
+      <c r="U114" t="n">
+        <v>12</v>
+      </c>
+      <c r="V114" t="n">
+        <v>7</v>
+      </c>
+      <c r="W114" t="n">
+        <v>26</v>
+      </c>
+      <c r="X114" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>74</v>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>AEL Arena</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>, Larissa</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>1106</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>26</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY114" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ114" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC114" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD114" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE114" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF114" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH114" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DI114" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ114" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK114" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL114" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM114" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN114" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DO114" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW114" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="DX114" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DY114" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="DZ114" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA114" t="inlineStr"/>
+      <c r="EB114" t="inlineStr"/>
+      <c r="EC114" t="inlineStr"/>
+      <c r="ED114" t="inlineStr"/>
+      <c r="EE114" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EH114" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI114" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EJ114" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="EK114" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL114" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EM114" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EN114" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EO114" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="EP114" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>17</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>46040.70833333334</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>3</v>
+      </c>
+      <c r="J115" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>6</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>5</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" t="n">
+        <v>7</v>
+      </c>
+      <c r="T115" t="n">
+        <v>2</v>
+      </c>
+      <c r="U115" t="n">
+        <v>12</v>
+      </c>
+      <c r="V115" t="n">
+        <v>3</v>
+      </c>
+      <c r="W115" t="n">
+        <v>14</v>
+      </c>
+      <c r="X115" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>68</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>32</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DN115" t="n">
+        <v>3</v>
+      </c>
+      <c r="DO115" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="DX115" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="DZ115" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr"/>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH115" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN115" t="inlineStr">
+        <is>
+          <t>8.12</t>
+        </is>
+      </c>
+      <c r="EO115" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EP115" t="inlineStr">
+        <is>
+          <t>14.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>17</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46040.79166666666</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>3</v>
+      </c>
+      <c r="S116" t="n">
+        <v>7</v>
+      </c>
+      <c r="T116" t="n">
+        <v>9</v>
+      </c>
+      <c r="U116" t="n">
+        <v>12</v>
+      </c>
+      <c r="V116" t="n">
+        <v>12</v>
+      </c>
+      <c r="W116" t="n">
+        <v>17</v>
+      </c>
+      <c r="X116" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>1101</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>68</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="DO116" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW116" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="DX116" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="DZ116" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EH116" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EJ116" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EL116" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM116" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EN116" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EO116" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP116" t="inlineStr">
+        <is>
+          <t>4.48</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP116" headerRowCount="1">
-  <autoFilter ref="A1:EP116"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP118" headerRowCount="1">
+  <autoFilter ref="A1:EP118"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP116"/>
+  <dimension ref="A1:EP118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2746,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE8" t="n">
         <v>2.13</v>
@@ -5643,7 +5643,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7053,7 +7053,7 @@
         <v>2.78</v>
       </c>
       <c r="DE13" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -7083,7 +7083,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7541,7 +7541,7 @@
         <v>2.13</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -8208,19 +8208,19 @@
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -8229,98 +8229,98 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U16" t="n">
         <v>7</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="Z16" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AM16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AU16" t="n">
         <v>3</v>
@@ -8329,22 +8329,22 @@
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>5131</v>
+        <v>5199</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8368,61 +8368,61 @@
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ16" t="n">
         <v>1</v>
       </c>
       <c r="BR16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BT16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW16" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="BX16" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BY16" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8470,46 +8470,46 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY16" t="n">
         <v>7</v>
       </c>
-      <c r="CY16" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ16" t="n">
         <v>0</v>
       </c>
       <c r="DA16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8521,25 +8521,25 @@
         <v>1.5</v>
       </c>
       <c r="DI16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8563,14 +8563,14 @@
         <v>1</v>
       </c>
       <c r="DW16" t="n">
-        <v>29.9</v>
+        <v>35.99</v>
       </c>
       <c r="DX16" t="n">
-        <v>6.93</v>
+        <v>5.68</v>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8582,72 +8582,64 @@
       <c r="EB16" t="inlineStr"/>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.89</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8659,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8688,119 +8680,119 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
         <v>7</v>
       </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
         <v>5</v>
       </c>
-      <c r="N17" t="n">
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z17" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" t="n">
         <v>2.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AR17" t="n">
         <v>3.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
@@ -8809,22 +8801,22 @@
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5199</v>
+        <v>5131</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8848,61 +8840,61 @@
         <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ17" t="n">
         <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW17" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="BX17" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="BY17" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="CB17" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8938,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8950,46 +8942,46 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CS17" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
         <v>17</v>
       </c>
-      <c r="CT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>16</v>
-      </c>
       <c r="CV17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
       </c>
       <c r="DA17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
       </c>
       <c r="DC17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9001,25 +8993,25 @@
         <v>1.5</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DJ17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9043,14 +9035,14 @@
         <v>1</v>
       </c>
       <c r="DW17" t="n">
-        <v>35.99</v>
+        <v>29.9</v>
       </c>
       <c r="DX17" t="n">
-        <v>5.68</v>
+        <v>6.93</v>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9062,64 +9054,72 @@
       <c r="EB17" t="inlineStr"/>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr"/>
-      <c r="EH17" t="inlineStr"/>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -9139,37 +9139,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -9181,122 +9181,122 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
         <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Stadio Theodoros Kolokotronis</t>
+          <t>Dimotiko Stadio Neapolis Volou</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Liagora, Tripoli</t>
+          <t>Efstratios Argenti, Volos</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.2</v>
+        <v>4.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>-1</v>
+        <v>5168</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9317,134 +9317,134 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY18" t="n">
         <v>6</v>
       </c>
-      <c r="BU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ18" t="n">
         <v>0</v>
       </c>
@@ -9458,10 +9458,10 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9470,25 +9470,25 @@
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
         <v>16</v>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
@@ -9515,14 +9515,14 @@
         <v>1</v>
       </c>
       <c r="DW18" t="n">
-        <v>27.55</v>
+        <v>29.47</v>
       </c>
       <c r="DX18" t="n">
-        <v>3.1</v>
+        <v>6.76</v>
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ18" t="inlineStr">
@@ -9532,74 +9532,50 @@
       </c>
       <c r="EA18" t="inlineStr"/>
       <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EE18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EF18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EH18" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+      <c r="EC18" t="inlineStr"/>
+      <c r="ED18" t="inlineStr"/>
+      <c r="EE18" t="inlineStr"/>
+      <c r="EF18" t="inlineStr"/>
+      <c r="EG18" t="inlineStr"/>
+      <c r="EH18" t="inlineStr"/>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EM18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EN18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EO18" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -9619,37 +9595,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
-        <v>9</v>
-      </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -9661,122 +9637,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
+        <v>16</v>
+      </c>
+      <c r="W19" t="n">
         <v>12</v>
       </c>
-      <c r="W19" t="n">
-        <v>22</v>
-      </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Dimotiko Stadio Neapolis Volou</t>
+          <t>Stadio Theodoros Kolokotronis</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Efstratios Argenti, Volos</t>
+          <t>Liagora, Tripoli</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS19" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5168</v>
+        <v>-1</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9797,64 +9773,64 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BW19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BX19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BY19" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9881,7 +9857,7 @@
         <v>1</v>
       </c>
       <c r="CK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -9902,28 +9878,28 @@
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ19" t="n">
         <v>0</v>
@@ -9938,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9950,25 +9926,25 @@
         <v>0</v>
       </c>
       <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
         <v>0.5</v>
       </c>
-      <c r="DI19" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DN19" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="DO19" t="n">
         <v>16</v>
@@ -9986,7 +9962,7 @@
         <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
@@ -9995,14 +9971,14 @@
         <v>1</v>
       </c>
       <c r="DW19" t="n">
-        <v>29.47</v>
+        <v>27.55</v>
       </c>
       <c r="DX19" t="n">
-        <v>6.76</v>
+        <v>3.1</v>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
@@ -10012,50 +9988,74 @@
       </c>
       <c r="EA19" t="inlineStr"/>
       <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
-      <c r="ED19" t="inlineStr"/>
-      <c r="EE19" t="inlineStr"/>
-      <c r="EF19" t="inlineStr"/>
-      <c r="EG19" t="inlineStr"/>
-      <c r="EH19" t="inlineStr"/>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EM19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EO19" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EP19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11051,162 +11051,170 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" t="n">
         <v>15</v>
       </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
       <c r="W22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.64</v>
+        <v>2.21</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ22" t="n">
         <v>1</v>
       </c>
       <c r="BA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>-1</v>
+        <v>5131</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -11221,40 +11229,40 @@
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL22" t="n">
         <v>4</v>
       </c>
       <c r="BM22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
       </c>
       <c r="BQ22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR22" t="n">
         <v>2</v>
       </c>
       <c r="BS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
@@ -11263,22 +11271,22 @@
         <v>41</v>
       </c>
       <c r="BW22" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="BX22" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.38</v>
+        <v>0.68</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -11311,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -11326,82 +11334,82 @@
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CW22" t="n">
         <v>1</v>
       </c>
       <c r="CX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY22" t="n">
         <v>6</v>
       </c>
-      <c r="CY22" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DB22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DF22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="DI22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DJ22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DL22" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="DM22" t="n">
-        <v>0.82</v>
+        <v>1.31</v>
       </c>
       <c r="DN22" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
       </c>
       <c r="DQ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR22" t="b">
         <v>0</v>
@@ -11416,17 +11424,17 @@
         <v>0</v>
       </c>
       <c r="DV22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW22" t="n">
-        <v>29.14</v>
+        <v>26.11</v>
       </c>
       <c r="DX22" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
@@ -11434,76 +11442,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA22" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="EB22" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr"/>
       <c r="EC22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="ED22" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr"/>
-      <c r="EH22" t="inlineStr"/>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EI22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EJ22" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EL22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EN22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EO22" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EP22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -11523,170 +11531,162 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>15</v>
+      </c>
+      <c r="V23" t="n">
         <v>11</v>
       </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>15</v>
-      </c>
       <c r="W23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Z23" t="n">
-        <v>71</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Stadio Panetolikou</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Nikitara, Agrinio</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD23" t="n">
         <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB23" t="n">
-        <v>5131</v>
+        <v>-1</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11701,40 +11701,40 @@
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL23" t="n">
         <v>4</v>
       </c>
       <c r="BM23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT23" t="n">
         <v>5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>3</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
@@ -11743,22 +11743,22 @@
         <v>41</v>
       </c>
       <c r="BW23" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="BX23" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY23" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11791,10 +11791,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11806,73 +11806,73 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CV23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
       </c>
       <c r="CX23" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY23" t="n">
         <v>10</v>
       </c>
-      <c r="CY23" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ23" t="n">
         <v>100</v>
       </c>
-      <c r="DA23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="DF23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DI23" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ23" t="n">
-        <v>0</v>
-      </c>
       <c r="DK23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="DL23" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="DM23" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="DN23" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="DO23" t="n">
         <v>17</v>
@@ -11881,7 +11881,7 @@
         <v>1</v>
       </c>
       <c r="DQ23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR23" t="b">
         <v>0</v>
@@ -11896,17 +11896,17 @@
         <v>0</v>
       </c>
       <c r="DV23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW23" t="n">
-        <v>26.11</v>
+        <v>29.14</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.6</v>
+        <v>4</v>
       </c>
       <c r="DY23" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="DZ23" t="inlineStr">
@@ -11914,76 +11914,76 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA23" t="inlineStr"/>
-      <c r="EB23" t="inlineStr"/>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EC23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="ED23" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EH23" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr"/>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EL23" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EN23" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EO23" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EP23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE24" t="n">
         <v>0.5600000000000001</v>
@@ -12823,7 +12823,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -14713,7 +14713,7 @@
         <v>2.75</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -15671,7 +15671,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -17086,7 +17086,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -19055,7 +19055,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19175,170 +19175,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
         <v>6</v>
       </c>
       <c r="U39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W39" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="X39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Stadio Levadias</t>
+          <t>Stadio Zirinio</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Agion Theodoron, Levadia</t>
+          <t>Kifissia, Athens</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU39" t="n">
         <v>5</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>6</v>
-      </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ39" t="n">
         <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB39" t="n">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19353,13 +19353,13 @@
         <v>1</v>
       </c>
       <c r="BI39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL39" t="n">
         <v>0</v>
@@ -19368,61 +19368,61 @@
         <v>5</v>
       </c>
       <c r="BN39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="n">
         <v>2</v>
       </c>
       <c r="BS39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BT39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY39" t="n">
         <v>77</v>
       </c>
-      <c r="BW39" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>137</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>57</v>
-      </c>
       <c r="BZ39" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="CB39" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="CC39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CD39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG39" t="n">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ39" t="n">
         <v>1</v>
@@ -19461,46 +19461,46 @@
         <v>17</v>
       </c>
       <c r="CS39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV39" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY39" t="n">
         <v>10</v>
       </c>
-      <c r="CY39" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DA39" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="DB39" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DC39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.11</v>
+        <v>1.13</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DF39" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG39" t="n">
         <v>2</v>
@@ -19509,25 +19509,25 @@
         <v>1.4</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ39" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="DK39" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.58</v>
+        <v>0.87</v>
       </c>
       <c r="DM39" t="n">
-        <v>0.76</v>
+        <v>2.14</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19545,20 +19545,20 @@
         <v>1</v>
       </c>
       <c r="DU39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>19.8</v>
+        <v>20.41</v>
       </c>
       <c r="DX39" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19568,82 +19568,82 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.41</t>
         </is>
       </c>
     </row>
@@ -19663,170 +19663,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45935.625</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
+        <v>10</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
         <v>7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>9</v>
       </c>
       <c r="T40" t="n">
         <v>6</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>11</v>
+      </c>
+      <c r="X40" t="n">
         <v>9</v>
       </c>
-      <c r="W40" t="n">
-        <v>20</v>
-      </c>
-      <c r="X40" t="n">
-        <v>18</v>
-      </c>
       <c r="Y40" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="Z40" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Stadio Zirinio</t>
+          <t>Stadio Levadias</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Kifissia, Athens</t>
+          <t>Agion Theodoron, Levadia</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="n">
-        <v>8.08</v>
+        <v>1.67</v>
       </c>
       <c r="AF40" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
         <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19841,13 +19841,13 @@
         <v>1</v>
       </c>
       <c r="BI40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL40" t="n">
         <v>0</v>
@@ -19856,61 +19856,61 @@
         <v>5</v>
       </c>
       <c r="BN40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BQ40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR40" t="n">
         <v>2</v>
       </c>
       <c r="BS40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BT40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="BW40" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY40" t="n">
         <v>57</v>
       </c>
-      <c r="BX40" t="n">
-        <v>73</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>77</v>
-      </c>
       <c r="BZ40" t="n">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CC40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG40" t="n">
         <v>0</v>
@@ -19931,7 +19931,7 @@
         <v>0</v>
       </c>
       <c r="CM40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
@@ -19940,7 +19940,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ40" t="n">
         <v>1</v>
@@ -19949,46 +19949,46 @@
         <v>17</v>
       </c>
       <c r="CS40" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB40" t="n">
         <v>17</v>
       </c>
-      <c r="CV40" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY40" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ40" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA40" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB40" t="n">
-        <v>25</v>
-      </c>
       <c r="DC40" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="DD40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE40" t="n">
         <v>1.13</v>
       </c>
-      <c r="DE40" t="n">
-        <v>2.13</v>
-      </c>
       <c r="DF40" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG40" t="n">
         <v>2</v>
@@ -19997,22 +19997,22 @@
         <v>1.4</v>
       </c>
       <c r="DI40" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="DJ40" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="DK40" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DL40" t="n">
-        <v>0.87</v>
+        <v>1.58</v>
       </c>
       <c r="DM40" t="n">
-        <v>2.14</v>
+        <v>0.76</v>
       </c>
       <c r="DN40" t="n">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="DO40" t="n">
         <v>17</v>
@@ -20033,20 +20033,20 @@
         <v>1</v>
       </c>
       <c r="DU40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW40" t="n">
-        <v>20.41</v>
+        <v>19.8</v>
       </c>
       <c r="DX40" t="n">
-        <v>3.34</v>
+        <v>2.29</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -20056,82 +20056,82 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>5.77</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
         <v>2.13</v>
       </c>
       <c r="DE42" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -21913,7 +21913,7 @@
         <v>0.63</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21943,7 +21943,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22398,7 +22398,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE45" t="n">
         <v>0.75</v>
@@ -23374,7 +23374,7 @@
         <v>59</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE47" t="n">
         <v>0.13</v>
@@ -23407,7 +23407,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -24839,7 +24839,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25761,7 +25761,7 @@
         <v>1.13</v>
       </c>
       <c r="DE52" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -26279,7 +26279,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -27247,7 +27247,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -28174,7 +28174,7 @@
         <v>84</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -28695,7 +28695,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29641,7 +29641,7 @@
         <v>0.78</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF60" t="n">
         <v>0.5</v>
@@ -29671,7 +29671,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30607,7 +30607,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31550,7 +31550,7 @@
         <v>75</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE64" t="n">
         <v>0.75</v>
@@ -31583,7 +31583,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31719,162 +31719,170 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="n">
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>8</v>
+      </c>
+      <c r="S65" t="n">
         <v>6</v>
       </c>
-      <c r="L65" t="n">
+      <c r="T65" t="n">
         <v>10</v>
       </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
+        <v>9</v>
+      </c>
+      <c r="V65" t="n">
+        <v>18</v>
+      </c>
+      <c r="W65" t="n">
+        <v>14</v>
+      </c>
+      <c r="X65" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU65" t="n">
         <v>4</v>
       </c>
-      <c r="S65" t="n">
-        <v>4</v>
-      </c>
-      <c r="T65" t="n">
-        <v>8</v>
-      </c>
-      <c r="U65" t="n">
-        <v>6</v>
-      </c>
-      <c r="V65" t="n">
-        <v>12</v>
-      </c>
-      <c r="W65" t="n">
-        <v>19</v>
-      </c>
-      <c r="X65" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -31889,76 +31897,76 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS65" t="n">
         <v>4</v>
       </c>
-      <c r="BN65" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>2</v>
-      </c>
       <c r="BT65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW65" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX65" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY65" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC65" t="n">
         <v>0</v>
       </c>
       <c r="CD65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE65" t="n">
         <v>0</v>
       </c>
       <c r="CF65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG65" t="n">
         <v>0</v>
@@ -31982,7 +31990,7 @@
         <v>0</v>
       </c>
       <c r="CN65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO65" t="n">
         <v>0</v>
@@ -31994,19 +32002,19 @@
         <v>1</v>
       </c>
       <c r="CR65" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS65" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV65" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -32015,67 +32023,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ65" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA65" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="DF65" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ65" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK65" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM65" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO65" t="n">
         <v>16</v>
       </c>
       <c r="DP65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -32084,102 +32092,86 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW65" t="n">
-        <v>18.44</v>
+        <v>20.82</v>
       </c>
       <c r="DX65" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="DZ65" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EB65" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC65" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="ED65" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr"/>
+      <c r="EB65" t="inlineStr"/>
+      <c r="EC65" t="inlineStr"/>
+      <c r="ED65" t="inlineStr"/>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EM65" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EO65" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EP65" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -32199,170 +32191,162 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>4</v>
       </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" t="n">
+        <v>6</v>
+      </c>
+      <c r="L66" t="n">
         <v>10</v>
       </c>
-      <c r="L66" t="n">
-        <v>11</v>
-      </c>
       <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
         <v>4</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
         <v>8</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>9</v>
-      </c>
       <c r="V66" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y66" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE66" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF66" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN66" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO66" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -32377,124 +32361,124 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN66" t="n">
         <v>6</v>
       </c>
-      <c r="BN66" t="n">
+      <c r="BO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
         <v>5</v>
       </c>
-      <c r="BO66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>0</v>
-      </c>
       <c r="BS66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS66" t="n">
         <v>23</v>
       </c>
-      <c r="BW66" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>30</v>
-      </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -32503,67 +32487,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ66" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA66" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="DE66" t="n">
-        <v>2.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DF66" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ66" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
         <v>16</v>
       </c>
       <c r="DP66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -32572,86 +32556,102 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>20.82</v>
+        <v>18.44</v>
       </c>
       <c r="DX66" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EA66" t="inlineStr"/>
-      <c r="EB66" t="inlineStr"/>
-      <c r="EC66" t="inlineStr"/>
-      <c r="ED66" t="inlineStr"/>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EM66" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EO66" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP66" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -33023,7 +33023,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33991,7 +33991,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -35393,7 +35393,7 @@
         <v>2.75</v>
       </c>
       <c r="DE72" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF72" t="n">
         <v>3</v>
@@ -37294,10 +37294,10 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF76" t="n">
         <v>2.25</v>
@@ -37327,7 +37327,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -38399,128 +38399,120 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" t="n">
         <v>4</v>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>6</v>
-      </c>
       <c r="R79" t="n">
         <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
+        <v>18</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>14</v>
+      </c>
+      <c r="X79" t="n">
         <v>21</v>
       </c>
-      <c r="V79" t="n">
-        <v>6</v>
-      </c>
-      <c r="W79" t="n">
-        <v>11</v>
-      </c>
-      <c r="X79" t="n">
-        <v>13</v>
-      </c>
       <c r="Y79" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z79" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -38529,10 +38521,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -38544,10 +38536,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -38556,13 +38548,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38577,19 +38569,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -38598,55 +38590,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW79" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX79" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY79" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -38667,7 +38659,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38682,73 +38674,73 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS79" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
         <v>13</v>
       </c>
-      <c r="CV79" t="n">
-        <v>11</v>
-      </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC79" t="n">
         <v>60</v>
       </c>
-      <c r="DA79" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB79" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC79" t="n">
+      <c r="DD79" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ79" t="n">
         <v>80</v>
       </c>
-      <c r="DD79" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>40</v>
-      </c>
       <c r="DK79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM79" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN79" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO79" t="n">
         <v>17</v>
@@ -38772,102 +38764,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>14.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DX79" t="n">
-        <v>7.45</v>
+        <v>5.91</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="EC79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EJ79" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EK79" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL79" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -38887,120 +38879,128 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>6</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>8</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
       <c r="U80" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y80" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z80" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF80" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK80" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -39009,10 +39009,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -39024,10 +39024,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -39036,13 +39036,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -39057,19 +39057,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -39078,55 +39078,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT80" t="n">
         <v>4</v>
       </c>
-      <c r="BT80" t="n">
-        <v>6</v>
-      </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW80" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX80" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY80" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -39147,7 +39147,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -39162,73 +39162,73 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV80" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA80" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC80" t="n">
         <v>80</v>
       </c>
-      <c r="DB80" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>60</v>
-      </c>
       <c r="DD80" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.75</v>
+        <v>0.13</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG80" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH80" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ80" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN80" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO80" t="n">
         <v>17</v>
@@ -39252,102 +39252,102 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="n">
-        <v>9.869999999999999</v>
+        <v>14.67</v>
       </c>
       <c r="DX80" t="n">
-        <v>5.91</v>
+        <v>7.45</v>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EM80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EN80" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EO80" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EP80" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -39686,7 +39686,7 @@
         <v>70</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE81" t="n">
         <v>2.13</v>
@@ -40695,7 +40695,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -42118,7 +42118,7 @@
         <v>74</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE86" t="n">
         <v>1.11</v>
@@ -42151,7 +42151,7 @@
         <v>3.01</v>
       </c>
       <c r="DO86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42593,7 +42593,7 @@
         <v>1.14</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF87" t="n">
         <v>1.4</v>
@@ -44001,7 +44001,7 @@
         <v>2.67</v>
       </c>
       <c r="DE90" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF90" t="n">
         <v>2.5</v>
@@ -44031,7 +44031,7 @@
         <v>2.86</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44495,7 +44495,7 @@
         <v>1.9</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44967,7 +44967,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -46382,7 +46382,7 @@
         <v>59</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DE95" t="n">
         <v>2.13</v>
@@ -46415,7 +46415,7 @@
         <v>2.56</v>
       </c>
       <c r="DO95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46903,7 +46903,7 @@
         <v>2.92</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -48782,7 +48782,7 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="DE100" t="n">
         <v>1.13</v>
@@ -48815,7 +48815,7 @@
         <v>2.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -49745,7 +49745,7 @@
         <v>0.78</v>
       </c>
       <c r="DE102" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF102" t="n">
         <v>0.43</v>
@@ -49775,7 +49775,7 @@
         <v>2.15</v>
       </c>
       <c r="DO102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -51177,7 +51177,7 @@
         <v>0.78</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DF105" t="n">
         <v>0.57</v>
@@ -51207,7 +51207,7 @@
         <v>2.24</v>
       </c>
       <c r="DO105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51815,12 +51815,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
@@ -51830,25 +51830,25 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M107" t="n">
         <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -51857,107 +51857,107 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="U107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V107" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W107" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X107" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y107" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Z107" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC107" t="n">
         <v>3</v>
       </c>
       <c r="AD107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE107" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AF107" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AG107" t="n">
         <v>1.33</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ107" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AN107" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="AO107" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AR107" t="n">
         <v>2.45</v>
       </c>
       <c r="AS107" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV107" t="n">
         <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX107" t="n">
         <v>0</v>
@@ -51969,10 +51969,10 @@
         <v>1</v>
       </c>
       <c r="BA107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB107" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
@@ -51984,7 +51984,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>2818</v>
+        <v>1843</v>
       </c>
       <c r="BG107" t="n">
         <v>2</v>
@@ -51993,37 +51993,37 @@
         <v>1</v>
       </c>
       <c r="BI107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ107" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM107" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BN107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BO107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP107" t="n">
         <v>0</v>
       </c>
       <c r="BQ107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT107" t="n">
         <v>3</v>
@@ -52032,25 +52032,25 @@
         <v>1</v>
       </c>
       <c r="BV107" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BW107" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="BX107" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="BY107" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BZ107" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="CA107" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="CB107" t="n">
-        <v>2.02</v>
+        <v>2.87</v>
       </c>
       <c r="CC107" t="n">
         <v>0</v>
@@ -52086,7 +52086,7 @@
         <v>0</v>
       </c>
       <c r="CN107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO107" t="n">
         <v>0</v>
@@ -52098,76 +52098,76 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CS107" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="CT107" t="n">
         <v>1</v>
       </c>
       <c r="CU107" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CV107" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW107" t="n">
         <v>1</v>
       </c>
       <c r="CX107" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CY107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ107" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="DA107" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="DB107" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="DC107" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DE107" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF107" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="DG107" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH107" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="DI107" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DJ107" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="DK107" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="DL107" t="n">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="DM107" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="DN107" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="DO107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -52176,7 +52176,7 @@
         <v>1</v>
       </c>
       <c r="DR107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS107" t="b">
         <v>0</v>
@@ -52191,87 +52191,99 @@
         <v>0</v>
       </c>
       <c r="DW107" t="n">
-        <v>14.86</v>
+        <v>13.04</v>
       </c>
       <c r="DX107" t="n">
-        <v>12.78</v>
+        <v>7.34</v>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="ED107" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EG107" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EI107" t="inlineStr"/>
-      <c r="EJ107" t="inlineStr"/>
-      <c r="EK107" t="inlineStr"/>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EM107" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN107" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="EO107" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="EP107" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
     </row>
@@ -52291,12 +52303,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
@@ -52306,25 +52318,25 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
         <v>5</v>
       </c>
-      <c r="K108" t="n">
-        <v>8</v>
-      </c>
       <c r="L108" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M108" t="n">
         <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -52333,107 +52345,107 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T108" t="n">
+        <v>4</v>
+      </c>
+      <c r="U108" t="n">
+        <v>4</v>
+      </c>
+      <c r="V108" t="n">
+        <v>9</v>
+      </c>
+      <c r="W108" t="n">
+        <v>16</v>
+      </c>
+      <c r="X108" t="n">
         <v>15</v>
       </c>
-      <c r="U108" t="n">
-        <v>2</v>
-      </c>
-      <c r="V108" t="n">
-        <v>23</v>
-      </c>
-      <c r="W108" t="n">
-        <v>14</v>
-      </c>
-      <c r="X108" t="n">
-        <v>13</v>
-      </c>
       <c r="Y108" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Z108" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC108" t="n">
         <v>3</v>
       </c>
       <c r="AD108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE108" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AF108" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AG108" t="n">
         <v>1.33</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="AO108" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR108" t="n">
         <v>2.45</v>
       </c>
       <c r="AS108" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AU108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
         <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX108" t="n">
         <v>0</v>
@@ -52445,10 +52457,10 @@
         <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -52460,7 +52472,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>1843</v>
+        <v>2818</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -52469,37 +52481,37 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL108" t="n">
         <v>4</v>
       </c>
-      <c r="BJ108" t="n">
+      <c r="BM108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN108" t="n">
         <v>6</v>
       </c>
-      <c r="BK108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM108" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN108" t="n">
-        <v>3</v>
-      </c>
       <c r="BO108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP108" t="n">
         <v>0</v>
       </c>
       <c r="BQ108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT108" t="n">
         <v>3</v>
@@ -52508,25 +52520,25 @@
         <v>1</v>
       </c>
       <c r="BV108" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BW108" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="BX108" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="BY108" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BZ108" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="CA108" t="n">
-        <v>2.44</v>
+        <v>1.47</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.87</v>
+        <v>2.02</v>
       </c>
       <c r="CC108" t="n">
         <v>0</v>
@@ -52562,7 +52574,7 @@
         <v>0</v>
       </c>
       <c r="CN108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO108" t="n">
         <v>0</v>
@@ -52574,73 +52586,73 @@
         <v>1</v>
       </c>
       <c r="CR108" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CS108" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
         <v>15</v>
       </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>13</v>
-      </c>
       <c r="CV108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CY108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ108" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA108" t="n">
         <v>71</v>
       </c>
-      <c r="DA108" t="n">
-        <v>93</v>
-      </c>
       <c r="DB108" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="DC108" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="DD108" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="DE108" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DF108" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="DG108" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DH108" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="DI108" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DJ108" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK108" t="n">
         <v>29</v>
       </c>
-      <c r="DK108" t="n">
-        <v>7</v>
-      </c>
       <c r="DL108" t="n">
-        <v>0.88</v>
+        <v>1.35</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="DO108" t="n">
         <v>16</v>
@@ -52652,7 +52664,7 @@
         <v>1</v>
       </c>
       <c r="DR108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS108" t="b">
         <v>0</v>
@@ -52667,99 +52679,87 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>13.04</v>
+        <v>14.86</v>
       </c>
       <c r="DX108" t="n">
-        <v>7.34</v>
+        <v>12.78</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED108" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG108" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EI108" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EJ108" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EK108" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr"/>
+      <c r="EJ108" t="inlineStr"/>
+      <c r="EK108" t="inlineStr"/>
       <c r="EL108" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EM108" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EN108" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="EO108" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="EP108" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
         <v>2.86</v>
       </c>
       <c r="DO109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -54832,7 +54832,7 @@
         <v>0</v>
       </c>
       <c r="BF113" t="n">
-        <v>-1</v>
+        <v>643</v>
       </c>
       <c r="BG113" t="n">
         <v>2</v>
@@ -55320,7 +55320,7 @@
         <v>0</v>
       </c>
       <c r="BF114" t="n">
-        <v>-1</v>
+        <v>6048</v>
       </c>
       <c r="BG114" t="n">
         <v>2</v>
@@ -55665,7 +55665,7 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R115" t="n">
         <v>1</v>
@@ -55677,7 +55677,7 @@
         <v>2</v>
       </c>
       <c r="U115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V115" t="n">
         <v>3</v>
@@ -55689,10 +55689,10 @@
         <v>8</v>
       </c>
       <c r="Y115" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z115" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr"/>
@@ -55784,7 +55784,7 @@
         <v>0</v>
       </c>
       <c r="BF115" t="n">
-        <v>-1</v>
+        <v>12816</v>
       </c>
       <c r="BG115" t="n">
         <v>2</v>
@@ -55844,13 +55844,13 @@
         <v>80</v>
       </c>
       <c r="BZ115" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="CA115" t="n">
         <v>0.44</v>
       </c>
       <c r="CB115" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -56256,7 +56256,7 @@
         <v>0</v>
       </c>
       <c r="BF116" t="n">
-        <v>-1</v>
+        <v>30921</v>
       </c>
       <c r="BG116" t="n">
         <v>2</v>
@@ -56556,6 +56556,966 @@
       <c r="EP116" t="inlineStr">
         <is>
           <t>4.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>17</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>46041.66666666666</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3</v>
+      </c>
+      <c r="I117" t="n">
+        <v>4</v>
+      </c>
+      <c r="J117" t="n">
+        <v>6</v>
+      </c>
+      <c r="K117" t="n">
+        <v>5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>11</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>3</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6</v>
+      </c>
+      <c r="S117" t="n">
+        <v>13</v>
+      </c>
+      <c r="T117" t="n">
+        <v>5</v>
+      </c>
+      <c r="U117" t="n">
+        <v>16</v>
+      </c>
+      <c r="V117" t="n">
+        <v>11</v>
+      </c>
+      <c r="W117" t="n">
+        <v>14</v>
+      </c>
+      <c r="X117" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>1108</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU117" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV117" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY117" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ117" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA117" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB117" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC117" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD117" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE117" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DF117" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG117" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DH117" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DI117" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DJ117" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK117" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL117" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DM117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN117" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO117" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW117" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="DX117" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="DZ117" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA117" t="inlineStr"/>
+      <c r="EB117" t="inlineStr"/>
+      <c r="EC117" t="inlineStr"/>
+      <c r="ED117" t="inlineStr"/>
+      <c r="EE117" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL117" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM117" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EN117" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EO117" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="EP117" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>17</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46041.75</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" t="n">
+        <v>3</v>
+      </c>
+      <c r="J118" t="n">
+        <v>3</v>
+      </c>
+      <c r="K118" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" t="n">
+        <v>7</v>
+      </c>
+      <c r="M118" t="n">
+        <v>6</v>
+      </c>
+      <c r="N118" t="n">
+        <v>3</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>9</v>
+      </c>
+      <c r="S118" t="n">
+        <v>6</v>
+      </c>
+      <c r="T118" t="n">
+        <v>6</v>
+      </c>
+      <c r="U118" t="n">
+        <v>7</v>
+      </c>
+      <c r="V118" t="n">
+        <v>15</v>
+      </c>
+      <c r="W118" t="n">
+        <v>15</v>
+      </c>
+      <c r="X118" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Dimotiko Stadio Neapolis Volou</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Efstratios Argenti, Volos</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1109</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW118" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="DX118" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED118" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EL118" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM118" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EN118" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EO118" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP118" t="inlineStr">
+        <is>
+          <t>3.87</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -56744,7 +56744,7 @@
         <v>0</v>
       </c>
       <c r="BF117" t="n">
-        <v>-1</v>
+        <v>1518</v>
       </c>
       <c r="BG117" t="n">
         <v>2</v>
@@ -57216,7 +57216,7 @@
         <v>0</v>
       </c>
       <c r="BF118" t="n">
-        <v>-1</v>
+        <v>134</v>
       </c>
       <c r="BG118" t="n">
         <v>2</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -57704,7 +57704,7 @@
         <v>0</v>
       </c>
       <c r="BF119" t="n">
-        <v>-1</v>
+        <v>27777</v>
       </c>
       <c r="BG119" t="n">
         <v>2</v>
@@ -58081,10 +58081,10 @@
         <v>18</v>
       </c>
       <c r="Y120" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z120" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="BF120" t="n">
-        <v>-1</v>
+        <v>4073</v>
       </c>
       <c r="BG120" t="n">
         <v>2</v>
@@ -58672,7 +58672,7 @@
         <v>0</v>
       </c>
       <c r="BF121" t="n">
-        <v>-1</v>
+        <v>4369</v>
       </c>
       <c r="BG121" t="n">
         <v>2</v>
@@ -59152,7 +59152,7 @@
         <v>0</v>
       </c>
       <c r="BF122" t="n">
-        <v>-1</v>
+        <v>3790</v>
       </c>
       <c r="BG122" t="n">
         <v>2</v>
@@ -59640,7 +59640,7 @@
         <v>0</v>
       </c>
       <c r="BF123" t="n">
-        <v>-1</v>
+        <v>6387</v>
       </c>
       <c r="BG123" t="n">
         <v>2</v>
@@ -60128,7 +60128,7 @@
         <v>0</v>
       </c>
       <c r="BF124" t="n">
-        <v>-1</v>
+        <v>1600</v>
       </c>
       <c r="BG124" t="n">
         <v>2</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL124" headerRowCount="1">
-  <autoFilter ref="A1:EL124"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL131" headerRowCount="1">
+  <autoFilter ref="A1:EL131"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL124"/>
+  <dimension ref="A1:EL131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>2.78</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE4" t="n">
         <v>1.22</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3134,10 +3134,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3590,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4054,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4526,10 +4526,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE8" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4993,7 +4993,7 @@
         <v>0.78</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5487,7 +5487,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5921,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5951,7 +5951,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6382,10 +6382,10 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6415,7 +6415,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6846,7 +6846,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE13" t="n">
         <v>1.22</v>
@@ -6879,7 +6879,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7318,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE14" t="n">
         <v>1.78</v>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7793,7 +7793,7 @@
         <v>2.78</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
@@ -7823,7 +7823,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8254,10 +8254,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8718,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE17" t="n">
         <v>1.2</v>
@@ -8751,7 +8751,7 @@
         <v>2.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9177,7 +9177,7 @@
         <v>1</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9207,7 +9207,7 @@
         <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9671,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10078,7 +10078,7 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE20" t="n">
         <v>2.22</v>
@@ -10111,7 +10111,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10583,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11047,7 +11047,7 @@
         <v>2.09</v>
       </c>
       <c r="DO22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11481,7 +11481,7 @@
         <v>1.13</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11511,7 +11511,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11942,10 +11942,10 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11975,7 +11975,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12394,7 +12394,7 @@
         <v>0</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE25" t="n">
         <v>1</v>
@@ -12427,7 +12427,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -12883,7 +12883,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13322,10 +13322,10 @@
         <v>25</v>
       </c>
       <c r="DD27" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13355,7 +13355,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13778,10 +13778,10 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13811,7 +13811,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14283,7 +14283,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14701,7 +14701,7 @@
         <v>1.33</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF30" t="n">
         <v>1.5</v>
@@ -14731,7 +14731,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15146,7 +15146,7 @@
         <v>75</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE31" t="n">
         <v>1.2</v>
@@ -15179,7 +15179,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15621,7 +15621,7 @@
         <v>1.33</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF32" t="n">
         <v>0</v>
@@ -15651,7 +15651,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16123,7 +16123,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16546,7 +16546,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -16579,7 +16579,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17018,10 +17018,10 @@
         <v>75</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF35" t="n">
         <v>0</v>
@@ -17051,7 +17051,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17485,7 +17485,7 @@
         <v>0.78</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -17515,7 +17515,7 @@
         <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17957,7 +17957,7 @@
         <v>1.33</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -17987,7 +17987,7 @@
         <v>2.34</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18451,7 +18451,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18874,7 +18874,7 @@
         <v>34</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE39" t="n">
         <v>1</v>
@@ -18907,7 +18907,7 @@
         <v>2.34</v>
       </c>
       <c r="DO39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19379,7 +19379,7 @@
         <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19810,10 +19810,10 @@
         <v>0</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE41" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF41" t="n">
         <v>2.33</v>
@@ -19843,7 +19843,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20282,7 +20282,7 @@
         <v>59</v>
       </c>
       <c r="DD42" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE42" t="n">
         <v>1.22</v>
@@ -20315,7 +20315,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20741,7 +20741,7 @@
         <v>1</v>
       </c>
       <c r="DE43" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF43" t="n">
         <v>0.67</v>
@@ -20771,7 +20771,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21210,7 +21210,7 @@
         <v>100</v>
       </c>
       <c r="DD44" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE44" t="n">
         <v>1.78</v>
@@ -21243,7 +21243,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21682,10 +21682,10 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>0</v>
@@ -21715,7 +21715,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22157,7 +22157,7 @@
         <v>1</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22187,7 +22187,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22626,10 +22626,10 @@
         <v>59</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -22659,7 +22659,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23107,7 +23107,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23538,7 +23538,7 @@
         <v>84</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE49" t="n">
         <v>2</v>
@@ -23571,7 +23571,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24043,7 +24043,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24477,7 +24477,7 @@
         <v>0.78</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF51" t="n">
         <v>1.33</v>
@@ -24507,7 +24507,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24963,7 +24963,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25402,10 +25402,10 @@
         <v>71</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF53" t="n">
         <v>2.25</v>
@@ -25435,7 +25435,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25874,10 +25874,10 @@
         <v>54</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF54" t="n">
         <v>1.67</v>
@@ -25907,7 +25907,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26338,7 +26338,7 @@
         <v>38</v>
       </c>
       <c r="DD55" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE55" t="n">
         <v>1.2</v>
@@ -26371,7 +26371,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26827,7 +26827,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27266,7 +27266,7 @@
         <v>84</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -27299,7 +27299,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27738,10 +27738,10 @@
         <v>88</v>
       </c>
       <c r="DD58" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE58" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF58" t="n">
         <v>0.67</v>
@@ -27771,7 +27771,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28213,7 +28213,7 @@
         <v>2.78</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF59" t="n">
         <v>3</v>
@@ -28243,7 +28243,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28715,7 +28715,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29163,7 +29163,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29586,7 +29586,7 @@
         <v>63</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE62" t="n">
         <v>1</v>
@@ -29619,7 +29619,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30061,7 +30061,7 @@
         <v>1</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF63" t="n">
         <v>1</v>
@@ -30091,7 +30091,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30530,10 +30530,10 @@
         <v>75</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF64" t="n">
         <v>0.75</v>
@@ -30563,7 +30563,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30683,162 +30683,170 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="n">
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>8</v>
+      </c>
+      <c r="S65" t="n">
         <v>6</v>
       </c>
-      <c r="L65" t="n">
+      <c r="T65" t="n">
         <v>10</v>
       </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
+        <v>9</v>
+      </c>
+      <c r="V65" t="n">
+        <v>18</v>
+      </c>
+      <c r="W65" t="n">
+        <v>14</v>
+      </c>
+      <c r="X65" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU65" t="n">
         <v>4</v>
       </c>
-      <c r="S65" t="n">
-        <v>4</v>
-      </c>
-      <c r="T65" t="n">
-        <v>8</v>
-      </c>
-      <c r="U65" t="n">
-        <v>6</v>
-      </c>
-      <c r="V65" t="n">
-        <v>12</v>
-      </c>
-      <c r="W65" t="n">
-        <v>19</v>
-      </c>
-      <c r="X65" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -30853,76 +30861,76 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS65" t="n">
         <v>4</v>
       </c>
-      <c r="BN65" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS65" t="n">
-        <v>2</v>
-      </c>
       <c r="BT65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW65" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX65" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY65" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ65" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB65" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC65" t="n">
         <v>0</v>
       </c>
       <c r="CD65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE65" t="n">
         <v>0</v>
       </c>
       <c r="CF65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG65" t="n">
         <v>0</v>
@@ -30946,7 +30954,7 @@
         <v>0</v>
       </c>
       <c r="CN65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO65" t="n">
         <v>0</v>
@@ -30958,19 +30966,19 @@
         <v>1</v>
       </c>
       <c r="CR65" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS65" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV65" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -30979,67 +30987,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ65" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA65" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC65" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.5600000000000001</v>
+        <v>2</v>
       </c>
       <c r="DF65" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ65" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK65" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM65" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -31048,86 +31056,70 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW65" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="DX65" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="DY65" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="DZ65" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW65" t="inlineStr"/>
+      <c r="DX65" t="inlineStr"/>
+      <c r="DY65" t="inlineStr"/>
+      <c r="DZ65" t="inlineStr"/>
       <c r="EA65" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EB65" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EC65" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="ED65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -31147,170 +31139,162 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>4</v>
       </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" t="n">
+        <v>6</v>
+      </c>
+      <c r="L66" t="n">
         <v>10</v>
       </c>
-      <c r="L66" t="n">
-        <v>11</v>
-      </c>
       <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
         <v>4</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>3</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
         <v>8</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>10</v>
-      </c>
-      <c r="U66" t="n">
-        <v>9</v>
-      </c>
       <c r="V66" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y66" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z66" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE66" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF66" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN66" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO66" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -31325,124 +31309,124 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN66" t="n">
         <v>6</v>
       </c>
-      <c r="BN66" t="n">
+      <c r="BO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
         <v>5</v>
       </c>
-      <c r="BO66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>0</v>
-      </c>
       <c r="BS66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS66" t="n">
         <v>23</v>
       </c>
-      <c r="BW66" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB66" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF66" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ66" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS66" t="n">
-        <v>30</v>
-      </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV66" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -31451,67 +31435,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ66" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA66" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE66" t="n">
-        <v>2.13</v>
+        <v>0.5</v>
       </c>
       <c r="DF66" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ66" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -31520,70 +31504,86 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW66" t="inlineStr"/>
-      <c r="DX66" t="inlineStr"/>
-      <c r="DY66" t="inlineStr"/>
-      <c r="DZ66" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW66" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="DX66" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DY66" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="DZ66" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -31922,10 +31922,10 @@
         <v>78</v>
       </c>
       <c r="DD67" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -31955,7 +31955,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32427,7 +32427,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32858,7 +32858,7 @@
         <v>58</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE69" t="n">
         <v>1.2</v>
@@ -32891,7 +32891,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33314,7 +33314,7 @@
         <v>75</v>
       </c>
       <c r="DD70" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE70" t="n">
         <v>2</v>
@@ -33347,7 +33347,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33803,7 +33803,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34275,7 +34275,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34739,7 +34739,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35170,10 +35170,10 @@
         <v>40</v>
       </c>
       <c r="DD74" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF74" t="n">
         <v>2.6</v>
@@ -35203,7 +35203,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35626,10 +35626,10 @@
         <v>60</v>
       </c>
       <c r="DD75" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF75" t="n">
         <v>2.4</v>
@@ -35659,7 +35659,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36082,7 +36082,7 @@
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE76" t="n">
         <v>1.78</v>
@@ -36115,7 +36115,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36549,7 +36549,7 @@
         <v>1</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF77" t="n">
         <v>0.4</v>
@@ -36579,7 +36579,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37035,7 +37035,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37139,128 +37139,120 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" t="n">
         <v>4</v>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>6</v>
-      </c>
       <c r="R79" t="n">
         <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
+        <v>18</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>14</v>
+      </c>
+      <c r="X79" t="n">
         <v>21</v>
       </c>
-      <c r="V79" t="n">
-        <v>6</v>
-      </c>
-      <c r="W79" t="n">
-        <v>11</v>
-      </c>
-      <c r="X79" t="n">
-        <v>13</v>
-      </c>
       <c r="Y79" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z79" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -37269,10 +37261,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -37284,10 +37276,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -37296,13 +37288,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37317,19 +37309,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -37338,55 +37330,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW79" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX79" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY79" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -37407,7 +37399,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -37422,76 +37414,76 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS79" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
         <v>13</v>
       </c>
-      <c r="CV79" t="n">
-        <v>11</v>
-      </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC79" t="n">
         <v>60</v>
       </c>
-      <c r="DA79" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB79" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC79" t="n">
+      <c r="DD79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ79" t="n">
         <v>80</v>
       </c>
-      <c r="DD79" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>40</v>
-      </c>
       <c r="DK79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM79" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN79" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO79" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37512,86 +37504,86 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DX79" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DY79" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DY79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -37611,120 +37603,128 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>6</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>8</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
       <c r="U80" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y80" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z80" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF80" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK80" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -37733,10 +37733,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -37748,10 +37748,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -37760,13 +37760,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -37781,19 +37781,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -37802,55 +37802,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT80" t="n">
         <v>4</v>
       </c>
-      <c r="BT80" t="n">
-        <v>6</v>
-      </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW80" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX80" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY80" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -37871,7 +37871,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -37886,73 +37886,73 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV80" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA80" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC80" t="n">
         <v>80</v>
       </c>
-      <c r="DB80" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>60</v>
-      </c>
       <c r="DD80" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG80" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH80" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ80" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN80" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO80" t="n">
         <v>18</v>
@@ -37976,86 +37976,86 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DX80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -38394,10 +38394,10 @@
         <v>74</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF81" t="n">
         <v>0.4</v>
@@ -38427,7 +38427,7 @@
         <v>2.34</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38866,10 +38866,10 @@
         <v>70</v>
       </c>
       <c r="DD82" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE82" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF82" t="n">
         <v>1.2</v>
@@ -38899,7 +38899,7 @@
         <v>2.5</v>
       </c>
       <c r="DO82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39338,7 +39338,7 @@
         <v>92</v>
       </c>
       <c r="DD83" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE83" t="n">
         <v>2</v>
@@ -39371,7 +39371,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39810,7 +39810,7 @@
         <v>50</v>
       </c>
       <c r="DD84" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE84" t="n">
         <v>2.22</v>
@@ -39843,7 +39843,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40285,7 +40285,7 @@
         <v>2.78</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF85" t="n">
         <v>3</v>
@@ -40315,7 +40315,7 @@
         <v>3.31</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40746,10 +40746,10 @@
         <v>74</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF86" t="n">
         <v>1.8</v>
@@ -40779,7 +40779,7 @@
         <v>3.01</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41235,7 +41235,7 @@
         <v>2.39</v>
       </c>
       <c r="DO87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41699,7 +41699,7 @@
         <v>3.02</v>
       </c>
       <c r="DO88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42114,10 +42114,10 @@
         <v>42</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF89" t="n">
         <v>2.67</v>
@@ -42147,7 +42147,7 @@
         <v>3.26</v>
       </c>
       <c r="DO89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42562,7 +42562,7 @@
         <v>59</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE90" t="n">
         <v>1.22</v>
@@ -42595,7 +42595,7 @@
         <v>2.86</v>
       </c>
       <c r="DO90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43043,7 +43043,7 @@
         <v>1.9</v>
       </c>
       <c r="DO91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43466,10 +43466,10 @@
         <v>85</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF92" t="n">
         <v>1.86</v>
@@ -43499,7 +43499,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43941,7 +43941,7 @@
         <v>1.33</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF93" t="n">
         <v>0.5</v>
@@ -43971,7 +43971,7 @@
         <v>1.48</v>
       </c>
       <c r="DO93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44397,7 +44397,7 @@
         <v>1.13</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF94" t="n">
         <v>1.17</v>
@@ -44427,7 +44427,7 @@
         <v>2.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP94" t="b">
         <v>0</v>
@@ -44866,7 +44866,7 @@
         <v>59</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE95" t="n">
         <v>2.22</v>
@@ -44899,7 +44899,7 @@
         <v>2.56</v>
       </c>
       <c r="DO95" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45338,7 +45338,7 @@
         <v>92</v>
       </c>
       <c r="DD96" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE96" t="n">
         <v>2</v>
@@ -45371,7 +45371,7 @@
         <v>2.92</v>
       </c>
       <c r="DO96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45805,7 +45805,7 @@
         <v>1.33</v>
       </c>
       <c r="DE97" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF97" t="n">
         <v>1.5</v>
@@ -45835,7 +45835,7 @@
         <v>3.37</v>
       </c>
       <c r="DO97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -46274,7 +46274,7 @@
         <v>55</v>
       </c>
       <c r="DD98" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE98" t="n">
         <v>1.2</v>
@@ -46307,7 +46307,7 @@
         <v>2.65</v>
       </c>
       <c r="DO98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46733,7 +46733,7 @@
         <v>1</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF99" t="n">
         <v>1.33</v>
@@ -46763,7 +46763,7 @@
         <v>2.41</v>
       </c>
       <c r="DO99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47186,7 +47186,7 @@
         <v>70</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE100" t="n">
         <v>1</v>
@@ -47219,7 +47219,7 @@
         <v>2.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47661,7 +47661,7 @@
         <v>2.78</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF101" t="n">
         <v>3</v>
@@ -47691,7 +47691,7 @@
         <v>4.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48147,7 +48147,7 @@
         <v>2.15</v>
       </c>
       <c r="DO102" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -48578,7 +48578,7 @@
         <v>72</v>
       </c>
       <c r="DD103" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE103" t="n">
         <v>1</v>
@@ -48611,7 +48611,7 @@
         <v>3.68</v>
       </c>
       <c r="DO103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49042,10 +49042,10 @@
         <v>62</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF104" t="n">
         <v>2.57</v>
@@ -49075,7 +49075,7 @@
         <v>2.97</v>
       </c>
       <c r="DO104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49531,7 +49531,7 @@
         <v>2.24</v>
       </c>
       <c r="DO105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49957,7 +49957,7 @@
         <v>1.13</v>
       </c>
       <c r="DE106" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF106" t="n">
         <v>1.14</v>
@@ -49987,7 +49987,7 @@
         <v>2.48</v>
       </c>
       <c r="DO106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50107,12 +50107,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
@@ -50122,25 +50122,25 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L107" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M107" t="n">
         <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -50149,107 +50149,107 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="U107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V107" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W107" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X107" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y107" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Z107" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC107" t="n">
         <v>3</v>
       </c>
       <c r="AD107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE107" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AF107" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AG107" t="n">
         <v>1.33</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ107" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AN107" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="AO107" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AR107" t="n">
         <v>2.45</v>
       </c>
       <c r="AS107" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV107" t="n">
         <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX107" t="n">
         <v>0</v>
@@ -50261,10 +50261,10 @@
         <v>1</v>
       </c>
       <c r="BA107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB107" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
@@ -50276,7 +50276,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>2818</v>
+        <v>1843</v>
       </c>
       <c r="BG107" t="n">
         <v>2</v>
@@ -50285,37 +50285,37 @@
         <v>1</v>
       </c>
       <c r="BI107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ107" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM107" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BN107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BO107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP107" t="n">
         <v>0</v>
       </c>
       <c r="BQ107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT107" t="n">
         <v>3</v>
@@ -50324,25 +50324,25 @@
         <v>1</v>
       </c>
       <c r="BV107" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BW107" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="BX107" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="BY107" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BZ107" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="CA107" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="CB107" t="n">
-        <v>2.02</v>
+        <v>2.87</v>
       </c>
       <c r="CC107" t="n">
         <v>0</v>
@@ -50378,7 +50378,7 @@
         <v>0</v>
       </c>
       <c r="CN107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO107" t="n">
         <v>0</v>
@@ -50390,76 +50390,76 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CS107" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="CT107" t="n">
         <v>1</v>
       </c>
       <c r="CU107" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CV107" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW107" t="n">
         <v>1</v>
       </c>
       <c r="CX107" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CY107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ107" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="DA107" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="DB107" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="DC107" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE107" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DF107" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="DG107" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH107" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="DI107" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DJ107" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="DK107" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="DL107" t="n">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="DM107" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="DN107" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="DO107" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50468,7 +50468,7 @@
         <v>1</v>
       </c>
       <c r="DR107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS107" t="b">
         <v>0</v>
@@ -50484,70 +50484,82 @@
       </c>
       <c r="DW107" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="DX107" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="ED107" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EE107" t="inlineStr"/>
-      <c r="EF107" t="inlineStr"/>
-      <c r="EG107" t="inlineStr"/>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="EK107" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
     </row>
@@ -50567,12 +50579,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
@@ -50582,25 +50594,25 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
         <v>5</v>
       </c>
-      <c r="K108" t="n">
-        <v>8</v>
-      </c>
       <c r="L108" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M108" t="n">
         <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -50609,107 +50621,107 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T108" t="n">
+        <v>4</v>
+      </c>
+      <c r="U108" t="n">
+        <v>4</v>
+      </c>
+      <c r="V108" t="n">
+        <v>9</v>
+      </c>
+      <c r="W108" t="n">
+        <v>16</v>
+      </c>
+      <c r="X108" t="n">
         <v>15</v>
       </c>
-      <c r="U108" t="n">
-        <v>2</v>
-      </c>
-      <c r="V108" t="n">
-        <v>23</v>
-      </c>
-      <c r="W108" t="n">
-        <v>14</v>
-      </c>
-      <c r="X108" t="n">
-        <v>13</v>
-      </c>
       <c r="Y108" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Z108" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC108" t="n">
         <v>3</v>
       </c>
       <c r="AD108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE108" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AF108" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AG108" t="n">
         <v>1.33</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="AO108" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR108" t="n">
         <v>2.45</v>
       </c>
       <c r="AS108" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AU108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
         <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX108" t="n">
         <v>0</v>
@@ -50721,10 +50733,10 @@
         <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -50736,7 +50748,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>1843</v>
+        <v>2818</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -50745,37 +50757,37 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL108" t="n">
         <v>4</v>
       </c>
-      <c r="BJ108" t="n">
+      <c r="BM108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN108" t="n">
         <v>6</v>
       </c>
-      <c r="BK108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM108" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN108" t="n">
-        <v>3</v>
-      </c>
       <c r="BO108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP108" t="n">
         <v>0</v>
       </c>
       <c r="BQ108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT108" t="n">
         <v>3</v>
@@ -50784,25 +50796,25 @@
         <v>1</v>
       </c>
       <c r="BV108" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BW108" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="BX108" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="BY108" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BZ108" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="CA108" t="n">
-        <v>2.44</v>
+        <v>1.47</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.87</v>
+        <v>2.02</v>
       </c>
       <c r="CC108" t="n">
         <v>0</v>
@@ -50838,7 +50850,7 @@
         <v>0</v>
       </c>
       <c r="CN108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO108" t="n">
         <v>0</v>
@@ -50850,76 +50862,76 @@
         <v>1</v>
       </c>
       <c r="CR108" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CS108" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
         <v>15</v>
       </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>13</v>
-      </c>
       <c r="CV108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CY108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ108" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA108" t="n">
         <v>71</v>
       </c>
-      <c r="DA108" t="n">
-        <v>93</v>
-      </c>
       <c r="DB108" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="DC108" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="DD108" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE108" t="n">
         <v>2</v>
       </c>
       <c r="DF108" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="DG108" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DH108" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="DI108" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DJ108" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK108" t="n">
         <v>29</v>
       </c>
-      <c r="DK108" t="n">
-        <v>7</v>
-      </c>
       <c r="DL108" t="n">
-        <v>0.88</v>
+        <v>1.35</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="DO108" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -50928,7 +50940,7 @@
         <v>1</v>
       </c>
       <c r="DR108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS108" t="b">
         <v>0</v>
@@ -50944,82 +50956,70 @@
       </c>
       <c r="DW108" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="DX108" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="ED108" t="inlineStr">
         <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EE108" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF108" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EG108" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr"/>
+      <c r="EF108" t="inlineStr"/>
+      <c r="EG108" t="inlineStr"/>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EI108" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EJ108" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="EK108" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="EL108" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
     </row>
@@ -51358,7 +51358,7 @@
         <v>69</v>
       </c>
       <c r="DD109" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DE109" t="n">
         <v>1.2</v>
@@ -51391,7 +51391,7 @@
         <v>2.86</v>
       </c>
       <c r="DO109" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51833,7 +51833,7 @@
         <v>1.33</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DF110" t="n">
         <v>0.86</v>
@@ -51863,7 +51863,7 @@
         <v>1.85</v>
       </c>
       <c r="DO110" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52311,7 +52311,7 @@
         <v>3.24</v>
       </c>
       <c r="DO111" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52734,10 +52734,10 @@
         <v>79</v>
       </c>
       <c r="DD112" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF112" t="n">
         <v>2</v>
@@ -52767,7 +52767,7 @@
         <v>2.12</v>
       </c>
       <c r="DO112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53181,7 +53181,7 @@
         <v>0.78</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF113" t="n">
         <v>0.5</v>
@@ -53211,7 +53211,7 @@
         <v>2.63</v>
       </c>
       <c r="DO113" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53653,7 +53653,7 @@
         <v>1</v>
       </c>
       <c r="DE114" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="DF114" t="n">
         <v>0.5</v>
@@ -53683,7 +53683,7 @@
         <v>2.44</v>
       </c>
       <c r="DO114" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54098,10 +54098,10 @@
         <v>61</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE115" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF115" t="n">
         <v>2.75</v>
@@ -54131,7 +54131,7 @@
         <v>3</v>
       </c>
       <c r="DO115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54554,7 +54554,7 @@
         <v>82</v>
       </c>
       <c r="DD116" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DE116" t="n">
         <v>1</v>
@@ -54587,7 +54587,7 @@
         <v>3.49</v>
       </c>
       <c r="DO116" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55026,7 +55026,7 @@
         <v>81</v>
       </c>
       <c r="DD117" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE117" t="n">
         <v>1.78</v>
@@ -55059,7 +55059,7 @@
         <v>2.12</v>
       </c>
       <c r="DO117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55482,7 +55482,7 @@
         <v>67</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE118" t="n">
         <v>1.22</v>
@@ -55515,7 +55515,7 @@
         <v>2.15</v>
       </c>
       <c r="DO118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55987,7 +55987,7 @@
         <v>3.62</v>
       </c>
       <c r="DO119" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56451,7 +56451,7 @@
         <v>2.76</v>
       </c>
       <c r="DO120" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56893,7 +56893,7 @@
         <v>1</v>
       </c>
       <c r="DE121" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF121" t="n">
         <v>0.78</v>
@@ -56923,7 +56923,7 @@
         <v>1.93</v>
       </c>
       <c r="DO121" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57387,7 +57387,7 @@
         <v>2.85</v>
       </c>
       <c r="DO122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57859,7 +57859,7 @@
         <v>1.96</v>
       </c>
       <c r="DO123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -58298,7 +58298,7 @@
         <v>94</v>
       </c>
       <c r="DD124" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DE124" t="n">
         <v>1</v>
@@ -58331,7 +58331,7 @@
         <v>2.73</v>
       </c>
       <c r="DO124" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP124" t="b">
         <v>0</v>
@@ -58424,6 +58424,3190 @@
       <c r="EL124" t="inlineStr">
         <is>
           <t>2.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>19</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46053.625</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>2</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>15</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
+        <v>22</v>
+      </c>
+      <c r="W125" t="n">
+        <v>12</v>
+      </c>
+      <c r="X125" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>5131</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>112</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW125" t="inlineStr"/>
+      <c r="DX125" t="inlineStr"/>
+      <c r="DY125" t="inlineStr"/>
+      <c r="DZ125" t="inlineStr"/>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EE125" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EF125" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="EG125" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>19</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46053.66666666666</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>8</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2</v>
+      </c>
+      <c r="L126" t="n">
+        <v>10</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>14</v>
+      </c>
+      <c r="T126" t="n">
+        <v>2</v>
+      </c>
+      <c r="U126" t="n">
+        <v>15</v>
+      </c>
+      <c r="V126" t="n">
+        <v>6</v>
+      </c>
+      <c r="W126" t="n">
+        <v>14</v>
+      </c>
+      <c r="X126" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>Stadio Peristeriou</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>93 Giannitson, Peristeri, Athens</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>5130</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>125</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>35</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW126" t="inlineStr"/>
+      <c r="DX126" t="inlineStr"/>
+      <c r="DY126" t="inlineStr"/>
+      <c r="DZ126" t="inlineStr"/>
+      <c r="EA126" t="inlineStr"/>
+      <c r="EB126" t="inlineStr"/>
+      <c r="EC126" t="inlineStr"/>
+      <c r="ED126" t="inlineStr"/>
+      <c r="EE126" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EF126" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EG126" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EL126" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>19</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46053.75</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4</v>
+      </c>
+      <c r="L127" t="n">
+        <v>11</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>2</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="n">
+        <v>11</v>
+      </c>
+      <c r="U127" t="n">
+        <v>12</v>
+      </c>
+      <c r="V127" t="n">
+        <v>18</v>
+      </c>
+      <c r="W127" t="n">
+        <v>15</v>
+      </c>
+      <c r="X127" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Dimotiko Stadio Neapolis Volou</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Efstratios Argenti, Volos</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1106</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="DX127" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr"/>
+      <c r="ED127" t="inlineStr"/>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>19</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46054.58333333334</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>4</v>
+      </c>
+      <c r="J128" t="n">
+        <v>3</v>
+      </c>
+      <c r="K128" t="n">
+        <v>6</v>
+      </c>
+      <c r="L128" t="n">
+        <v>9</v>
+      </c>
+      <c r="M128" t="n">
+        <v>3</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>4</v>
+      </c>
+      <c r="R128" t="n">
+        <v>5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>6</v>
+      </c>
+      <c r="T128" t="n">
+        <v>13</v>
+      </c>
+      <c r="U128" t="n">
+        <v>10</v>
+      </c>
+      <c r="V128" t="n">
+        <v>18</v>
+      </c>
+      <c r="W128" t="n">
+        <v>18</v>
+      </c>
+      <c r="X128" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Stadio Levadias</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Agion Theodoron, Levadia</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>1108</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>39</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>35</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW128" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="DX128" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>19</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46054.64583333334</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" t="n">
+        <v>5</v>
+      </c>
+      <c r="L129" t="n">
+        <v>9</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>6</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>6</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>8</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3</v>
+      </c>
+      <c r="U129" t="n">
+        <v>14</v>
+      </c>
+      <c r="V129" t="n">
+        <v>7</v>
+      </c>
+      <c r="W129" t="n">
+        <v>14</v>
+      </c>
+      <c r="X129" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Olympiako Stadio Spyros Louis</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>37 Kifissias Avenue, Maroussi, Athens</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>960</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>76</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>124</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW129" t="inlineStr"/>
+      <c r="DX129" t="inlineStr"/>
+      <c r="DY129" t="inlineStr"/>
+      <c r="DZ129" t="inlineStr"/>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EC129" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="ED129" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EE129" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>7.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>19</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46054.72916666666</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5</v>
+      </c>
+      <c r="J130" t="n">
+        <v>6</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" t="n">
+        <v>7</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>6</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1</v>
+      </c>
+      <c r="S130" t="n">
+        <v>7</v>
+      </c>
+      <c r="T130" t="n">
+        <v>4</v>
+      </c>
+      <c r="U130" t="n">
+        <v>13</v>
+      </c>
+      <c r="V130" t="n">
+        <v>5</v>
+      </c>
+      <c r="W130" t="n">
+        <v>7</v>
+      </c>
+      <c r="X130" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>81</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>39</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW130" t="inlineStr"/>
+      <c r="DX130" t="inlineStr"/>
+      <c r="DY130" t="inlineStr"/>
+      <c r="DZ130" t="inlineStr"/>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="ED130" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>25.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>19</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46054.79166666666</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
+        <v>3</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4</v>
+      </c>
+      <c r="M131" t="n">
+        <v>3</v>
+      </c>
+      <c r="N131" t="n">
+        <v>5</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>4</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="n">
+        <v>5</v>
+      </c>
+      <c r="U131" t="n">
+        <v>9</v>
+      </c>
+      <c r="V131" t="n">
+        <v>11</v>
+      </c>
+      <c r="W131" t="n">
+        <v>14</v>
+      </c>
+      <c r="X131" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>143</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>12</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW131" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="DX131" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr"/>
+      <c r="EB131" t="inlineStr"/>
+      <c r="EC131" t="inlineStr"/>
+      <c r="ED131" t="inlineStr"/>
+      <c r="EE131" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF131" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EG131" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>2.98</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -58612,7 +58612,7 @@
         <v>0</v>
       </c>
       <c r="BF125" t="n">
-        <v>-1</v>
+        <v>1755</v>
       </c>
       <c r="BG125" t="n">
         <v>2</v>
@@ -59068,7 +59068,7 @@
         <v>0</v>
       </c>
       <c r="BF126" t="n">
-        <v>-1</v>
+        <v>1036</v>
       </c>
       <c r="BG126" t="n">
         <v>2</v>
@@ -59508,7 +59508,7 @@
         <v>0</v>
       </c>
       <c r="BF127" t="n">
-        <v>-1</v>
+        <v>3760</v>
       </c>
       <c r="BG127" t="n">
         <v>2</v>
@@ -59972,7 +59972,7 @@
         <v>0</v>
       </c>
       <c r="BF128" t="n">
-        <v>-1</v>
+        <v>1201</v>
       </c>
       <c r="BG128" t="n">
         <v>2</v>
@@ -60444,7 +60444,7 @@
         <v>0</v>
       </c>
       <c r="BF129" t="n">
-        <v>-1</v>
+        <v>5516</v>
       </c>
       <c r="BG129" t="n">
         <v>2</v>
@@ -60892,7 +60892,7 @@
         <v>0</v>
       </c>
       <c r="BF130" t="n">
-        <v>-1</v>
+        <v>14416</v>
       </c>
       <c r="BG130" t="n">
         <v>2</v>
@@ -61340,7 +61340,7 @@
         <v>0</v>
       </c>
       <c r="BF131" t="n">
-        <v>-1</v>
+        <v>31100</v>
       </c>
       <c r="BG131" t="n">
         <v>2</v>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL131" headerRowCount="1">
-  <autoFilter ref="A1:EL131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL132" headerRowCount="1">
+  <autoFilter ref="A1:EL132"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL131"/>
+  <dimension ref="A1:EL132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -4529,7 +4529,7 @@
         <v>1.44</v>
       </c>
       <c r="DE8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -6415,7 +6415,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7823,7 +7823,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -9174,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE18" t="n">
         <v>1</v>
@@ -9207,7 +9207,7 @@
         <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -11975,7 +11975,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -13781,7 +13781,7 @@
         <v>2.22</v>
       </c>
       <c r="DE28" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14283,7 +14283,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -16090,7 +16090,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE33" t="n">
         <v>2</v>
@@ -17515,7 +17515,7 @@
         <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -19813,7 +19813,7 @@
         <v>2.8</v>
       </c>
       <c r="DE41" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF41" t="n">
         <v>2.33</v>
@@ -20741,7 +20741,7 @@
         <v>1</v>
       </c>
       <c r="DE43" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF43" t="n">
         <v>0.67</v>
@@ -20771,7 +20771,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22154,7 +22154,7 @@
         <v>84</v>
       </c>
       <c r="DD46" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE46" t="n">
         <v>1</v>
@@ -26827,7 +26827,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28243,7 +28243,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -30058,7 +30058,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -30683,170 +30683,162 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>4</v>
       </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
       <c r="K65" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" t="n">
         <v>10</v>
       </c>
-      <c r="L65" t="n">
-        <v>11</v>
-      </c>
       <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2</v>
+      </c>
+      <c r="R65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
         <v>8</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>6</v>
       </c>
-      <c r="T65" t="n">
-        <v>10</v>
-      </c>
-      <c r="U65" t="n">
-        <v>9</v>
-      </c>
       <c r="V65" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Y65" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z65" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE65" t="n">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF65" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.26</v>
+        <v>4.33</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL65" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AN65" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="AO65" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AS65" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="n">
         <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>116</v>
+        <v>-1</v>
       </c>
       <c r="BC65" t="n">
         <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BE65" t="n">
         <v>0</v>
@@ -30861,124 +30853,124 @@
         <v>1</v>
       </c>
       <c r="BI65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BK65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL65" t="n">
         <v>5</v>
       </c>
       <c r="BM65" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN65" t="n">
         <v>6</v>
       </c>
-      <c r="BN65" t="n">
+      <c r="BO65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR65" t="n">
         <v>5</v>
       </c>
-      <c r="BO65" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ65" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR65" t="n">
-        <v>0</v>
-      </c>
       <c r="BS65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU65" t="n">
         <v>1</v>
       </c>
       <c r="BV65" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS65" t="n">
         <v>23</v>
       </c>
-      <c r="BW65" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX65" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY65" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ65" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA65" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CB65" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF65" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ65" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS65" t="n">
-        <v>30</v>
-      </c>
       <c r="CT65" t="n">
         <v>1</v>
       </c>
       <c r="CU65" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="CV65" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -30987,67 +30979,67 @@
         <v>9</v>
       </c>
       <c r="CY65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ65" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="DA65" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DB65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC65" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DE65" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DF65" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="DH65" t="n">
         <v>1.33</v>
       </c>
       <c r="DI65" t="n">
-        <v>2.44</v>
+        <v>0.67</v>
       </c>
       <c r="DJ65" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="DK65" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="DL65" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="DM65" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="DN65" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="DO65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT65" t="b">
         <v>0</v>
@@ -31056,70 +31048,86 @@
         <v>0</v>
       </c>
       <c r="DV65" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW65" t="inlineStr"/>
-      <c r="DX65" t="inlineStr"/>
-      <c r="DY65" t="inlineStr"/>
-      <c r="DZ65" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW65" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="DX65" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DY65" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="DZ65" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
       <c r="EA65" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB65" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC65" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="ED65" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE65" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EF65" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EH65" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EI65" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ65" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="EK65" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EL65" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.57</t>
         </is>
       </c>
     </row>
@@ -31139,162 +31147,170 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>11</v>
+      </c>
+      <c r="M66" t="n">
         <v>4</v>
       </c>
-      <c r="K66" t="n">
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>8</v>
+      </c>
+      <c r="S66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="n">
+      <c r="T66" t="n">
         <v>10</v>
       </c>
-      <c r="M66" t="n">
-        <v>2</v>
-      </c>
-      <c r="N66" t="n">
-        <v>6</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
+        <v>9</v>
+      </c>
+      <c r="V66" t="n">
+        <v>18</v>
+      </c>
+      <c r="W66" t="n">
+        <v>14</v>
+      </c>
+      <c r="X66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU66" t="n">
         <v>4</v>
       </c>
-      <c r="S66" t="n">
-        <v>4</v>
-      </c>
-      <c r="T66" t="n">
-        <v>8</v>
-      </c>
-      <c r="U66" t="n">
-        <v>6</v>
-      </c>
-      <c r="V66" t="n">
-        <v>12</v>
-      </c>
-      <c r="W66" t="n">
-        <v>19</v>
-      </c>
-      <c r="X66" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
       <c r="AV66" t="n">
         <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>-1</v>
+        <v>116</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -31309,76 +31325,76 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL66" t="n">
         <v>5</v>
       </c>
       <c r="BM66" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS66" t="n">
         <v>4</v>
       </c>
-      <c r="BN66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>2</v>
-      </c>
       <c r="BT66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BU66" t="n">
         <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BW66" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="BX66" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="BY66" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="CA66" t="n">
-        <v>1.23</v>
+        <v>2.16</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="CC66" t="n">
         <v>0</v>
       </c>
       <c r="CD66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE66" t="n">
         <v>0</v>
       </c>
       <c r="CF66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -31402,7 +31418,7 @@
         <v>0</v>
       </c>
       <c r="CN66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO66" t="n">
         <v>0</v>
@@ -31414,19 +31430,19 @@
         <v>1</v>
       </c>
       <c r="CR66" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CS66" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="CV66" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
@@ -31435,67 +31451,67 @@
         <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CZ66" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DA66" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="DB66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC66" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="DF66" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH66" t="n">
         <v>1.33</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.67</v>
+        <v>2.44</v>
       </c>
       <c r="DJ66" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DK66" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="DM66" t="n">
-        <v>0.79</v>
+        <v>1.37</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DO66" t="n">
         <v>18</v>
       </c>
       <c r="DP66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -31504,86 +31520,70 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW66" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="DX66" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="DY66" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="DZ66" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW66" t="inlineStr"/>
+      <c r="DX66" t="inlineStr"/>
+      <c r="DY66" t="inlineStr"/>
+      <c r="DZ66" t="inlineStr"/>
       <c r="EA66" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EB66" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EC66" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="ED66" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -33770,7 +33770,7 @@
         <v>70</v>
       </c>
       <c r="DD71" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE71" t="n">
         <v>1</v>
@@ -33803,7 +33803,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34275,7 +34275,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -37139,120 +37139,128 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>6</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>8</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
       <c r="U79" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W79" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y79" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z79" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF79" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK79" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -37261,10 +37269,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -37276,10 +37284,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -37288,13 +37296,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37309,19 +37317,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -37330,55 +37338,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT79" t="n">
         <v>4</v>
       </c>
-      <c r="BT79" t="n">
-        <v>6</v>
-      </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW79" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX79" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY79" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -37399,7 +37407,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -37414,76 +37422,76 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA79" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC79" t="n">
         <v>80</v>
       </c>
-      <c r="DB79" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC79" t="n">
-        <v>60</v>
-      </c>
       <c r="DD79" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="DE79" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG79" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH79" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ79" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37504,86 +37512,86 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DX79" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -37603,128 +37611,120 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>7</v>
+      </c>
+      <c r="M80" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
         <v>8</v>
       </c>
-      <c r="M80" t="n">
-        <v>2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>6</v>
-      </c>
       <c r="R80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
+        <v>18</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>14</v>
+      </c>
+      <c r="X80" t="n">
         <v>21</v>
       </c>
-      <c r="V80" t="n">
-        <v>6</v>
-      </c>
-      <c r="W80" t="n">
-        <v>11</v>
-      </c>
-      <c r="X80" t="n">
-        <v>13</v>
-      </c>
       <c r="Y80" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z80" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -37733,10 +37733,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -37748,10 +37748,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -37760,13 +37760,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -37781,19 +37781,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -37802,55 +37802,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW80" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX80" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY80" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -37871,7 +37871,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -37886,76 +37886,76 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS80" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
         <v>13</v>
       </c>
-      <c r="CV80" t="n">
-        <v>11</v>
-      </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC80" t="n">
         <v>60</v>
       </c>
-      <c r="DA80" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC80" t="n">
+      <c r="DD80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ80" t="n">
         <v>80</v>
       </c>
-      <c r="DD80" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>40</v>
-      </c>
       <c r="DK80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM80" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN80" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO80" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37976,86 +37976,86 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DX80" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DY80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EF80" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EG80" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH80" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI80" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -38075,12 +38075,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -38096,119 +38096,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>19</v>
+      </c>
+      <c r="U81" t="n">
         <v>6</v>
       </c>
-      <c r="L81" t="n">
+      <c r="V81" t="n">
+        <v>24</v>
+      </c>
+      <c r="W81" t="n">
+        <v>8</v>
+      </c>
+      <c r="X81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
         <v>13</v>
       </c>
-      <c r="M81" t="n">
-        <v>2</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>4</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6</v>
-      </c>
-      <c r="S81" t="n">
-        <v>7</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3</v>
-      </c>
-      <c r="U81" t="n">
-        <v>11</v>
-      </c>
-      <c r="V81" t="n">
-        <v>9</v>
-      </c>
-      <c r="W81" t="n">
-        <v>15</v>
-      </c>
-      <c r="X81" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF81" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI81" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ81" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM81" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR81" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -38217,28 +38217,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38250,13 +38250,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ81" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -38265,52 +38265,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW81" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX81" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY81" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ81" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -38343,91 +38343,91 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS81" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>22</v>
       </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
+      <c r="CY81" t="n">
         <v>4</v>
       </c>
-      <c r="CY81" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ81" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA81" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD81" t="n">
         <v>0.6</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="DF81" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG81" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH81" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI81" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ81" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM81" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38452,82 +38452,82 @@
       </c>
       <c r="DW81" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DX81" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -38547,12 +38547,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -38568,119 +38568,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" t="n">
+        <v>13</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>11</v>
+      </c>
+      <c r="V82" t="n">
         <v>9</v>
       </c>
-      <c r="L82" t="n">
-        <v>12</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2</v>
-      </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
-        <v>4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>19</v>
-      </c>
-      <c r="U82" t="n">
-        <v>6</v>
-      </c>
-      <c r="V82" t="n">
-        <v>24</v>
-      </c>
       <c r="W82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X82" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y82" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z82" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE82" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF82" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL82" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM82" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ82" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ82" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR82" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -38689,28 +38689,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB82" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -38722,13 +38722,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -38737,52 +38737,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW82" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX82" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY82" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA82" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB82" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -38815,91 +38815,91 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV82" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW82" t="n">
         <v>1</v>
       </c>
       <c r="CX82" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ82" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD82" t="n">
         <v>0.6</v>
       </c>
       <c r="DE82" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DF82" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG82" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH82" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI82" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ82" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL82" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -38924,82 +38924,82 @@
       </c>
       <c r="DW82" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="DX82" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EG82" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EH82" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EF82" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EG82" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EH82" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EI82" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EJ82" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41202,7 @@
         <v>100</v>
       </c>
       <c r="DD87" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE87" t="n">
         <v>1.78</v>
@@ -41235,7 +41235,7 @@
         <v>2.39</v>
       </c>
       <c r="DO87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -45805,7 +45805,7 @@
         <v>1.33</v>
       </c>
       <c r="DE97" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF97" t="n">
         <v>1.5</v>
@@ -45835,7 +45835,7 @@
         <v>3.37</v>
       </c>
       <c r="DO97" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -46730,7 +46730,7 @@
         <v>79</v>
       </c>
       <c r="DD99" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE99" t="n">
         <v>1.3</v>
@@ -46763,7 +46763,7 @@
         <v>2.41</v>
       </c>
       <c r="DO99" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -50107,12 +50107,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
@@ -50122,25 +50122,25 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
         <v>5</v>
       </c>
-      <c r="K107" t="n">
-        <v>8</v>
-      </c>
       <c r="L107" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M107" t="n">
         <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -50149,107 +50149,107 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T107" t="n">
+        <v>4</v>
+      </c>
+      <c r="U107" t="n">
+        <v>4</v>
+      </c>
+      <c r="V107" t="n">
+        <v>9</v>
+      </c>
+      <c r="W107" t="n">
+        <v>16</v>
+      </c>
+      <c r="X107" t="n">
         <v>15</v>
       </c>
-      <c r="U107" t="n">
-        <v>2</v>
-      </c>
-      <c r="V107" t="n">
-        <v>23</v>
-      </c>
-      <c r="W107" t="n">
-        <v>14</v>
-      </c>
-      <c r="X107" t="n">
-        <v>13</v>
-      </c>
       <c r="Y107" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="Z107" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC107" t="n">
         <v>3</v>
       </c>
       <c r="AD107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE107" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AF107" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AG107" t="n">
         <v>1.33</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ107" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="AK107" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL107" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AN107" t="n">
-        <v>2.87</v>
+        <v>2.56</v>
       </c>
       <c r="AO107" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR107" t="n">
         <v>2.45</v>
       </c>
       <c r="AS107" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AU107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
         <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX107" t="n">
         <v>0</v>
@@ -50261,10 +50261,10 @@
         <v>1</v>
       </c>
       <c r="BA107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB107" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
@@ -50276,7 +50276,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>1843</v>
+        <v>2818</v>
       </c>
       <c r="BG107" t="n">
         <v>2</v>
@@ -50285,37 +50285,37 @@
         <v>1</v>
       </c>
       <c r="BI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL107" t="n">
         <v>4</v>
       </c>
-      <c r="BJ107" t="n">
+      <c r="BM107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN107" t="n">
         <v>6</v>
       </c>
-      <c r="BK107" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL107" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM107" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN107" t="n">
-        <v>3</v>
-      </c>
       <c r="BO107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP107" t="n">
         <v>0</v>
       </c>
       <c r="BQ107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT107" t="n">
         <v>3</v>
@@ -50324,25 +50324,25 @@
         <v>1</v>
       </c>
       <c r="BV107" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BW107" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="BX107" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="BY107" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BZ107" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="CA107" t="n">
-        <v>2.44</v>
+        <v>1.47</v>
       </c>
       <c r="CB107" t="n">
-        <v>2.87</v>
+        <v>2.02</v>
       </c>
       <c r="CC107" t="n">
         <v>0</v>
@@ -50378,7 +50378,7 @@
         <v>0</v>
       </c>
       <c r="CN107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO107" t="n">
         <v>0</v>
@@ -50390,76 +50390,76 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CS107" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
         <v>15</v>
       </c>
-      <c r="CT107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU107" t="n">
-        <v>13</v>
-      </c>
       <c r="CV107" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CW107" t="n">
         <v>1</v>
       </c>
       <c r="CX107" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CY107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ107" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA107" t="n">
         <v>71</v>
       </c>
-      <c r="DA107" t="n">
-        <v>93</v>
-      </c>
       <c r="DB107" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="DC107" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="DD107" t="n">
         <v>0.6</v>
       </c>
       <c r="DE107" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF107" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="DG107" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DH107" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="DI107" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DJ107" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK107" t="n">
         <v>29</v>
       </c>
-      <c r="DK107" t="n">
-        <v>7</v>
-      </c>
       <c r="DL107" t="n">
-        <v>0.88</v>
+        <v>1.35</v>
       </c>
       <c r="DM107" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="DN107" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="DO107" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50468,7 +50468,7 @@
         <v>1</v>
       </c>
       <c r="DR107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS107" t="b">
         <v>0</v>
@@ -50484,82 +50484,70 @@
       </c>
       <c r="DW107" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="DX107" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="ED107" t="inlineStr">
         <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EE107" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF107" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EG107" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr"/>
+      <c r="EF107" t="inlineStr"/>
+      <c r="EG107" t="inlineStr"/>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="EK107" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
     </row>
@@ -50579,12 +50567,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
@@ -50594,25 +50582,25 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K108" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L108" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M108" t="n">
         <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -50621,107 +50609,107 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="U108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V108" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W108" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X108" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y108" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Z108" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Stadio Peristeriou</t>
+          <t>Stadio Panetolikou</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
+          <t>Nikitara, Agrinio</t>
         </is>
       </c>
       <c r="AC108" t="n">
         <v>3</v>
       </c>
       <c r="AD108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE108" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AF108" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AG108" t="n">
         <v>1.33</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ108" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="AO108" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AR108" t="n">
         <v>2.45</v>
       </c>
       <c r="AS108" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AU108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV108" t="n">
         <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX108" t="n">
         <v>0</v>
@@ -50733,10 +50721,10 @@
         <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB108" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -50748,7 +50736,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>2818</v>
+        <v>1843</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -50757,37 +50745,37 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ108" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM108" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BN108" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BO108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP108" t="n">
         <v>0</v>
       </c>
       <c r="BQ108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT108" t="n">
         <v>3</v>
@@ -50796,25 +50784,25 @@
         <v>1</v>
       </c>
       <c r="BV108" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BW108" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="BX108" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="BY108" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BZ108" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="CA108" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.02</v>
+        <v>2.87</v>
       </c>
       <c r="CC108" t="n">
         <v>0</v>
@@ -50850,7 +50838,7 @@
         <v>0</v>
       </c>
       <c r="CN108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO108" t="n">
         <v>0</v>
@@ -50862,40 +50850,40 @@
         <v>1</v>
       </c>
       <c r="CR108" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CS108" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="CT108" t="n">
         <v>1</v>
       </c>
       <c r="CU108" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CV108" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CY108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ108" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="DA108" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="DB108" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="DC108" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="DD108" t="n">
         <v>0.6</v>
@@ -50904,31 +50892,31 @@
         <v>2</v>
       </c>
       <c r="DF108" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="DG108" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH108" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="DI108" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DJ108" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="DK108" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="DL108" t="n">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="DN108" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="DO108" t="n">
         <v>18</v>
@@ -50940,7 +50928,7 @@
         <v>1</v>
       </c>
       <c r="DR108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS108" t="b">
         <v>0</v>
@@ -50956,70 +50944,82 @@
       </c>
       <c r="DW108" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="DX108" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="ED108" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EE108" t="inlineStr"/>
-      <c r="EF108" t="inlineStr"/>
-      <c r="EG108" t="inlineStr"/>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EF108" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EI108" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ108" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="EK108" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="EL108" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
     </row>
@@ -55987,7 +55987,7 @@
         <v>3.62</v>
       </c>
       <c r="DO119" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56418,7 +56418,7 @@
         <v>82</v>
       </c>
       <c r="DD120" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE120" t="n">
         <v>2.22</v>
@@ -56451,7 +56451,7 @@
         <v>2.76</v>
       </c>
       <c r="DO120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -60155,7 +60155,7 @@
         <v>2.72</v>
       </c>
       <c r="DO128" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -60794,7 +60794,7 @@
         <v>7</v>
       </c>
       <c r="X130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y130" t="n">
         <v>64</v>
@@ -61015,7 +61015,7 @@
         <v>1</v>
       </c>
       <c r="CU130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CV130" t="n">
         <v>7</v>
@@ -61493,7 +61493,7 @@
         <v>2.5</v>
       </c>
       <c r="DE131" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DF131" t="n">
         <v>2.67</v>
@@ -61523,7 +61523,7 @@
         <v>3.58</v>
       </c>
       <c r="DO131" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61608,6 +61608,478 @@
       <c r="EL131" t="inlineStr">
         <is>
           <t>2.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>17</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46057.6875</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>7</v>
+      </c>
+      <c r="L132" t="n">
+        <v>7</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>2</v>
+      </c>
+      <c r="R132" t="n">
+        <v>9</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>11</v>
+      </c>
+      <c r="U132" t="n">
+        <v>3</v>
+      </c>
+      <c r="V132" t="n">
+        <v>20</v>
+      </c>
+      <c r="W132" t="n">
+        <v>14</v>
+      </c>
+      <c r="X132" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>116</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>53</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>140</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>36</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>18</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW132" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="DX132" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="ED132" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EH132" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EI132" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>5.97</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>14.64</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>1.24</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL132" headerRowCount="1">
-  <autoFilter ref="A1:EL132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL135" headerRowCount="1">
+  <autoFilter ref="A1:EL135"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL132"/>
+  <dimension ref="A1:EL135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -2241,7 +2241,7 @@
         <v>1.33</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5457,7 +5457,7 @@
         <v>1.33</v>
       </c>
       <c r="DE10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF10" t="n">
         <v>3</v>
@@ -5918,7 +5918,7 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE11" t="n">
         <v>1</v>
@@ -5951,7 +5951,7 @@
         <v>1.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6849,7 +6849,7 @@
         <v>2.8</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -8721,7 +8721,7 @@
         <v>0.6</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>2.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9174,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE18" t="n">
         <v>1</v>
@@ -9207,7 +9207,7 @@
         <v>0.71</v>
       </c>
       <c r="DO18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE19" t="n">
         <v>1</v>
@@ -11017,7 +11017,7 @@
         <v>0.78</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE23" t="n">
         <v>1.3</v>
@@ -11511,7 +11511,7 @@
         <v>2.38</v>
       </c>
       <c r="DO23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11975,7 +11975,7 @@
         <v>1.5</v>
       </c>
       <c r="DO24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12397,7 +12397,7 @@
         <v>2.8</v>
       </c>
       <c r="DE25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12850,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="DD26" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE26" t="n">
         <v>2.22</v>
@@ -15149,7 +15149,7 @@
         <v>2.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -16090,7 +16090,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE33" t="n">
         <v>2</v>
@@ -17051,7 +17051,7 @@
         <v>2.12</v>
       </c>
       <c r="DO35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18418,10 +18418,10 @@
         <v>17</v>
       </c>
       <c r="DD38" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18451,7 +18451,7 @@
         <v>2.3</v>
       </c>
       <c r="DO38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18877,7 +18877,7 @@
         <v>2.2</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -19346,7 +19346,7 @@
         <v>25</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE40" t="n">
         <v>2.22</v>
@@ -19379,7 +19379,7 @@
         <v>3.01</v>
       </c>
       <c r="DO40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20285,7 +20285,7 @@
         <v>2.22</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -20738,7 +20738,7 @@
         <v>33</v>
       </c>
       <c r="DD43" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE43" t="n">
         <v>2.1</v>
@@ -22154,7 +22154,7 @@
         <v>84</v>
       </c>
       <c r="DD46" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE46" t="n">
         <v>1</v>
@@ -22187,7 +22187,7 @@
         <v>2.98</v>
       </c>
       <c r="DO46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -24010,10 +24010,10 @@
         <v>50</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE50" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -24043,7 +24043,7 @@
         <v>1.92</v>
       </c>
       <c r="DO50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24933,7 +24933,7 @@
         <v>1.33</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -26341,7 +26341,7 @@
         <v>2.8</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF55" t="n">
         <v>2.5</v>
@@ -27771,7 +27771,7 @@
         <v>2.9</v>
       </c>
       <c r="DO58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28682,7 +28682,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE60" t="n">
         <v>1.78</v>
@@ -29589,7 +29589,7 @@
         <v>2.5</v>
       </c>
       <c r="DE62" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF62" t="n">
         <v>2.25</v>
@@ -30058,7 +30058,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -30563,7 +30563,7 @@
         <v>2.22</v>
       </c>
       <c r="DO64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31466,7 +31466,7 @@
         <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE66" t="n">
         <v>2.1</v>
@@ -31499,7 +31499,7 @@
         <v>2.57</v>
       </c>
       <c r="DO66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32861,7 +32861,7 @@
         <v>0.6</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF69" t="n">
         <v>0.5</v>
@@ -32891,7 +32891,7 @@
         <v>2.37</v>
       </c>
       <c r="DO69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33770,10 +33770,10 @@
         <v>70</v>
       </c>
       <c r="DD71" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE71" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF71" t="n">
         <v>1.5</v>
@@ -33803,7 +33803,7 @@
         <v>2.2</v>
       </c>
       <c r="DO71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34245,7 +34245,7 @@
         <v>2.78</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF72" t="n">
         <v>3</v>
@@ -36546,7 +36546,7 @@
         <v>55</v>
       </c>
       <c r="DD77" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE77" t="n">
         <v>1</v>
@@ -37005,7 +37005,7 @@
         <v>1.33</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF78" t="n">
         <v>0.6</v>
@@ -37139,128 +37139,120 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" t="n">
         <v>4</v>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>6</v>
-      </c>
       <c r="R79" t="n">
         <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
+        <v>18</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" t="n">
+        <v>14</v>
+      </c>
+      <c r="X79" t="n">
         <v>21</v>
       </c>
-      <c r="V79" t="n">
-        <v>6</v>
-      </c>
-      <c r="W79" t="n">
-        <v>11</v>
-      </c>
-      <c r="X79" t="n">
-        <v>13</v>
-      </c>
       <c r="Y79" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z79" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -37269,10 +37261,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -37284,10 +37276,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -37296,13 +37288,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37317,19 +37309,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -37338,55 +37330,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW79" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX79" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY79" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -37407,7 +37399,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -37422,76 +37414,76 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS79" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV79" t="n">
         <v>13</v>
       </c>
-      <c r="CV79" t="n">
-        <v>11</v>
-      </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC79" t="n">
         <v>60</v>
       </c>
-      <c r="DA79" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB79" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC79" t="n">
+      <c r="DD79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ79" t="n">
         <v>80</v>
       </c>
-      <c r="DD79" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>40</v>
-      </c>
       <c r="DK79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM79" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN79" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37512,86 +37504,86 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DX79" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DY79" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DY79" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EG79" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH79" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -37611,120 +37603,128 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>6</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="n">
         <v>5</v>
       </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>8</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
       <c r="U80" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y80" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z80" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF80" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK80" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -37733,10 +37733,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -37748,10 +37748,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -37760,13 +37760,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -37781,19 +37781,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -37802,55 +37802,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT80" t="n">
         <v>4</v>
       </c>
-      <c r="BT80" t="n">
-        <v>6</v>
-      </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW80" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX80" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY80" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -37871,7 +37871,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -37886,73 +37886,73 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV80" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA80" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC80" t="n">
         <v>80</v>
       </c>
-      <c r="DB80" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>60</v>
-      </c>
       <c r="DD80" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DE80" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="DF80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG80" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH80" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI80" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ80" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN80" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO80" t="n">
         <v>19</v>
@@ -37976,86 +37976,86 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW80" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DX80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -38075,12 +38075,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -38096,119 +38096,119 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K81" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" t="n">
+        <v>13</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>7</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>11</v>
+      </c>
+      <c r="V81" t="n">
         <v>9</v>
       </c>
-      <c r="L81" t="n">
-        <v>12</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5</v>
-      </c>
-      <c r="S81" t="n">
-        <v>4</v>
-      </c>
-      <c r="T81" t="n">
-        <v>19</v>
-      </c>
-      <c r="U81" t="n">
-        <v>6</v>
-      </c>
-      <c r="V81" t="n">
-        <v>24</v>
-      </c>
       <c r="W81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="X81" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Y81" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z81" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Stadio Panetolikou</t>
+          <t>Stadio Peristeriou</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Nikitara, Agrinio</t>
+          <t>93 Giannitson, Peristeri, Athens</t>
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE81" t="n">
-        <v>13</v>
+        <v>2.34</v>
       </c>
       <c r="AF81" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.27</v>
+        <v>3.29</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AI81" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL81" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AM81" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AP81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ81" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ81" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR81" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AU81" t="n">
         <v>1</v>
@@ -38217,28 +38217,28 @@
         <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>116</v>
+        <v>1107</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38250,13 +38250,13 @@
         <v>2</v>
       </c>
       <c r="BH81" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -38265,52 +38265,52 @@
         <v>4</v>
       </c>
       <c r="BM81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN81" t="n">
         <v>6</v>
       </c>
       <c r="BO81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR81" t="n">
         <v>0</v>
       </c>
       <c r="BS81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BW81" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="BX81" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="BY81" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0.78</v>
+        <v>1.31</v>
       </c>
       <c r="CA81" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="CB81" t="n">
-        <v>3.23</v>
+        <v>2.51</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -38343,91 +38343,91 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN81" t="n">
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="CS81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="CV81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="CW81" t="n">
         <v>1</v>
       </c>
       <c r="CX81" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CY81" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CZ81" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="DA81" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="DB81" t="n">
         <v>20</v>
       </c>
       <c r="DC81" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="DD81" t="n">
         <v>0.6</v>
       </c>
       <c r="DE81" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="DF81" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DG81" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DH81" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="DI81" t="n">
-        <v>2.55</v>
+        <v>0.73</v>
       </c>
       <c r="DJ81" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="DK81" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL81" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.53</v>
+        <v>0.87</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="DO81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38452,82 +38452,82 @@
       </c>
       <c r="DW81" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="DX81" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EG81" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EH81" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EI81" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="EF81" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EG81" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="EH81" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EI81" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.39</t>
         </is>
       </c>
     </row>
@@ -38547,12 +38547,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -38568,119 +38568,119 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K82" t="n">
+        <v>9</v>
+      </c>
+      <c r="L82" t="n">
+        <v>12</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>19</v>
+      </c>
+      <c r="U82" t="n">
         <v>6</v>
       </c>
-      <c r="L82" t="n">
+      <c r="V82" t="n">
+        <v>24</v>
+      </c>
+      <c r="W82" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
         <v>13</v>
       </c>
-      <c r="M82" t="n">
-        <v>2</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>4</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>7</v>
-      </c>
-      <c r="T82" t="n">
-        <v>3</v>
-      </c>
-      <c r="U82" t="n">
-        <v>11</v>
-      </c>
-      <c r="V82" t="n">
-        <v>9</v>
-      </c>
-      <c r="W82" t="n">
-        <v>15</v>
-      </c>
-      <c r="X82" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Stadio Peristeriou</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>93 Giannitson, Peristeri, Athens</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF82" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AI82" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ82" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM82" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AO82" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR82" t="n">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU82" t="n">
         <v>1</v>
@@ -38689,28 +38689,28 @@
         <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1107</v>
+        <v>116</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -38722,13 +38722,13 @@
         <v>2</v>
       </c>
       <c r="BH82" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ82" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ82" t="n">
-        <v>2</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -38737,52 +38737,52 @@
         <v>4</v>
       </c>
       <c r="BM82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN82" t="n">
         <v>6</v>
       </c>
       <c r="BO82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR82" t="n">
         <v>0</v>
       </c>
       <c r="BS82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="BW82" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="BX82" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="BY82" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="BZ82" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="CB82" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -38815,88 +38815,88 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="CS82" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
         <v>22</v>
       </c>
-      <c r="CT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU82" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
+      <c r="CY82" t="n">
         <v>4</v>
       </c>
-      <c r="CY82" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ82" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="DA82" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB82" t="n">
         <v>20</v>
       </c>
       <c r="DC82" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="DD82" t="n">
         <v>0.6</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="DF82" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DG82" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DH82" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="DI82" t="n">
-        <v>0.73</v>
+        <v>2.55</v>
       </c>
       <c r="DJ82" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="DK82" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="DM82" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="DO82" t="n">
         <v>19</v>
@@ -38924,82 +38924,82 @@
       </c>
       <c r="DW82" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DX82" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EJ82" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -40779,7 +40779,7 @@
         <v>3.01</v>
       </c>
       <c r="DO86" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41202,7 +41202,7 @@
         <v>100</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE87" t="n">
         <v>1.78</v>
@@ -41666,7 +41666,7 @@
         <v>84</v>
       </c>
       <c r="DD88" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE88" t="n">
         <v>1</v>
@@ -42565,7 +42565,7 @@
         <v>2.5</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF90" t="n">
         <v>2.5</v>
@@ -43013,7 +43013,7 @@
         <v>0.78</v>
       </c>
       <c r="DE91" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF91" t="n">
         <v>0.67</v>
@@ -44394,7 +44394,7 @@
         <v>77</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE94" t="n">
         <v>0.5</v>
@@ -44427,7 +44427,7 @@
         <v>2.2</v>
       </c>
       <c r="DO94" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP94" t="b">
         <v>0</v>
@@ -46277,7 +46277,7 @@
         <v>2.22</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF98" t="n">
         <v>1.83</v>
@@ -46730,7 +46730,7 @@
         <v>79</v>
       </c>
       <c r="DD99" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE99" t="n">
         <v>1.3</v>
@@ -47189,7 +47189,7 @@
         <v>1.44</v>
       </c>
       <c r="DE100" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF100" t="n">
         <v>1.67</v>
@@ -47219,7 +47219,7 @@
         <v>2.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47691,7 +47691,7 @@
         <v>4.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48114,10 +48114,10 @@
         <v>71</v>
       </c>
       <c r="DD102" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF102" t="n">
         <v>0.43</v>
@@ -48147,7 +48147,7 @@
         <v>2.15</v>
       </c>
       <c r="DO102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -49954,7 +49954,7 @@
         <v>79</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DE106" t="n">
         <v>1</v>
@@ -49987,7 +49987,7 @@
         <v>2.48</v>
       </c>
       <c r="DO106" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51361,7 +51361,7 @@
         <v>2.2</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF109" t="n">
         <v>2</v>
@@ -53211,7 +53211,7 @@
         <v>2.63</v>
       </c>
       <c r="DO113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53650,7 +53650,7 @@
         <v>63</v>
       </c>
       <c r="DD114" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE114" t="n">
         <v>1.3</v>
@@ -55485,7 +55485,7 @@
         <v>1.44</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF118" t="n">
         <v>1.86</v>
@@ -55515,7 +55515,7 @@
         <v>2.15</v>
       </c>
       <c r="DO118" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55957,7 +55957,7 @@
         <v>2.78</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DF119" t="n">
         <v>2.75</v>
@@ -56418,7 +56418,7 @@
         <v>82</v>
       </c>
       <c r="DD120" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE120" t="n">
         <v>2.22</v>
@@ -56890,7 +56890,7 @@
         <v>78</v>
       </c>
       <c r="DD121" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DE121" t="n">
         <v>0.1</v>
@@ -57829,7 +57829,7 @@
         <v>1.33</v>
       </c>
       <c r="DE123" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF123" t="n">
         <v>1.13</v>
@@ -59691,7 +59691,7 @@
         <v>2.37</v>
       </c>
       <c r="DO127" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61946,7 +61946,7 @@
         <v>72</v>
       </c>
       <c r="DD132" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DE132" t="n">
         <v>2.1</v>
@@ -62080,6 +62080,1358 @@
       <c r="EL132" t="inlineStr">
         <is>
           <t>1.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>20</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Panaitolikos</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>46060.625</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>4</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>5</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>7</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>2</v>
+      </c>
+      <c r="R133" t="n">
+        <v>5</v>
+      </c>
+      <c r="S133" t="n">
+        <v>9</v>
+      </c>
+      <c r="T133" t="n">
+        <v>3</v>
+      </c>
+      <c r="U133" t="n">
+        <v>11</v>
+      </c>
+      <c r="V133" t="n">
+        <v>8</v>
+      </c>
+      <c r="W133" t="n">
+        <v>16</v>
+      </c>
+      <c r="X133" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>AEL Arena</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>, Larissa</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1103</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>21</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>57</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>58</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>80</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>43</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW133" t="inlineStr"/>
+      <c r="DX133" t="inlineStr"/>
+      <c r="DY133" t="inlineStr"/>
+      <c r="DZ133" t="inlineStr"/>
+      <c r="EA133" t="inlineStr"/>
+      <c r="EB133" t="inlineStr"/>
+      <c r="EC133" t="inlineStr"/>
+      <c r="ED133" t="inlineStr"/>
+      <c r="EE133" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EF133" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EI133" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>20</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46060.66666666666</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2</v>
+      </c>
+      <c r="J134" t="n">
+        <v>11</v>
+      </c>
+      <c r="K134" t="n">
+        <v>5</v>
+      </c>
+      <c r="L134" t="n">
+        <v>16</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>2</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>7</v>
+      </c>
+      <c r="T134" t="n">
+        <v>11</v>
+      </c>
+      <c r="U134" t="n">
+        <v>9</v>
+      </c>
+      <c r="V134" t="n">
+        <v>12</v>
+      </c>
+      <c r="W134" t="n">
+        <v>10</v>
+      </c>
+      <c r="X134" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Stadio Theodoros Kolokotronis</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Liagora, Tripoli</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1107</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>47</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW134" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="DX134" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr"/>
+      <c r="EB134" t="inlineStr"/>
+      <c r="EC134" t="inlineStr"/>
+      <c r="ED134" t="inlineStr"/>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Greece_Super_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>20</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46060.75</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" t="n">
+        <v>8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>2</v>
+      </c>
+      <c r="R135" t="n">
+        <v>4</v>
+      </c>
+      <c r="S135" t="n">
+        <v>9</v>
+      </c>
+      <c r="T135" t="n">
+        <v>3</v>
+      </c>
+      <c r="U135" t="n">
+        <v>11</v>
+      </c>
+      <c r="V135" t="n">
+        <v>7</v>
+      </c>
+      <c r="W135" t="n">
+        <v>12</v>
+      </c>
+      <c r="X135" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Dimotiko Gipedo Neapolis Nikaias</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>Grigoriou Labraki &amp; Parnassou, Neapoli, Nikaia, Athens</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>1109</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW135" t="inlineStr"/>
+      <c r="DX135" t="inlineStr"/>
+      <c r="DY135" t="inlineStr"/>
+      <c r="DZ135" t="inlineStr"/>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="ED135" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
+          <t>2.69</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
+++ b/data/matches/leagues/Greece_Super_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL135" headerRowCount="1">
-  <autoFilter ref="A1:EL135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL139" headerRowCount="1">
+  <autoFilter ref="A1:EL139"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL135"/>
+  <dimension ref="A1:EL139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37.2" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE2" t="n">
         <v>0.5</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE3" t="n">
         <v>1.09</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE9" t="n">
         <v>1</v>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5454,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE10" t="n">
         <v>1.2</v>
@@ -5487,7 +5487,7 @@
         <v>1.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6415,7 +6415,7 @@
         <v>3.01</v>
       </c>
       <c r="DO12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6879,7 +6879,7 @@
         <v>3.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7321,7 +7321,7 @@
         <v>2.22</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7790,7 +7790,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE15" t="n">
         <v>0.1</v>
@@ -7823,7 +7823,7 @@
         <v>2.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8855,37 +8855,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -8897,122 +8897,122 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
         <v>8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Stadio Theodoros Kolokotronis</t>
+          <t>Dimotiko Stadio Neapolis Volou</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Liagora, Tripoli</t>
+          <t>Efstratios Argenti, Volos</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.2</v>
+        <v>4.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
       </c>
       <c r="BB18" t="n">
-        <v>-1</v>
+        <v>5168</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -9033,182 +9033,182 @@
         <v>1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BM18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO18" t="n">
         <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BS18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>67</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY18" t="n">
         <v>6</v>
       </c>
-      <c r="BU18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>43</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>96</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS18" t="n">
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO18" t="n">
         <v>19</v>
       </c>
-      <c r="CT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>50</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>20</v>
-      </c>
       <c r="DP18" t="b">
         <v>1</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="DT18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU18" t="b">
         <v>0</v>
@@ -9232,74 +9232,50 @@
       </c>
       <c r="DW18" t="inlineStr"/>
       <c r="DX18" t="inlineStr"/>
-      <c r="DY18" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="DZ18" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EA18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EB18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EC18" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+      <c r="DY18" t="inlineStr"/>
+      <c r="DZ18" t="inlineStr"/>
+      <c r="EA18" t="inlineStr"/>
+      <c r="EB18" t="inlineStr"/>
+      <c r="EC18" t="inlineStr"/>
+      <c r="ED18" t="inlineStr"/>
       <c r="EE18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EF18" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EH18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EI18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EJ18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -9319,37 +9295,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>45914.625</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
-        <v>9</v>
-      </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>4</v>
@@ -9361,122 +9337,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
       </c>
       <c r="V19" t="n">
+        <v>16</v>
+      </c>
+      <c r="W19" t="n">
         <v>12</v>
       </c>
-      <c r="W19" t="n">
-        <v>22</v>
-      </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Dimotiko Stadio Neapolis Volou</t>
+          <t>Stadio Theodoros Kolokotronis</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Efstratios Argenti, Volos</t>
+          <t>Liagora, Tripoli</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>6.5</v>
+        <v>1.93</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AS19" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5168</v>
+        <v>-1</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9497,64 +9473,64 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BW19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BX19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BY19" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9581,7 +9557,7 @@
         <v>1</v>
       </c>
       <c r="CK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -9602,77 +9578,77 @@
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="CS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DO19" t="n">
         <v>20</v>
       </c>
-      <c r="CV19" t="n">
-        <v>21</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO19" t="n">
-        <v>18</v>
-      </c>
       <c r="DP19" t="b">
         <v>1</v>
       </c>
@@ -9686,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="DT19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU19" t="b">
         <v>0</v>
@@ -9696,50 +9672,74 @@
       </c>
       <c r="DW19" t="inlineStr"/>
       <c r="DX19" t="inlineStr"/>
-      <c r="DY19" t="inlineStr"/>
-      <c r="DZ19" t="inlineStr"/>
-      <c r="EA19" t="inlineStr"/>
-      <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
-      <c r="ED19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EE19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="EG19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EH19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.65</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10081,7 @@
         <v>2.2</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10111,7 +10111,7 @@
         <v>1.51</v>
       </c>
       <c r="DO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10550,10 +10550,10 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE21" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10703,162 +10703,170 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" t="n">
         <v>15</v>
       </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
       <c r="W22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Stadio Panetolikou</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Nikitara, Agrinio</t>
+        </is>
+      </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.64</v>
+        <v>2.21</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ22" t="n">
         <v>1</v>
       </c>
       <c r="BA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>-1</v>
+        <v>5131</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -10873,40 +10881,40 @@
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL22" t="n">
         <v>4</v>
       </c>
       <c r="BM22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
       </c>
       <c r="BQ22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR22" t="n">
         <v>2</v>
       </c>
       <c r="BS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
@@ -10915,22 +10923,22 @@
         <v>41</v>
       </c>
       <c r="BW22" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="BX22" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.38</v>
+        <v>0.68</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -10963,10 +10971,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -10978,73 +10986,73 @@
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CW22" t="n">
         <v>1</v>
       </c>
       <c r="CX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY22" t="n">
         <v>6</v>
       </c>
-      <c r="CY22" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DA22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DB22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DC22" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="DF22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="DI22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DJ22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DK22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DL22" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="DM22" t="n">
-        <v>0.82</v>
+        <v>1.31</v>
       </c>
       <c r="DN22" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="DO22" t="n">
         <v>19</v>
@@ -11053,7 +11061,7 @@
         <v>1</v>
       </c>
       <c r="DQ22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR22" t="b">
         <v>0</v>
@@ -11068,78 +11076,78 @@
         <v>0</v>
       </c>
       <c r="DV22" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW22" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="DX22" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW22" t="inlineStr"/>
+      <c r="DX22" t="inlineStr"/>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EA22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EB22" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="EC22" t="inlineStr"/>
-      <c r="ED22" t="inlineStr"/>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EG22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EH22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EJ22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EL22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -11159,170 +11167,162 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>45920.625</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>15</v>
+      </c>
+      <c r="V23" t="n">
         <v>11</v>
       </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>15</v>
-      </c>
       <c r="W23" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Z23" t="n">
-        <v>71</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Stadio Panetolikou</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Nikitara, Agrinio</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD23" t="n">
         <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB23" t="n">
-        <v>5131</v>
+        <v>-1</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11337,40 +11337,40 @@
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL23" t="n">
         <v>4</v>
       </c>
       <c r="BM23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT23" t="n">
         <v>5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>3</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
@@ -11379,22 +11379,22 @@
         <v>41</v>
       </c>
       <c r="BW23" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="BX23" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BY23" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11427,10 +11427,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11442,82 +11442,82 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS23" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX23" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>75</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DO23" t="n">
         <v>20</v>
       </c>
-      <c r="CT23" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU23" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV23" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW23" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX23" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY23" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DA23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DC23" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD23" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DF23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DI23" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DM23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DN23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DO23" t="n">
-        <v>19</v>
-      </c>
       <c r="DP23" t="b">
         <v>1</v>
       </c>
       <c r="DQ23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR23" t="b">
         <v>0</v>
@@ -11532,78 +11532,78 @@
         <v>0</v>
       </c>
       <c r="DV23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW23" t="inlineStr"/>
-      <c r="DX23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="DY23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DZ23" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EA23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EB23" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EC23" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="ED23" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr"/>
+      <c r="ED23" t="inlineStr"/>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EG23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EH23" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EL23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.47</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
         <v>3.52</v>
       </c>
       <c r="DO25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -12853,7 +12853,7 @@
         <v>0.91</v>
       </c>
       <c r="DE26" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF26" t="n">
         <v>1</v>
@@ -12883,7 +12883,7 @@
         <v>3.53</v>
       </c>
       <c r="DO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13355,7 +13355,7 @@
         <v>2.98</v>
       </c>
       <c r="DO27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13811,7 +13811,7 @@
         <v>3.53</v>
       </c>
       <c r="DO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14250,10 +14250,10 @@
         <v>50</v>
       </c>
       <c r="DD29" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14283,7 +14283,7 @@
         <v>3.59</v>
       </c>
       <c r="DO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14698,7 +14698,7 @@
         <v>25</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE30" t="n">
         <v>0.1</v>
@@ -14731,7 +14731,7 @@
         <v>2.25</v>
       </c>
       <c r="DO30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15179,7 +15179,7 @@
         <v>3.39</v>
       </c>
       <c r="DO31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15618,7 +15618,7 @@
         <v>75</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE32" t="n">
         <v>1</v>
@@ -15651,7 +15651,7 @@
         <v>2.18</v>
       </c>
       <c r="DO32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16093,7 +16093,7 @@
         <v>1.1</v>
       </c>
       <c r="DE33" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -16123,7 +16123,7 @@
         <v>2.65</v>
       </c>
       <c r="DO33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16549,7 +16549,7 @@
         <v>0.6</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -16579,7 +16579,7 @@
         <v>2.33</v>
       </c>
       <c r="DO34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17482,7 +17482,7 @@
         <v>59</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE36" t="n">
         <v>0.5</v>
@@ -17515,7 +17515,7 @@
         <v>2.08</v>
       </c>
       <c r="DO36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17954,7 +17954,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE37" t="n">
         <v>1.3</v>
@@ -17987,7 +17987,7 @@
         <v>2.34</v>
       </c>
       <c r="DO37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18907,7 +18907,7 @@
         <v>2.34</v>
       </c>
       <c r="DO39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19349,7 +19349,7 @@
         <v>1</v>
       </c>
       <c r="DE40" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF40" t="n">
         <v>1.5</v>
@@ -19843,7 +19843,7 @@
         <v>4.03</v>
       </c>
       <c r="DO41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20315,7 +20315,7 @@
         <v>2.21</v>
       </c>
       <c r="DO42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20771,7 +20771,7 @@
         <v>2.78</v>
       </c>
       <c r="DO43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21213,7 +21213,7 @@
         <v>0.6</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF44" t="n">
         <v>0.5</v>
@@ -21243,7 +21243,7 @@
         <v>1.97</v>
       </c>
       <c r="DO44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21715,7 +21715,7 @@
         <v>1.91</v>
       </c>
       <c r="DO45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22659,7 +22659,7 @@
         <v>1.86</v>
       </c>
       <c r="DO47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23074,10 +23074,10 @@
         <v>67</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF48" t="n">
         <v>1.33</v>
@@ -23107,7 +23107,7 @@
         <v>3.52</v>
       </c>
       <c r="DO48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23541,7 +23541,7 @@
         <v>2.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF49" t="n">
         <v>3</v>
@@ -23571,7 +23571,7 @@
         <v>3.5</v>
       </c>
       <c r="DO49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24474,7 +24474,7 @@
         <v>67</v>
       </c>
       <c r="DD51" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE51" t="n">
         <v>1</v>
@@ -24507,7 +24507,7 @@
         <v>2.24</v>
       </c>
       <c r="DO51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24930,7 +24930,7 @@
         <v>75</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE52" t="n">
         <v>1.4</v>
@@ -24963,7 +24963,7 @@
         <v>1.7</v>
       </c>
       <c r="DO52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25435,7 +25435,7 @@
         <v>3.34</v>
       </c>
       <c r="DO53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25907,7 +25907,7 @@
         <v>2.55</v>
       </c>
       <c r="DO54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26371,7 +26371,7 @@
         <v>3.48</v>
       </c>
       <c r="DO55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26794,10 +26794,10 @@
         <v>33</v>
       </c>
       <c r="DD56" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE56" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF56" t="n">
         <v>3</v>
@@ -26827,7 +26827,7 @@
         <v>4.44</v>
       </c>
       <c r="DO56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27269,7 +27269,7 @@
         <v>1.44</v>
       </c>
       <c r="DE57" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF57" t="n">
         <v>2</v>
@@ -27299,7 +27299,7 @@
         <v>2.81</v>
       </c>
       <c r="DO57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28210,7 +28210,7 @@
         <v>63</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE59" t="n">
         <v>1.3</v>
@@ -28243,7 +28243,7 @@
         <v>3.69</v>
       </c>
       <c r="DO59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28685,7 +28685,7 @@
         <v>0.91</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF60" t="n">
         <v>0.5</v>
@@ -28715,7 +28715,7 @@
         <v>2.05</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29130,10 +29130,10 @@
         <v>88</v>
       </c>
       <c r="DD61" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE61" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF61" t="n">
         <v>1</v>
@@ -29163,7 +29163,7 @@
         <v>2.6</v>
       </c>
       <c r="DO61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29619,7 +29619,7 @@
         <v>2.68</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30091,7 +30091,7 @@
         <v>2.31</v>
       </c>
       <c r="DO63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30994,7 +30994,7 @@
         <v>65</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE65" t="n">
         <v>0.5</v>
@@ -31027,7 +31027,7 @@
         <v>2.65</v>
       </c>
       <c r="DO65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP65" t="b">
         <v>0</v>
@@ -31955,7 +31955,7 @@
         <v>2.27</v>
       </c>
       <c r="DO67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32394,10 +32394,10 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE68" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF68" t="n">
         <v>0.75</v>
@@ -32427,7 +32427,7 @@
         <v>2.64</v>
       </c>
       <c r="DO68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33317,7 +33317,7 @@
         <v>2.22</v>
       </c>
       <c r="DE70" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF70" t="n">
         <v>2</v>
@@ -33347,7 +33347,7 @@
         <v>3.3</v>
       </c>
       <c r="DO70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34242,7 +34242,7 @@
         <v>50</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE72" t="n">
         <v>1.4</v>
@@ -34275,7 +34275,7 @@
         <v>3.04</v>
       </c>
       <c r="DO72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34706,10 +34706,10 @@
         <v>90</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE73" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF73" t="n">
         <v>0.8</v>
@@ -34739,7 +34739,7 @@
         <v>2.59</v>
       </c>
       <c r="DO73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35203,7 +35203,7 @@
         <v>3.9</v>
       </c>
       <c r="DO74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35659,7 +35659,7 @@
         <v>3.23</v>
       </c>
       <c r="DO75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36085,7 +36085,7 @@
         <v>1.44</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF76" t="n">
         <v>2.25</v>
@@ -36115,7 +36115,7 @@
         <v>2.12</v>
       </c>
       <c r="DO76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36579,7 +36579,7 @@
         <v>2.4</v>
       </c>
       <c r="DO77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -37002,7 +37002,7 @@
         <v>65</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE78" t="n">
         <v>1.09</v>
@@ -37035,7 +37035,7 @@
         <v>1.95</v>
       </c>
       <c r="DO78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37139,120 +37139,128 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>6</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="n">
         <v>5</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>8</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
       <c r="U79" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W79" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y79" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Z79" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Stadio Zirinio</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Kifissia, Athens</t>
+        </is>
+      </c>
       <c r="AC79" t="n">
         <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF79" t="n">
-        <v>4.18</v>
+        <v>3.5</v>
       </c>
       <c r="AG79" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI79" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ79" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK79" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.41</v>
@@ -37261,10 +37269,10 @@
         <v>2.75</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AU79" t="n">
         <v>3</v>
@@ -37276,10 +37284,10 @@
         <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
         <v>2</v>
@@ -37288,13 +37296,13 @@
         <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>5131</v>
+        <v>5168</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37309,19 +37317,19 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN79" t="n">
         <v>5</v>
@@ -37330,55 +37338,55 @@
         <v>1</v>
       </c>
       <c r="BP79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT79" t="n">
         <v>4</v>
       </c>
-      <c r="BT79" t="n">
-        <v>6</v>
-      </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="BW79" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BX79" t="n">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="BY79" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BZ79" t="n">
         <v>2.03</v>
       </c>
       <c r="CA79" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="CB79" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE79" t="n">
         <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -37399,7 +37407,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -37414,73 +37422,73 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CS79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CY79" t="n">
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DA79" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC79" t="n">
         <v>80</v>
       </c>
-      <c r="DB79" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC79" t="n">
-        <v>60</v>
-      </c>
       <c r="DD79" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DE79" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DG79" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH79" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="DJ79" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DK79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.96</v>
+        <v>1.76</v>
       </c>
       <c r="DO79" t="n">
         <v>19</v>
@@ -37504,86 +37512,86 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DX79" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.91</t>
         </is>
       </c>
     </row>
@@ -37603,128 +37611,120 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45990.72916666666</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>7</v>
+      </c>
+      <c r="M80" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
         <v>8</v>
       </c>
-      <c r="M80" t="n">
-        <v>2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>6</v>
-      </c>
       <c r="R80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
+        <v>18</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>14</v>
+      </c>
+      <c r="X80" t="n">
         <v>21</v>
       </c>
-      <c r="V80" t="n">
-        <v>6</v>
-      </c>
-      <c r="W80" t="n">
-        <v>11</v>
-      </c>
-      <c r="X80" t="n">
-        <v>13</v>
-      </c>
       <c r="Y80" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z80" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Stadio Zirinio</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>Kifissia, Athens</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="AG80" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI80" t="n">
         <v>1.97</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.41</v>
@@ -37733,10 +37733,10 @@
         <v>2.75</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AU80" t="n">
         <v>3</v>
@@ -37748,10 +37748,10 @@
         <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ80" t="n">
         <v>2</v>
@@ -37760,13 +37760,13 @@
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>5168</v>
+        <v>5131</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -37781,19 +37781,19 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN80" t="n">
         <v>5</v>
@@ -37802,55 +37802,55 @@
         <v>1</v>
       </c>
       <c r="BP80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="BW80" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="BX80" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="BY80" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ80" t="n">
         <v>2.03</v>
       </c>
       <c r="CA80" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="CB80" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
       </c>
       <c r="CD80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE80" t="n">
         <v>0</v>
       </c>
       <c r="CF80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG80" t="n">
         <v>0</v>
@@ -37871,7 +37871,7 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
@@ -37886,76 +37886,76 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS80" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
       </c>
       <c r="CU80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV80" t="n">
         <v>13</v>
       </c>
-      <c r="CV80" t="n">
-        <v>11</v>
-      </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CY80" t="n">
         <v>9</v>
       </c>
       <c r="CZ80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC80" t="n">
         <v>60</v>
       </c>
-      <c r="DA80" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC80" t="n">
+      <c r="DD80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ80" t="n">
         <v>80</v>
       </c>
-      <c r="DD80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>40</v>
-      </c>
       <c r="DK80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="DM80" t="n">
-        <v>0.61</v>
+        <v>1.34</v>
       </c>
       <c r="DN80" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="DO80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37976,86 +37976,86 @@
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW80" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DX80" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DY80" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EF80" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="EG80" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH80" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI80" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -38899,7 +38899,7 @@
         <v>2.5</v>
       </c>
       <c r="DO82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39341,7 +39341,7 @@
         <v>2.2</v>
       </c>
       <c r="DE83" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF83" t="n">
         <v>2.17</v>
@@ -39371,7 +39371,7 @@
         <v>3.21</v>
       </c>
       <c r="DO83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39813,7 +39813,7 @@
         <v>2.22</v>
       </c>
       <c r="DE84" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF84" t="n">
         <v>2.2</v>
@@ -39843,7 +39843,7 @@
         <v>3.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40282,7 +40282,7 @@
         <v>55</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE85" t="n">
         <v>1</v>
@@ -40315,7 +40315,7 @@
         <v>3.31</v>
       </c>
       <c r="DO85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41205,7 +41205,7 @@
         <v>1.1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DF87" t="n">
         <v>1.4</v>
@@ -41235,7 +41235,7 @@
         <v>2.39</v>
       </c>
       <c r="DO87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -41669,7 +41669,7 @@
         <v>0.91</v>
       </c>
       <c r="DE88" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF88" t="n">
         <v>0.33</v>
@@ -41699,7 +41699,7 @@
         <v>3.02</v>
       </c>
       <c r="DO88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42147,7 +42147,7 @@
         <v>3.26</v>
       </c>
       <c r="DO89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42595,7 +42595,7 @@
         <v>2.86</v>
       </c>
       <c r="DO90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43010,7 +43010,7 @@
         <v>67</v>
       </c>
       <c r="DD91" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DE91" t="n">
         <v>1.2</v>
@@ -43043,7 +43043,7 @@
         <v>1.9</v>
       </c>
       <c r="DO91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43499,7 +43499,7 @@
         <v>2.88</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43938,7 +43938,7 @@
         <v>75</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE93" t="n">
         <v>0.1</v>
@@ -43971,7 +43971,7 @@
         <v>1.48</v>
       </c>
       <c r="DO93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44869,7 +44869,7 @@
         <v>0.6</v>
       </c>
       <c r="DE95" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF95" t="n">
         <v>1</v>
@@ -44899,7 +44899,7 @@
         <v>2.56</v>
       </c>
       <c r="DO95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45341,7 +45341,7 @@
         <v>0.6</v>
       </c>
       <c r="DE96" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DF96" t="n">
         <v>0.33</v>
@@ -45371,7 +45371,7 @@
         <v>2.92</v>
       </c>
       <c r="DO96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45802,7 +45802,7 @@
         <v>50</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DE97" t="n">
         <v>2.1</v>
@@ -45835,7 +45835,7 @@
         <v>3.37</v>
       </c>
       <c r="DO97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -46307,7 +46307,7 @@
         <v>2.65</v>
       </c>
       <c r="DO98" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46763,7 +46763,7 @@
         <v>2.41</v>
       </c>
       <c r="DO99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47658,7 +47658,7 @@
         <v>64</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="DE101" t="n">
         <v>1</v>
@@ -48581,7 +48581,7 @@
         <v>2.8</v>
       </c>
       <c r="DE103" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF103" t="n">
         <v>2.71</v>
@@ -48611,7 +48611,7 @@
         <v>3.68</v>
       </c>
       <c r="DO103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP1